--- a/resultados_algoritmos/datos_para_RISK.xlsx
+++ b/resultados_algoritmos/datos_para_RISK.xlsx
@@ -480,3802 +480,3802 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>0.1977920182980597</v>
+        <v>0.2712999994400889</v>
       </c>
       <c r="B2" t="n">
-        <v>0.1177919912151992</v>
+        <v>0.1774999982444569</v>
       </c>
       <c r="C2" t="n">
-        <v>0.07745801121927798</v>
+        <v>0.1371999969705939</v>
       </c>
       <c r="D2" t="n">
-        <v>0.9706249984446913</v>
+        <v>1.680800007306971</v>
       </c>
       <c r="E2" t="n">
-        <v>0.4784160119015723</v>
+        <v>0.7436000014422461</v>
       </c>
       <c r="F2" t="n">
-        <v>0.2379590005148202</v>
+        <v>0.2892000047722831</v>
       </c>
       <c r="G2" t="n">
-        <v>4.826917022000998</v>
+        <v>7.054299989249557</v>
       </c>
       <c r="H2" t="n">
-        <v>2.005583985010162</v>
+        <v>3.378299996256828</v>
       </c>
       <c r="I2" t="n">
-        <v>0.4427079984452575</v>
+        <v>0.5945000011706725</v>
       </c>
       <c r="J2" t="n">
-        <v>21.3391249999404</v>
+        <v>33.53290000814013</v>
       </c>
       <c r="K2" t="n">
-        <v>8.676292025484145</v>
+        <v>14.27349999721628</v>
       </c>
       <c r="L2" t="n">
-        <v>0.8537089743185788</v>
+        <v>1.265899991267361</v>
       </c>
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>0.179166003363207</v>
+        <v>0.2815999905578792</v>
       </c>
       <c r="B3" t="n">
-        <v>0.08624998736195266</v>
+        <v>0.1457999896956608</v>
       </c>
       <c r="C3" t="n">
-        <v>0.08691599941812456</v>
+        <v>0.1008999970508739</v>
       </c>
       <c r="D3" t="n">
-        <v>1.048167003318667</v>
+        <v>1.834800001233816</v>
       </c>
       <c r="E3" t="n">
-        <v>0.4590829776134342</v>
+        <v>0.9172999998554587</v>
       </c>
       <c r="F3" t="n">
-        <v>0.1726250047795475</v>
+        <v>0.2712999994400889</v>
       </c>
       <c r="G3" t="n">
-        <v>4.602125001838431</v>
+        <v>7.045499995001592</v>
       </c>
       <c r="H3" t="n">
-        <v>1.825209008529782</v>
+        <v>3.131899997242726</v>
       </c>
       <c r="I3" t="n">
-        <v>0.370249996194616</v>
+        <v>0.5990000063320622</v>
       </c>
       <c r="J3" t="n">
-        <v>21.31116698728874</v>
+        <v>30.88570000545587</v>
       </c>
       <c r="K3" t="n">
-        <v>8.586874988395721</v>
+        <v>13.6179999972228</v>
       </c>
       <c r="L3" t="n">
-        <v>0.8132499933708459</v>
+        <v>1.271300003281794</v>
       </c>
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>0.1946669945027679</v>
+        <v>0.2867000002879649</v>
       </c>
       <c r="B4" t="n">
-        <v>0.07700000423938036</v>
+        <v>0.141500000609085</v>
       </c>
       <c r="C4" t="n">
-        <v>0.0659999786876142</v>
+        <v>0.1017000031424686</v>
       </c>
       <c r="D4" t="n">
-        <v>1.07308299629949</v>
+        <v>1.785600004950538</v>
       </c>
       <c r="E4" t="n">
-        <v>0.4694999952334911</v>
+        <v>0.8812000014586374</v>
       </c>
       <c r="F4" t="n">
-        <v>0.1707079936750233</v>
+        <v>0.2714000002015382</v>
       </c>
       <c r="G4" t="n">
-        <v>4.705833998741582</v>
+        <v>7.268899993505329</v>
       </c>
       <c r="H4" t="n">
-        <v>1.891082996735349</v>
+        <v>3.298600000562146</v>
       </c>
       <c r="I4" t="n">
-        <v>0.3732919867616147</v>
+        <v>0.5986000032862648</v>
       </c>
       <c r="J4" t="n">
-        <v>21.34145799209364</v>
+        <v>30.65020000212826</v>
       </c>
       <c r="K4" t="n">
-        <v>8.702041988726705</v>
+        <v>13.86669999919832</v>
       </c>
       <c r="L4" t="n">
-        <v>0.8122079889290035</v>
+        <v>1.27500000235159</v>
       </c>
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>0.2047909947577864</v>
+        <v>0.2948999899672344</v>
       </c>
       <c r="B5" t="n">
-        <v>0.08525000885128975</v>
+        <v>0.1566999999340624</v>
       </c>
       <c r="C5" t="n">
-        <v>0.06554200081154704</v>
+        <v>0.1020000054268166</v>
       </c>
       <c r="D5" t="n">
-        <v>1.049958984367549</v>
+        <v>1.808999993954785</v>
       </c>
       <c r="E5" t="n">
-        <v>0.4242910072207451</v>
+        <v>0.8317000028910115</v>
       </c>
       <c r="F5" t="n">
-        <v>0.1789999951142818</v>
+        <v>0.2717000024858862</v>
       </c>
       <c r="G5" t="n">
-        <v>4.649040987715125</v>
+        <v>7.139599998481572</v>
       </c>
       <c r="H5" t="n">
-        <v>1.954334002221003</v>
+        <v>3.384299998288043</v>
       </c>
       <c r="I5" t="n">
-        <v>0.3737910010386258</v>
+        <v>0.5941999988863245</v>
       </c>
       <c r="J5" t="n">
-        <v>21.40179197886027</v>
+        <v>31.17799999017734</v>
       </c>
       <c r="K5" t="n">
-        <v>8.613332989625633</v>
+        <v>13.64640000974759</v>
       </c>
       <c r="L5" t="n">
-        <v>0.8195839764084667</v>
+        <v>1.261099998373538</v>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>0.1641659764572978</v>
+        <v>0.2590999938547611</v>
       </c>
       <c r="B6" t="n">
-        <v>0.06404201849363744</v>
+        <v>0.1243000006070361</v>
       </c>
       <c r="C6" t="n">
-        <v>0.06474999827332795</v>
+        <v>0.1027999969664961</v>
       </c>
       <c r="D6" t="n">
-        <v>1.074583997251466</v>
+        <v>1.733700002660044</v>
       </c>
       <c r="E6" t="n">
-        <v>0.4588750016409904</v>
+        <v>0.8674999990034848</v>
       </c>
       <c r="F6" t="n">
-        <v>0.175583001691848</v>
+        <v>0.2708999963942915</v>
       </c>
       <c r="G6" t="n">
-        <v>4.81933300034143</v>
+        <v>7.262599989189766</v>
       </c>
       <c r="H6" t="n">
-        <v>2.058250014670193</v>
+        <v>3.501999992295168</v>
       </c>
       <c r="I6" t="n">
-        <v>0.3752910124603659</v>
+        <v>0.5947999889031053</v>
       </c>
       <c r="J6" t="n">
-        <v>21.67066599940881</v>
+        <v>31.67900000698864</v>
       </c>
       <c r="K6" t="n">
-        <v>8.792125008767471</v>
+        <v>13.95759999286383</v>
       </c>
       <c r="L6" t="n">
-        <v>0.8109580085147172</v>
+        <v>1.289099993300624</v>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>0.1479579950682819</v>
+        <v>0.2589999930933118</v>
       </c>
       <c r="B7" t="n">
-        <v>0.06370799383148551</v>
+        <v>0.1274999958695844</v>
       </c>
       <c r="C7" t="n">
-        <v>0.06170800770632923</v>
+        <v>0.09869999485090375</v>
       </c>
       <c r="D7" t="n">
-        <v>1.053166983183473</v>
+        <v>1.735800004098564</v>
       </c>
       <c r="E7" t="n">
-        <v>0.4497080226428807</v>
+        <v>0.8831999875837937</v>
       </c>
       <c r="F7" t="n">
-        <v>0.1738749851938337</v>
+        <v>0.2759000053629279</v>
       </c>
       <c r="G7" t="n">
-        <v>4.806333978194743</v>
+        <v>7.3302000091644</v>
       </c>
       <c r="H7" t="n">
-        <v>2.057041972875595</v>
+        <v>3.563200007192791</v>
       </c>
       <c r="I7" t="n">
-        <v>0.3717920044437051</v>
+        <v>0.6009000062476844</v>
       </c>
       <c r="J7" t="n">
-        <v>21.45629201550037</v>
+        <v>31.27530000347178</v>
       </c>
       <c r="K7" t="n">
-        <v>8.732624992262572</v>
+        <v>13.86160000402015</v>
       </c>
       <c r="L7" t="n">
-        <v>0.8133329974953085</v>
+        <v>1.280499986023642</v>
       </c>
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>0.1609580067452043</v>
+        <v>0.2773000014713034</v>
       </c>
       <c r="B8" t="n">
-        <v>0.06879199645482004</v>
+        <v>0.1388000091537833</v>
       </c>
       <c r="C8" t="n">
-        <v>0.06362498970702291</v>
+        <v>0.09840000711847097</v>
       </c>
       <c r="D8" t="n">
-        <v>1.067292003426701</v>
+        <v>1.828499996918254</v>
       </c>
       <c r="E8" t="n">
-        <v>0.4737919953186065</v>
+        <v>0.934299998334609</v>
       </c>
       <c r="F8" t="n">
-        <v>0.1784170162864029</v>
+        <v>0.2778000052785501</v>
       </c>
       <c r="G8" t="n">
-        <v>4.553041973849759</v>
+        <v>6.96730001072865</v>
       </c>
       <c r="H8" t="n">
-        <v>1.800124999135733</v>
+        <v>3.160399995977059</v>
       </c>
       <c r="I8" t="n">
-        <v>0.3712089965119958</v>
+        <v>0.5930000043008476</v>
       </c>
       <c r="J8" t="n">
-        <v>21.3925419957377</v>
+        <v>31.41860000323504</v>
       </c>
       <c r="K8" t="n">
-        <v>8.748166990699247</v>
+        <v>13.86920000368264</v>
       </c>
       <c r="L8" t="n">
-        <v>0.8087090100161731</v>
+        <v>1.290800006245263</v>
       </c>
     </row>
     <row r="9">
       <c r="A9" t="n">
-        <v>0.1598749950062484</v>
+        <v>0.3029000072274357</v>
       </c>
       <c r="B9" t="n">
-        <v>0.07166698924265802</v>
+        <v>0.1420000044163316</v>
       </c>
       <c r="C9" t="n">
-        <v>0.06141597987152636</v>
+        <v>0.09800000407267362</v>
       </c>
       <c r="D9" t="n">
-        <v>0.9942920005414635</v>
+        <v>1.639599999180064</v>
       </c>
       <c r="E9" t="n">
-        <v>0.420292024500668</v>
+        <v>0.8323000074597076</v>
       </c>
       <c r="F9" t="n">
-        <v>0.17120799748227</v>
+        <v>0.2742999931797385</v>
       </c>
       <c r="G9" t="n">
-        <v>4.846875002840534</v>
+        <v>7.419899993692525</v>
       </c>
       <c r="H9" t="n">
-        <v>2.020208979956806</v>
+        <v>3.538700009812601</v>
       </c>
       <c r="I9" t="n">
-        <v>0.3686249838210642</v>
+        <v>0.5954000080237165</v>
       </c>
       <c r="J9" t="n">
-        <v>21.5898749884218</v>
+        <v>31.38740001304541</v>
       </c>
       <c r="K9" t="n">
-        <v>8.770749991526827</v>
+        <v>14.0118999988772</v>
       </c>
       <c r="L9" t="n">
-        <v>0.8188339998014271</v>
+        <v>1.29420000303071</v>
       </c>
     </row>
     <row r="10">
       <c r="A10" t="n">
-        <v>0.1732500095386058</v>
+        <v>0.2813000028254464</v>
       </c>
       <c r="B10" t="n">
-        <v>0.07820900646038353</v>
+        <v>0.1456000027246773</v>
       </c>
       <c r="C10" t="n">
-        <v>0.0635419855825603</v>
+        <v>0.09970000246539712</v>
       </c>
       <c r="D10" t="n">
-        <v>1.012958004139364</v>
+        <v>1.679100008914247</v>
       </c>
       <c r="E10" t="n">
-        <v>0.4024159861728549</v>
+        <v>0.7812999974703416</v>
       </c>
       <c r="F10" t="n">
-        <v>0.1718330022413284</v>
+        <v>0.2834999904735014</v>
       </c>
       <c r="G10" t="n">
-        <v>4.639417020371184</v>
+        <v>7.106200006091967</v>
       </c>
       <c r="H10" t="n">
-        <v>1.876374997664243</v>
+        <v>3.322199991089292</v>
       </c>
       <c r="I10" t="n">
-        <v>0.3726249851752073</v>
+        <v>0.6980000034673139</v>
       </c>
       <c r="J10" t="n">
-        <v>21.31895802449435</v>
+        <v>31.17059999203775</v>
       </c>
       <c r="K10" t="n">
-        <v>8.550958009436727</v>
+        <v>13.56650001253001</v>
       </c>
       <c r="L10" t="n">
-        <v>0.8154999813996255</v>
+        <v>1.280199998291209</v>
       </c>
     </row>
     <row r="11">
       <c r="A11" t="n">
-        <v>0.1544579863548279</v>
+        <v>0.2779999922495335</v>
       </c>
       <c r="B11" t="n">
-        <v>0.06895797559991479</v>
+        <v>0.1311000087298453</v>
       </c>
       <c r="C11" t="n">
-        <v>0.06312501500360668</v>
+        <v>0.0973999995039776</v>
       </c>
       <c r="D11" t="n">
-        <v>1.054833002854139</v>
+        <v>1.714300000458024</v>
       </c>
       <c r="E11" t="n">
-        <v>0.4359580052550882</v>
+        <v>0.8343999943463132</v>
       </c>
       <c r="F11" t="n">
-        <v>0.1718749990686774</v>
+        <v>0.2728000108618289</v>
       </c>
       <c r="G11" t="n">
-        <v>4.762749973451719</v>
+        <v>7.238899997901171</v>
       </c>
       <c r="H11" t="n">
-        <v>1.961458998266608</v>
+        <v>3.461300002527423</v>
       </c>
       <c r="I11" t="n">
-        <v>0.3727090079337358</v>
+        <v>0.5932999920332804</v>
       </c>
       <c r="J11" t="n">
-        <v>21.11837500706315</v>
+        <v>31.32700000423938</v>
       </c>
       <c r="K11" t="n">
-        <v>8.500416995957494</v>
+        <v>13.43479999923147</v>
       </c>
       <c r="L11" t="n">
-        <v>0.811167003121227</v>
+        <v>1.288800005568191</v>
       </c>
     </row>
     <row r="12">
       <c r="A12" t="n">
-        <v>0.1713749952614307</v>
+        <v>0.2659000019775704</v>
       </c>
       <c r="B12" t="n">
-        <v>0.06929200026206672</v>
+        <v>0.1226000022143126</v>
       </c>
       <c r="C12" t="n">
-        <v>0.06916699931025505</v>
+        <v>0.09900001168716699</v>
       </c>
       <c r="D12" t="n">
-        <v>1.00899999961257</v>
+        <v>1.799699995899573</v>
       </c>
       <c r="E12" t="n">
-        <v>0.5094160151202232</v>
+        <v>0.8803999953670427</v>
       </c>
       <c r="F12" t="n">
-        <v>0.1740419829729944</v>
+        <v>0.2792000013869256</v>
       </c>
       <c r="G12" t="n">
-        <v>5.057834001490846</v>
+        <v>7.538000005297363</v>
       </c>
       <c r="H12" t="n">
-        <v>2.092500013532117</v>
+        <v>3.583900004741736</v>
       </c>
       <c r="I12" t="n">
-        <v>0.3817919932771474</v>
+        <v>0.5893000052310526</v>
       </c>
       <c r="J12" t="n">
-        <v>21.39258300303482</v>
+        <v>30.34019999904558</v>
       </c>
       <c r="K12" t="n">
-        <v>8.813874999759719</v>
+        <v>13.66810000035912</v>
       </c>
       <c r="L12" t="n">
-        <v>0.9217909828294069</v>
+        <v>1.435099999071099</v>
       </c>
     </row>
     <row r="13">
       <c r="A13" t="n">
-        <v>0.1733340031933039</v>
+        <v>0.2724000078160316</v>
       </c>
       <c r="B13" t="n">
-        <v>0.0720839889254421</v>
+        <v>0.1241999998455867</v>
       </c>
       <c r="C13" t="n">
-        <v>0.06983400089666247</v>
+        <v>0.1023999939206988</v>
       </c>
       <c r="D13" t="n">
-        <v>0.9690419828984886</v>
+        <v>1.56089999654796</v>
       </c>
       <c r="E13" t="n">
-        <v>0.4072080191690475</v>
+        <v>0.7710999925620854</v>
       </c>
       <c r="F13" t="n">
-        <v>0.1706669863779098</v>
+        <v>0.2822999958880246</v>
       </c>
       <c r="G13" t="n">
-        <v>4.739124997286126</v>
+        <v>6.960800004890189</v>
       </c>
       <c r="H13" t="n">
-        <v>1.850166998337954</v>
+        <v>3.351000006659888</v>
       </c>
       <c r="I13" t="n">
-        <v>0.3814579977188259</v>
+        <v>0.5903999990550801</v>
       </c>
       <c r="J13" t="n">
-        <v>21.17449999786913</v>
+        <v>29.79230000346433</v>
       </c>
       <c r="K13" t="n">
-        <v>8.809124992694706</v>
+        <v>13.97450000513345</v>
       </c>
       <c r="L13" t="n">
-        <v>0.8084579894784838</v>
+        <v>1.282500001252629</v>
       </c>
     </row>
     <row r="14">
       <c r="A14" t="n">
-        <v>0.1782499894034117</v>
+        <v>0.2697999880183488</v>
       </c>
       <c r="B14" t="n">
-        <v>0.07237499812617898</v>
+        <v>0.1323000033153221</v>
       </c>
       <c r="C14" t="n">
-        <v>0.06766599835827947</v>
+        <v>0.09919999865815043</v>
       </c>
       <c r="D14" t="n">
-        <v>1.044791017193347</v>
+        <v>1.696699997410178</v>
       </c>
       <c r="E14" t="n">
-        <v>0.4650419868994504</v>
+        <v>0.8720999903744087</v>
       </c>
       <c r="F14" t="n">
-        <v>0.1821250189095736</v>
+        <v>0.2729999978328124</v>
       </c>
       <c r="G14" t="n">
-        <v>4.729166015749797</v>
+        <v>7.165999995777383</v>
       </c>
       <c r="H14" t="n">
-        <v>1.985707989661023</v>
+        <v>3.458600011072122</v>
       </c>
       <c r="I14" t="n">
-        <v>0.3741669934242964</v>
+        <v>0.5881000106455758</v>
       </c>
       <c r="J14" t="n">
-        <v>21.37991698691621</v>
+        <v>30.71009999257512</v>
       </c>
       <c r="K14" t="n">
-        <v>8.723042003111914</v>
+        <v>13.80950000020675</v>
       </c>
       <c r="L14" t="n">
-        <v>0.8149160130415112</v>
+        <v>1.311100000748411</v>
       </c>
     </row>
     <row r="15">
       <c r="A15" t="n">
-        <v>0.1542500103823841</v>
+        <v>0.2420999953756109</v>
       </c>
       <c r="B15" t="n">
-        <v>0.06387499161064625</v>
+        <v>0.1181999978143722</v>
       </c>
       <c r="C15" t="n">
-        <v>0.06291599129326642</v>
+        <v>0.09929999941959977</v>
       </c>
       <c r="D15" t="n">
-        <v>0.9769999887794256</v>
+        <v>1.606399993761443</v>
       </c>
       <c r="E15" t="n">
-        <v>0.4137499781791121</v>
+        <v>0.7926000107545406</v>
       </c>
       <c r="F15" t="n">
-        <v>0.2091669884976</v>
+        <v>0.2736000024015084</v>
       </c>
       <c r="G15" t="n">
-        <v>4.672915994888172</v>
+        <v>7.061099997372366</v>
       </c>
       <c r="H15" t="n">
-        <v>1.897499983897433</v>
+        <v>3.37809999473393</v>
       </c>
       <c r="I15" t="n">
-        <v>0.3733339835889637</v>
+        <v>0.5903999990550801</v>
       </c>
       <c r="J15" t="n">
-        <v>21.49625000311062</v>
+        <v>30.61109999543987</v>
       </c>
       <c r="K15" t="n">
-        <v>8.727500011445954</v>
+        <v>13.74899999063928</v>
       </c>
       <c r="L15" t="n">
-        <v>0.8415829797741026</v>
+        <v>1.292900007683784</v>
       </c>
     </row>
     <row r="16">
       <c r="A16" t="n">
-        <v>0.1772499817889184</v>
+        <v>0.2871000033337623</v>
       </c>
       <c r="B16" t="n">
-        <v>0.07766700582578778</v>
+        <v>0.1441000058548525</v>
       </c>
       <c r="C16" t="n">
-        <v>0.06366698653437197</v>
+        <v>0.0990999978967011</v>
       </c>
       <c r="D16" t="n">
-        <v>1.051833009114489</v>
+        <v>1.750600000377744</v>
       </c>
       <c r="E16" t="n">
-        <v>0.4333750111982226</v>
+        <v>0.8361000072909519</v>
       </c>
       <c r="F16" t="n">
-        <v>0.1753749966155738</v>
+        <v>0.2750999992713332</v>
       </c>
       <c r="G16" t="n">
-        <v>4.622374981408939</v>
+        <v>6.852899998193607</v>
       </c>
       <c r="H16" t="n">
-        <v>1.970792014617473</v>
+        <v>3.443499997956678</v>
       </c>
       <c r="I16" t="n">
-        <v>0.3710839955601841</v>
+        <v>0.5920999974478036</v>
       </c>
       <c r="J16" t="n">
-        <v>21.1017920228187</v>
+        <v>30.12009999656584</v>
       </c>
       <c r="K16" t="n">
-        <v>8.359125000424683</v>
+        <v>13.20180000038818</v>
       </c>
       <c r="L16" t="n">
-        <v>0.8138339908327907</v>
+        <v>1.290700005483814</v>
       </c>
     </row>
     <row r="17">
       <c r="A17" t="n">
-        <v>0.1586659927852452</v>
+        <v>0.2485000004526228</v>
       </c>
       <c r="B17" t="n">
-        <v>0.06570797995664179</v>
+        <v>0.11629999789875</v>
       </c>
       <c r="C17" t="n">
-        <v>0.1051249855663627</v>
+        <v>0.09719999798107892</v>
       </c>
       <c r="D17" t="n">
-        <v>1.007832994218916</v>
+        <v>1.674300001468509</v>
       </c>
       <c r="E17" t="n">
-        <v>0.422792014433071</v>
+        <v>0.81490000593476</v>
       </c>
       <c r="F17" t="n">
-        <v>0.1851249835453928</v>
+        <v>0.2755000023171306</v>
       </c>
       <c r="G17" t="n">
-        <v>4.614167002728209</v>
+        <v>6.946100009372458</v>
       </c>
       <c r="H17" t="n">
-        <v>1.851292006904259</v>
+        <v>3.264700004365295</v>
       </c>
       <c r="I17" t="n">
-        <v>0.3719580126926303</v>
+        <v>0.5872000037925318</v>
       </c>
       <c r="J17" t="n">
-        <v>21.35670901043341</v>
+        <v>30.6739999941783</v>
       </c>
       <c r="K17" t="n">
-        <v>8.742584002902731</v>
+        <v>13.6140999966301</v>
       </c>
       <c r="L17" t="n">
-        <v>0.809291988844052</v>
+        <v>1.285999998799525</v>
       </c>
     </row>
     <row r="18">
       <c r="A18" t="n">
-        <v>0.1647089957259595</v>
+        <v>0.2460999967297539</v>
       </c>
       <c r="B18" t="n">
-        <v>0.07695800741203129</v>
+        <v>0.1211000053444877</v>
       </c>
       <c r="C18" t="n">
-        <v>0.06204101373441517</v>
+        <v>0.09849999332800508</v>
       </c>
       <c r="D18" t="n">
-        <v>0.9696249908301979</v>
+        <v>1.675899999099784</v>
       </c>
       <c r="E18" t="n">
-        <v>0.3894999972544611</v>
+        <v>0.7748999923933297</v>
       </c>
       <c r="F18" t="n">
-        <v>0.1686250034254044</v>
+        <v>0.272299992502667</v>
       </c>
       <c r="G18" t="n">
-        <v>4.768958024214953</v>
+        <v>7.086699988576584</v>
       </c>
       <c r="H18" t="n">
-        <v>1.980875007575378</v>
+        <v>3.480900006252341</v>
       </c>
       <c r="I18" t="n">
-        <v>0.3715000057127327</v>
+        <v>0.5898999952478334</v>
       </c>
       <c r="J18" t="n">
-        <v>21.79108301061206</v>
+        <v>31.12929999770131</v>
       </c>
       <c r="K18" t="n">
-        <v>8.874042017851025</v>
+        <v>13.78009999461938</v>
       </c>
       <c r="L18" t="n">
-        <v>0.8160409925039858</v>
+        <v>1.280500000575557</v>
       </c>
     </row>
     <row r="19">
       <c r="A19" t="n">
-        <v>0.1830419932957739</v>
+        <v>0.269199998001568</v>
       </c>
       <c r="B19" t="n">
-        <v>0.08116700337268412</v>
+        <v>0.1376000000163913</v>
       </c>
       <c r="C19" t="n">
-        <v>0.06937500438652933</v>
+        <v>0.0973999995039776</v>
       </c>
       <c r="D19" t="n">
-        <v>1.037333015119657</v>
+        <v>1.687600000877865</v>
       </c>
       <c r="E19" t="n">
-        <v>0.4240000271238387</v>
+        <v>0.814300001366064</v>
       </c>
       <c r="F19" t="n">
-        <v>0.1677909749560058</v>
+        <v>0.2754999877652153</v>
       </c>
       <c r="G19" t="n">
-        <v>4.70458299969323</v>
+        <v>7.084800003212877</v>
       </c>
       <c r="H19" t="n">
-        <v>1.976917003048584</v>
+        <v>3.464199995505624</v>
       </c>
       <c r="I19" t="n">
-        <v>0.3742080007214099</v>
+        <v>0.5862999969394878</v>
       </c>
       <c r="J19" t="n">
-        <v>21.41799998935312</v>
+        <v>30.25450000131968</v>
       </c>
       <c r="K19" t="n">
-        <v>8.643042005132884</v>
+        <v>13.64380000450183</v>
       </c>
       <c r="L19" t="n">
-        <v>0.8207079954445362</v>
+        <v>1.28240000049118</v>
       </c>
     </row>
     <row r="20">
       <c r="A20" t="n">
-        <v>0.1631250197533518</v>
+        <v>0.2766999969026074</v>
       </c>
       <c r="B20" t="n">
-        <v>0.0688339932821691</v>
+        <v>0.130499989609234</v>
       </c>
       <c r="C20" t="n">
-        <v>0.064416992245242</v>
+        <v>0.09899999713525176</v>
       </c>
       <c r="D20" t="n">
-        <v>1.042834017425776</v>
+        <v>1.700299995718524</v>
       </c>
       <c r="E20" t="n">
-        <v>0.4298340063542128</v>
+        <v>0.8204999903682619</v>
       </c>
       <c r="F20" t="n">
-        <v>0.1725830079521984</v>
+        <v>0.2727000101003796</v>
       </c>
       <c r="G20" t="n">
-        <v>4.855499981204048</v>
+        <v>7.290600013220683</v>
       </c>
       <c r="H20" t="n">
-        <v>2.022166998358443</v>
+        <v>3.562699988833629</v>
       </c>
       <c r="I20" t="n">
-        <v>0.3718750085681677</v>
+        <v>0.588800001423806</v>
       </c>
       <c r="J20" t="n">
-        <v>20.92933401581831</v>
+        <v>30.59270000085235</v>
       </c>
       <c r="K20" t="n">
-        <v>8.397040975978598</v>
+        <v>13.17190000554547</v>
       </c>
       <c r="L20" t="n">
-        <v>0.8215419948101044</v>
+        <v>1.280900003621355</v>
       </c>
     </row>
     <row r="21">
       <c r="A21" t="n">
-        <v>0.1517909986432642</v>
+        <v>0.2496000088285655</v>
       </c>
       <c r="B21" t="n">
-        <v>0.06991700502112508</v>
+        <v>0.1295999973081052</v>
       </c>
       <c r="C21" t="n">
-        <v>0.0628340058028698</v>
+        <v>0.09810000483412296</v>
       </c>
       <c r="D21" t="n">
-        <v>1.054082997143269</v>
+        <v>1.711599994450808</v>
       </c>
       <c r="E21" t="n">
-        <v>0.416291004512459</v>
+        <v>0.8157999982358888</v>
       </c>
       <c r="F21" t="n">
-        <v>0.167582998983562</v>
+        <v>0.2749999985098839</v>
       </c>
       <c r="G21" t="n">
-        <v>4.730708023998886</v>
+        <v>7.168099997215904</v>
       </c>
       <c r="H21" t="n">
-        <v>1.975042017875239</v>
+        <v>3.47880000481382</v>
       </c>
       <c r="I21" t="n">
-        <v>0.370291993021965</v>
+        <v>0.6104000058257952</v>
       </c>
       <c r="J21" t="n">
-        <v>21.38512500096112</v>
+        <v>30.10839999478776</v>
       </c>
       <c r="K21" t="n">
-        <v>8.460542012471706</v>
+        <v>13.53699999162927</v>
       </c>
       <c r="L21" t="n">
-        <v>0.8414589974563569</v>
+        <v>1.286600003368221</v>
       </c>
     </row>
     <row r="22">
       <c r="A22" t="n">
-        <v>0.1784999913070351</v>
+        <v>0.323900007060729</v>
       </c>
       <c r="B22" t="n">
-        <v>0.0815840030554682</v>
+        <v>0.1331000094069168</v>
       </c>
       <c r="C22" t="n">
-        <v>0.06849999772384763</v>
+        <v>0.1067999983206391</v>
       </c>
       <c r="D22" t="n">
-        <v>0.9727500146254897</v>
+        <v>1.517800003057346</v>
       </c>
       <c r="E22" t="n">
-        <v>0.4013339930679649</v>
+        <v>0.6851000071037561</v>
       </c>
       <c r="F22" t="n">
-        <v>0.1698330161161721</v>
+        <v>0.2766999969026074</v>
       </c>
       <c r="G22" t="n">
-        <v>4.612375021679327</v>
+        <v>6.965400010813028</v>
       </c>
       <c r="H22" t="n">
-        <v>1.806999993277714</v>
+        <v>3.10469999385532</v>
       </c>
       <c r="I22" t="n">
-        <v>0.3977500018663704</v>
+        <v>0.5913999921176583</v>
       </c>
       <c r="J22" t="n">
-        <v>21.39191702008247</v>
+        <v>30.37870000116527</v>
       </c>
       <c r="K22" t="n">
-        <v>8.738792006624863</v>
+        <v>13.78409999597352</v>
       </c>
       <c r="L22" t="n">
-        <v>0.8137919940054417</v>
+        <v>1.292799992370419</v>
       </c>
     </row>
     <row r="23">
       <c r="A23" t="n">
-        <v>0.1823750208131969</v>
+        <v>0.2810000005410984</v>
       </c>
       <c r="B23" t="n">
-        <v>0.07895799353718758</v>
+        <v>0.1687000039964914</v>
       </c>
       <c r="C23" t="n">
-        <v>0.06254197796806693</v>
+        <v>0.1367000077152625</v>
       </c>
       <c r="D23" t="n">
-        <v>1.056332985172048</v>
+        <v>1.913400003104471</v>
       </c>
       <c r="E23" t="n">
-        <v>0.446999998530373</v>
+        <v>0.8591999940108508</v>
       </c>
       <c r="F23" t="n">
-        <v>0.1730420044623315</v>
+        <v>0.275399987003766</v>
       </c>
       <c r="G23" t="n">
-        <v>4.80516700190492</v>
+        <v>7.248199995956384</v>
       </c>
       <c r="H23" t="n">
-        <v>1.995791011722758</v>
+        <v>3.454300007433631</v>
       </c>
       <c r="I23" t="n">
-        <v>0.3773750213440508</v>
+        <v>0.596500001847744</v>
       </c>
       <c r="J23" t="n">
-        <v>21.48083297652192</v>
+        <v>30.718900001375</v>
       </c>
       <c r="K23" t="n">
-        <v>8.681749983225018</v>
+        <v>13.80280000739731</v>
       </c>
       <c r="L23" t="n">
-        <v>0.8700839825905859</v>
+        <v>1.309399987803772</v>
       </c>
     </row>
     <row r="24">
       <c r="A24" t="n">
-        <v>0.1750840165186673</v>
+        <v>0.2783999952953309</v>
       </c>
       <c r="B24" t="n">
-        <v>0.0693329784553498</v>
+        <v>0.1365999924018979</v>
       </c>
       <c r="C24" t="n">
-        <v>0.06187500548548996</v>
+        <v>0.1000999909592792</v>
       </c>
       <c r="D24" t="n">
-        <v>1.077749999240041</v>
+        <v>1.675899999099784</v>
       </c>
       <c r="E24" t="n">
-        <v>0.4282080044504255</v>
+        <v>0.8350999996764585</v>
       </c>
       <c r="F24" t="n">
-        <v>0.1716249971650541</v>
+        <v>0.2733000001171604</v>
       </c>
       <c r="G24" t="n">
-        <v>4.744915990158916</v>
+        <v>7.346300000790507</v>
       </c>
       <c r="H24" t="n">
-        <v>1.982166024390608</v>
+        <v>3.321199998026714</v>
       </c>
       <c r="I24" t="n">
-        <v>0.372500013327226</v>
+        <v>0.6031999946571887</v>
       </c>
       <c r="J24" t="n">
-        <v>21.65716598392464</v>
+        <v>30.78329999698326</v>
       </c>
       <c r="K24" t="n">
-        <v>8.915416983654723</v>
+        <v>14.06069999211468</v>
       </c>
       <c r="L24" t="n">
-        <v>0.8154580136761069</v>
+        <v>1.279200005228631</v>
       </c>
     </row>
     <row r="25">
       <c r="A25" t="n">
-        <v>0.1482920197304338</v>
+        <v>0.2539999986765906</v>
       </c>
       <c r="B25" t="n">
-        <v>0.06587500683963299</v>
+        <v>0.1316999987466261</v>
       </c>
       <c r="C25" t="n">
-        <v>0.06091600516811013</v>
+        <v>0.09760000102687627</v>
       </c>
       <c r="D25" t="n">
-        <v>1.035208988469094</v>
+        <v>1.725599999190308</v>
       </c>
       <c r="E25" t="n">
-        <v>0.4354999982751906</v>
+        <v>0.8414000039920211</v>
       </c>
       <c r="F25" t="n">
-        <v>0.1744999899528921</v>
+        <v>0.2723999932641163</v>
       </c>
       <c r="G25" t="n">
-        <v>4.613124998286366</v>
+        <v>7.192000004579313</v>
       </c>
       <c r="H25" t="n">
-        <v>1.91012499271892</v>
+        <v>3.291300003184006</v>
       </c>
       <c r="I25" t="n">
-        <v>0.373916991520673</v>
+        <v>0.5987999902572483</v>
       </c>
       <c r="J25" t="n">
-        <v>21.50354097830132</v>
+        <v>30.9869000047911</v>
       </c>
       <c r="K25" t="n">
-        <v>8.752583002205938</v>
+        <v>13.89370000106283</v>
       </c>
       <c r="L25" t="n">
-        <v>0.8301660127472132</v>
+        <v>1.297599999816157</v>
       </c>
     </row>
     <row r="26">
       <c r="A26" t="n">
-        <v>0.1607919984962791</v>
+        <v>0.2701000048546121</v>
       </c>
       <c r="B26" t="n">
-        <v>0.06900000153109431</v>
+        <v>0.1403000060236081</v>
       </c>
       <c r="C26" t="n">
-        <v>0.06174997542984784</v>
+        <v>0.0985000078799203</v>
       </c>
       <c r="D26" t="n">
-        <v>1.026041019940749</v>
+        <v>1.640000002225861</v>
       </c>
       <c r="E26" t="n">
-        <v>0.4315830010455102</v>
+        <v>0.8379000064451247</v>
       </c>
       <c r="F26" t="n">
-        <v>0.1717499981168658</v>
+        <v>0.2727999963099137</v>
       </c>
       <c r="G26" t="n">
-        <v>4.712499998277053</v>
+        <v>7.219700011773966</v>
       </c>
       <c r="H26" t="n">
-        <v>1.931375009007752</v>
+        <v>3.300600001239218</v>
       </c>
       <c r="I26" t="n">
-        <v>0.375333009287715</v>
+        <v>0.5960999988019466</v>
       </c>
       <c r="J26" t="n">
-        <v>21.48808402125724</v>
+        <v>30.88320000097156</v>
       </c>
       <c r="K26" t="n">
-        <v>8.67866599583067</v>
+        <v>13.83359999454115</v>
       </c>
       <c r="L26" t="n">
-        <v>0.8248329977504909</v>
+        <v>1.300799995078705</v>
       </c>
     </row>
     <row r="27">
       <c r="A27" t="n">
-        <v>0.1624159922357649</v>
+        <v>0.2742999931797385</v>
       </c>
       <c r="B27" t="n">
-        <v>0.0728330051060766</v>
+        <v>0.146100006531924</v>
       </c>
       <c r="C27" t="n">
-        <v>0.06237500929273665</v>
+        <v>0.09800000407267362</v>
       </c>
       <c r="D27" t="n">
-        <v>1.159250008640811</v>
+        <v>1.766599991242401</v>
       </c>
       <c r="E27" t="n">
-        <v>0.4636670055333525</v>
+        <v>0.8990999922389165</v>
       </c>
       <c r="F27" t="n">
-        <v>0.1885000092443079</v>
+        <v>0.272899997071363</v>
       </c>
       <c r="G27" t="n">
-        <v>4.613791010342538</v>
+        <v>7.105700002284721</v>
       </c>
       <c r="H27" t="n">
-        <v>1.852208020864055</v>
+        <v>3.164499998092651</v>
       </c>
       <c r="I27" t="n">
-        <v>0.3740419924724847</v>
+        <v>0.6020000000717118</v>
       </c>
       <c r="J27" t="n">
-        <v>21.50658398750238</v>
+        <v>32.32879999268334</v>
       </c>
       <c r="K27" t="n">
-        <v>8.948667004005983</v>
+        <v>14.07819999440107</v>
       </c>
       <c r="L27" t="n">
-        <v>0.8486660080961883</v>
+        <v>1.425099995685741</v>
       </c>
     </row>
     <row r="28">
       <c r="A28" t="n">
-        <v>0.1639160036575049</v>
+        <v>0.2775000029942021</v>
       </c>
       <c r="B28" t="n">
-        <v>0.07370900129899383</v>
+        <v>0.1442999928258359</v>
       </c>
       <c r="C28" t="n">
-        <v>0.06179200136102736</v>
+        <v>0.09869999485090375</v>
       </c>
       <c r="D28" t="n">
-        <v>0.9709580044727772</v>
+        <v>1.648100005695596</v>
       </c>
       <c r="E28" t="n">
-        <v>0.4104999825358391</v>
+        <v>0.8206000056816265</v>
       </c>
       <c r="F28" t="n">
-        <v>0.1752910029608756</v>
+        <v>0.2707999956328422</v>
       </c>
       <c r="G28" t="n">
-        <v>4.66854200931266</v>
+        <v>7.218700004159473</v>
       </c>
       <c r="H28" t="n">
-        <v>1.928958983626217</v>
+        <v>3.305699996417388</v>
       </c>
       <c r="I28" t="n">
-        <v>0.372083013644442</v>
+        <v>0.596199999563396</v>
       </c>
       <c r="J28" t="n">
-        <v>21.13545901374891</v>
+        <v>30.12959999614395</v>
       </c>
       <c r="K28" t="n">
-        <v>8.232291002059355</v>
+        <v>13.19529999454971</v>
       </c>
       <c r="L28" t="n">
-        <v>0.8094160002656281</v>
+        <v>1.687899988610297</v>
       </c>
     </row>
     <row r="29">
       <c r="A29" t="n">
-        <v>0.1583749835845083</v>
+        <v>0.2657000004546717</v>
       </c>
       <c r="B29" t="n">
-        <v>0.0752079940866679</v>
+        <v>0.149200001033023</v>
       </c>
       <c r="C29" t="n">
-        <v>0.06187497638165951</v>
+        <v>0.09750000026542693</v>
       </c>
       <c r="D29" t="n">
-        <v>1.057584013324231</v>
+        <v>1.694899998256005</v>
       </c>
       <c r="E29" t="n">
-        <v>0.4239999980200082</v>
+        <v>0.8214000117732212</v>
       </c>
       <c r="F29" t="n">
-        <v>0.1714579993858933</v>
+        <v>0.2693999995244667</v>
       </c>
       <c r="G29" t="n">
-        <v>4.748375009512529</v>
+        <v>7.173900012276135</v>
       </c>
       <c r="H29" t="n">
-        <v>1.959499990334734</v>
+        <v>3.282099991338328</v>
       </c>
       <c r="I29" t="n">
-        <v>0.3726249851752073</v>
+        <v>0.5966000026091933</v>
       </c>
       <c r="J29" t="n">
-        <v>21.51299998513423</v>
+        <v>30.75400000670925</v>
       </c>
       <c r="K29" t="n">
-        <v>8.768833999056369</v>
+        <v>14.18119999289047</v>
       </c>
       <c r="L29" t="n">
-        <v>0.8130840142257512</v>
+        <v>1.286700004129671</v>
       </c>
     </row>
     <row r="30">
       <c r="A30" t="n">
-        <v>0.1610420003999025</v>
+        <v>0.2807999990181997</v>
       </c>
       <c r="B30" t="n">
-        <v>0.06691701128147542</v>
+        <v>0.1309999934164807</v>
       </c>
       <c r="C30" t="n">
-        <v>0.06408299668692052</v>
+        <v>0.09990000398829579</v>
       </c>
       <c r="D30" t="n">
-        <v>1.05141699896194</v>
+        <v>1.702599998679943</v>
       </c>
       <c r="E30" t="n">
-        <v>0.4638329846784472</v>
+        <v>0.8421000093221664</v>
       </c>
       <c r="F30" t="n">
-        <v>0.1738750142976642</v>
+        <v>0.2739000046858564</v>
       </c>
       <c r="G30" t="n">
-        <v>4.591249977238476</v>
+        <v>6.993999995756894</v>
       </c>
       <c r="H30" t="n">
-        <v>1.960749999852851</v>
+        <v>3.349500009790063</v>
       </c>
       <c r="I30" t="n">
-        <v>0.3625419922173023</v>
+        <v>0.5953999934718013</v>
       </c>
       <c r="J30" t="n">
-        <v>21.13858298980631</v>
+        <v>30.39980000176001</v>
       </c>
       <c r="K30" t="n">
-        <v>8.49791697692126</v>
+        <v>13.88900000893045</v>
       </c>
       <c r="L30" t="n">
-        <v>0.832833000458777</v>
+        <v>1.282700002775528</v>
       </c>
     </row>
     <row r="31">
       <c r="A31" t="n">
-        <v>0.1723750028759241</v>
+        <v>0.2862999972421676</v>
       </c>
       <c r="B31" t="n">
-        <v>0.07850001566112041</v>
+        <v>0.1545999984955415</v>
       </c>
       <c r="C31" t="n">
-        <v>0.06337498780339956</v>
+        <v>0.1001000055111945</v>
       </c>
       <c r="D31" t="n">
-        <v>1.039374998072162</v>
+        <v>1.728500006720424</v>
       </c>
       <c r="E31" t="n">
-        <v>0.4448329855222255</v>
+        <v>0.8492999913869426</v>
       </c>
       <c r="F31" t="n">
-        <v>0.1726250047795475</v>
+        <v>0.2752000000327826</v>
       </c>
       <c r="G31" t="n">
-        <v>4.732291010441259</v>
+        <v>7.414899999275804</v>
       </c>
       <c r="H31" t="n">
-        <v>1.963624992640689</v>
+        <v>3.393499995581806</v>
       </c>
       <c r="I31" t="n">
-        <v>0.3593340225052088</v>
+        <v>0.5898999952478334</v>
       </c>
       <c r="J31" t="n">
-        <v>21.36795900878496</v>
+        <v>31.02349999244325</v>
       </c>
       <c r="K31" t="n">
-        <v>8.650708012282848</v>
+        <v>14.25900000322144</v>
       </c>
       <c r="L31" t="n">
-        <v>0.8070000039879233</v>
+        <v>1.270599997951649</v>
       </c>
     </row>
     <row r="32">
       <c r="A32" t="n">
-        <v>0.232708000112325</v>
+        <v>0.3005000035045668</v>
       </c>
       <c r="B32" t="n">
-        <v>0.08541700663045049</v>
+        <v>0.1981999957934022</v>
       </c>
       <c r="C32" t="n">
-        <v>0.07170799653977156</v>
+        <v>0.123999998322688</v>
       </c>
       <c r="D32" t="n">
-        <v>1.049417012836784</v>
+        <v>1.67130000772886</v>
       </c>
       <c r="E32" t="n">
-        <v>0.4457920149434358</v>
+        <v>0.890900002559647</v>
       </c>
       <c r="F32" t="n">
-        <v>0.176959001692012</v>
+        <v>0.272599994787015</v>
       </c>
       <c r="G32" t="n">
-        <v>4.677791992435232</v>
+        <v>6.730000008246861</v>
       </c>
       <c r="H32" t="n">
-        <v>1.866125006927177</v>
+        <v>3.254700000979938</v>
       </c>
       <c r="I32" t="n">
-        <v>0.3816249954979867</v>
+        <v>0.5895999929634854</v>
       </c>
       <c r="J32" t="n">
-        <v>21.37779199983925</v>
+        <v>30.46170000743587</v>
       </c>
       <c r="K32" t="n">
-        <v>8.91441700514406</v>
+        <v>13.69210000848398</v>
       </c>
       <c r="L32" t="n">
-        <v>0.8107080066110939</v>
+        <v>1.287599996430799</v>
       </c>
     </row>
     <row r="33">
       <c r="A33" t="n">
-        <v>0.1807090011425316</v>
+        <v>0.2573999954620376</v>
       </c>
       <c r="B33" t="n">
-        <v>0.07350000669248402</v>
+        <v>0.1307000056840479</v>
       </c>
       <c r="C33" t="n">
-        <v>0.06912500248290598</v>
+        <v>0.1029999984893948</v>
       </c>
       <c r="D33" t="n">
-        <v>1.013541012071073</v>
+        <v>1.735500001814216</v>
       </c>
       <c r="E33" t="n">
-        <v>0.4048329719807953</v>
+        <v>0.7888999971328303</v>
       </c>
       <c r="F33" t="n">
-        <v>0.1754589902702719</v>
+        <v>0.2820000081555918</v>
       </c>
       <c r="G33" t="n">
-        <v>4.691416979767382</v>
+        <v>7.272800008649938</v>
       </c>
       <c r="H33" t="n">
-        <v>1.988709002034739</v>
+        <v>3.456499995081685</v>
       </c>
       <c r="I33" t="n">
-        <v>0.3704160044435412</v>
+        <v>0.5975999956717715</v>
       </c>
       <c r="J33" t="n">
-        <v>21.07179097947665</v>
+        <v>30.48159999889322</v>
       </c>
       <c r="K33" t="n">
-        <v>8.393041993258521</v>
+        <v>13.35280000057537</v>
       </c>
       <c r="L33" t="n">
-        <v>0.8331249991897494</v>
+        <v>1.42460000643041</v>
       </c>
     </row>
     <row r="34">
       <c r="A34" t="n">
-        <v>0.1630000188015401</v>
+        <v>0.2613000106066465</v>
       </c>
       <c r="B34" t="n">
-        <v>0.07220800034701824</v>
+        <v>0.1382999907946214</v>
       </c>
       <c r="C34" t="n">
-        <v>0.06587500683963299</v>
+        <v>0.09719999798107892</v>
       </c>
       <c r="D34" t="n">
-        <v>1.050291990395635</v>
+        <v>1.686300005530939</v>
       </c>
       <c r="E34" t="n">
-        <v>0.4592910117935389</v>
+        <v>0.8212999964598566</v>
       </c>
       <c r="F34" t="n">
-        <v>0.1726250047795475</v>
+        <v>0.2726000093389302</v>
       </c>
       <c r="G34" t="n">
-        <v>4.938083991874009</v>
+        <v>7.52430000284221</v>
       </c>
       <c r="H34" t="n">
-        <v>2.106041996739805</v>
+        <v>3.687899996293709</v>
       </c>
       <c r="I34" t="n">
-        <v>0.3681670059449971</v>
+        <v>0.606099987635389</v>
       </c>
       <c r="J34" t="n">
-        <v>21.30995798506774</v>
+        <v>30.82529999664985</v>
       </c>
       <c r="K34" t="n">
-        <v>8.622458000900224</v>
+        <v>13.77199999114964</v>
       </c>
       <c r="L34" t="n">
-        <v>0.821666995761916</v>
+        <v>1.283699995838106</v>
       </c>
     </row>
     <row r="35">
       <c r="A35" t="n">
-        <v>0.16654102364555</v>
+        <v>0.335300006554462</v>
       </c>
       <c r="B35" t="n">
-        <v>0.07866599480621517</v>
+        <v>0.1477000041631982</v>
       </c>
       <c r="C35" t="n">
-        <v>0.0620420032646507</v>
+        <v>0.1003000070340931</v>
       </c>
       <c r="D35" t="n">
-        <v>0.9883749880827963</v>
+        <v>1.626299999770708</v>
       </c>
       <c r="E35" t="n">
-        <v>0.4037499893456697</v>
+        <v>0.8000999951036647</v>
       </c>
       <c r="F35" t="n">
-        <v>0.1725420006550848</v>
+        <v>0.275699989288114</v>
       </c>
       <c r="G35" t="n">
-        <v>4.844791023060679</v>
+        <v>7.494699995731935</v>
       </c>
       <c r="H35" t="n">
-        <v>2.101709018461406</v>
+        <v>3.698699991218746</v>
       </c>
       <c r="I35" t="n">
-        <v>0.3737499937415123</v>
+        <v>0.5930000043008476</v>
       </c>
       <c r="J35" t="n">
-        <v>20.80391597701237</v>
+        <v>29.71139999863226</v>
       </c>
       <c r="K35" t="n">
-        <v>7.984541007317603</v>
+        <v>13.03380000172183</v>
       </c>
       <c r="L35" t="n">
-        <v>0.8126670145429671</v>
+        <v>1.282000011997297</v>
       </c>
     </row>
     <row r="36">
       <c r="A36" t="n">
-        <v>0.1589589810464531</v>
+        <v>0.2623999898787588</v>
       </c>
       <c r="B36" t="n">
-        <v>0.06979098543524742</v>
+        <v>0.1607000012882054</v>
       </c>
       <c r="C36" t="n">
-        <v>0.06279099034145474</v>
+        <v>0.1214999938383698</v>
       </c>
       <c r="D36" t="n">
-        <v>0.945042003877461</v>
+        <v>1.556100003654137</v>
       </c>
       <c r="E36" t="n">
-        <v>0.3892919921781868</v>
+        <v>0.7498999912058935</v>
       </c>
       <c r="F36" t="n">
-        <v>0.1720000000204891</v>
+        <v>0.2708999963942915</v>
       </c>
       <c r="G36" t="n">
-        <v>4.494457971304655</v>
+        <v>6.941699990420602</v>
       </c>
       <c r="H36" t="n">
-        <v>1.84304200229235</v>
+        <v>3.198499995050952</v>
       </c>
       <c r="I36" t="n">
-        <v>0.3719159867614508</v>
+        <v>0.593100005062297</v>
       </c>
       <c r="J36" t="n">
-        <v>21.36750001227483</v>
+        <v>31.21020000253338</v>
       </c>
       <c r="K36" t="n">
-        <v>8.547332981834188</v>
+        <v>13.60249999561347</v>
       </c>
       <c r="L36" t="n">
-        <v>0.8138749981299043</v>
+        <v>1.27789999532979</v>
       </c>
     </row>
     <row r="37">
       <c r="A37" t="n">
-        <v>0.1449590199626982</v>
+        <v>0.2417999930912629</v>
       </c>
       <c r="B37" t="n">
-        <v>0.06341701373457909</v>
+        <v>0.1200999977299944</v>
       </c>
       <c r="C37" t="n">
-        <v>0.06149997352622449</v>
+        <v>0.09619999036658555</v>
       </c>
       <c r="D37" t="n">
-        <v>1.018665992887691</v>
+        <v>1.668400000198744</v>
       </c>
       <c r="E37" t="n">
-        <v>0.4298329877201468</v>
+        <v>0.8354000019608065</v>
       </c>
       <c r="F37" t="n">
-        <v>0.1734170073177665</v>
+        <v>0.2763999946182594</v>
       </c>
       <c r="G37" t="n">
-        <v>4.388958011986688</v>
+        <v>6.785799996578135</v>
       </c>
       <c r="H37" t="n">
-        <v>1.815833995351568</v>
+        <v>3.102299990132451</v>
       </c>
       <c r="I37" t="n">
-        <v>0.3603750083129853</v>
+        <v>0.6004999886499718</v>
       </c>
       <c r="J37" t="n">
-        <v>21.43475000048056</v>
+        <v>31.31900000153109</v>
       </c>
       <c r="K37" t="n">
-        <v>8.714458002941683</v>
+        <v>13.88749999750871</v>
       </c>
       <c r="L37" t="n">
-        <v>0.8118330151773989</v>
+        <v>1.303199998801574</v>
       </c>
     </row>
     <row r="38">
       <c r="A38" t="n">
-        <v>0.1600420218892395</v>
+        <v>0.2687999949557707</v>
       </c>
       <c r="B38" t="n">
-        <v>0.07650000043213367</v>
+        <v>0.1430999982403591</v>
       </c>
       <c r="C38" t="n">
-        <v>0.06299998494796455</v>
+        <v>0.09780000254977494</v>
       </c>
       <c r="D38" t="n">
-        <v>1.06041700928472</v>
+        <v>1.749300005030818</v>
       </c>
       <c r="E38" t="n">
-        <v>0.4481670039240271</v>
+        <v>0.8722000056877732</v>
       </c>
       <c r="F38" t="n">
-        <v>0.173374981386587</v>
+        <v>0.2730999985942617</v>
       </c>
       <c r="G38" t="n">
-        <v>4.627500020433217</v>
+        <v>7.158599997637793</v>
       </c>
       <c r="H38" t="n">
-        <v>1.864958001533523</v>
+        <v>3.262400001403876</v>
       </c>
       <c r="I38" t="n">
-        <v>0.3727079892996699</v>
+        <v>0.5862999969394878</v>
       </c>
       <c r="J38" t="n">
-        <v>21.25145800528117</v>
+        <v>30.92600000672974</v>
       </c>
       <c r="K38" t="n">
-        <v>8.594332990469411</v>
+        <v>13.65799999621231</v>
       </c>
       <c r="L38" t="n">
-        <v>0.8180830045603216</v>
+        <v>1.295500012929551</v>
       </c>
     </row>
     <row r="39">
       <c r="A39" t="n">
-        <v>0.1584170095156878</v>
+        <v>0.2657000004546717</v>
       </c>
       <c r="B39" t="n">
-        <v>0.06600000779144466</v>
+        <v>0.1210000045830384</v>
       </c>
       <c r="C39" t="n">
-        <v>0.06133300485089421</v>
+        <v>0.1014000008581206</v>
       </c>
       <c r="D39" t="n">
-        <v>1.032291998853907</v>
+        <v>1.7268000083277</v>
       </c>
       <c r="E39" t="n">
-        <v>0.4180839750915766</v>
+        <v>0.8202000026358292</v>
       </c>
       <c r="F39" t="n">
-        <v>0.1717080012895167</v>
+        <v>0.2763000084087253</v>
       </c>
       <c r="G39" t="n">
-        <v>4.654542019125074</v>
+        <v>7.142600006773137</v>
       </c>
       <c r="H39" t="n">
-        <v>1.89895901712589</v>
+        <v>3.281599987531081</v>
       </c>
       <c r="I39" t="n">
-        <v>0.3718750085681677</v>
+        <v>0.6111999973654747</v>
       </c>
       <c r="J39" t="n">
-        <v>20.8842919964809</v>
+        <v>30.49570000439417</v>
       </c>
       <c r="K39" t="n">
-        <v>8.448415988823399</v>
+        <v>13.39870000083465</v>
       </c>
       <c r="L39" t="n">
-        <v>0.8087080204859376</v>
+        <v>1.283600009628572</v>
       </c>
     </row>
     <row r="40">
       <c r="A40" t="n">
-        <v>0.1671669888310134</v>
+        <v>0.2724999940255657</v>
       </c>
       <c r="B40" t="n">
-        <v>0.07554201874881983</v>
+        <v>0.1460000057704747</v>
       </c>
       <c r="C40" t="n">
-        <v>0.06374999065883458</v>
+        <v>0.1000999909592792</v>
       </c>
       <c r="D40" t="n">
-        <v>1.037165988236666</v>
+        <v>1.735099998768419</v>
       </c>
       <c r="E40" t="n">
-        <v>0.4701249999925494</v>
+        <v>0.9188999974867329</v>
       </c>
       <c r="F40" t="n">
-        <v>0.1767079811543226</v>
+        <v>0.2775000029942021</v>
       </c>
       <c r="G40" t="n">
-        <v>4.802082985406741</v>
+        <v>7.397699999273755</v>
       </c>
       <c r="H40" t="n">
-        <v>2.035667013842613</v>
+        <v>3.559300006600097</v>
       </c>
       <c r="I40" t="n">
-        <v>0.3768750175368041</v>
+        <v>0.5945000011706725</v>
       </c>
       <c r="J40" t="n">
-        <v>21.73750000656582</v>
+        <v>31.29269999044482</v>
       </c>
       <c r="K40" t="n">
-        <v>8.921041997382417</v>
+        <v>14.25959999323823</v>
       </c>
       <c r="L40" t="n">
-        <v>0.8204169862437993</v>
+        <v>1.29190000006929</v>
       </c>
     </row>
     <row r="41">
       <c r="A41" t="n">
-        <v>0.1765830093063414</v>
+        <v>0.258700005360879</v>
       </c>
       <c r="B41" t="n">
-        <v>0.06645798566751182</v>
+        <v>0.1232999929925427</v>
       </c>
       <c r="C41" t="n">
-        <v>0.06112499977461994</v>
+        <v>0.09760000102687627</v>
       </c>
       <c r="D41" t="n">
-        <v>1.003750017844141</v>
+        <v>1.675100007560104</v>
       </c>
       <c r="E41" t="n">
-        <v>0.3956659929826856</v>
+        <v>0.7762999885017052</v>
       </c>
       <c r="F41" t="n">
-        <v>0.1726250047795475</v>
+        <v>0.2687999949557707</v>
       </c>
       <c r="G41" t="n">
-        <v>4.672707989811897</v>
+        <v>7.220399988000281</v>
       </c>
       <c r="H41" t="n">
-        <v>1.870209001936018</v>
+        <v>3.223399995476939</v>
       </c>
       <c r="I41" t="n">
-        <v>0.3710420278366655</v>
+        <v>0.5930000043008476</v>
       </c>
       <c r="J41" t="n">
-        <v>21.53841700055636</v>
+        <v>30.98060000047553</v>
       </c>
       <c r="K41" t="n">
-        <v>8.781083015492186</v>
+        <v>14.00070000090636</v>
       </c>
       <c r="L41" t="n">
-        <v>0.8206249913200736</v>
+        <v>1.303299999563023</v>
       </c>
     </row>
     <row r="42">
       <c r="A42" t="n">
-        <v>0.1814999850466847</v>
+        <v>0.2927000023191795</v>
       </c>
       <c r="B42" t="n">
-        <v>0.08862497634254396</v>
+        <v>0.155999994603917</v>
       </c>
       <c r="C42" t="n">
-        <v>0.06841699359938502</v>
+        <v>0.1008999970508739</v>
       </c>
       <c r="D42" t="n">
-        <v>1.091500016627833</v>
+        <v>1.728999995975755</v>
       </c>
       <c r="E42" t="n">
-        <v>0.4463749937713146</v>
+        <v>0.8343999943463132</v>
       </c>
       <c r="F42" t="n">
-        <v>0.2065000007860363</v>
+        <v>0.3460000007180497</v>
       </c>
       <c r="G42" t="n">
-        <v>4.754875000799075</v>
+        <v>7.197799990535714</v>
       </c>
       <c r="H42" t="n">
-        <v>1.880875002825633</v>
+        <v>3.292400011559948</v>
       </c>
       <c r="I42" t="n">
-        <v>0.3685829869937152</v>
+        <v>0.6031000084476545</v>
       </c>
       <c r="J42" t="n">
-        <v>21.35420797276311</v>
+        <v>29.97439999307971</v>
       </c>
       <c r="K42" t="n">
-        <v>8.491083019180223</v>
+        <v>13.71839999046642</v>
       </c>
       <c r="L42" t="n">
-        <v>0.8123330189846456</v>
+        <v>1.334300002781674</v>
       </c>
     </row>
     <row r="43">
       <c r="A43" t="n">
-        <v>0.1557919895276427</v>
+        <v>0.2812999882735312</v>
       </c>
       <c r="B43" t="n">
-        <v>0.07083397940732539</v>
+        <v>0.1456999889342114</v>
       </c>
       <c r="C43" t="n">
-        <v>0.07570799789391458</v>
+        <v>0.1259999989997596</v>
       </c>
       <c r="D43" t="n">
-        <v>1.061165996361524</v>
+        <v>1.746399997500703</v>
       </c>
       <c r="E43" t="n">
-        <v>0.4615420184563845</v>
+        <v>0.8738999895285815</v>
       </c>
       <c r="F43" t="n">
-        <v>0.1727499766275287</v>
+        <v>0.2787999983411282</v>
       </c>
       <c r="G43" t="n">
-        <v>4.626667010597885</v>
+        <v>7.005199993727729</v>
       </c>
       <c r="H43" t="n">
-        <v>1.86791701707989</v>
+        <v>3.161900007398799</v>
       </c>
       <c r="I43" t="n">
-        <v>0.3752500051632524</v>
+        <v>0.5938999966019765</v>
       </c>
       <c r="J43" t="n">
-        <v>21.18424998479895</v>
+        <v>30.03629999875557</v>
       </c>
       <c r="K43" t="n">
-        <v>8.464708982501179</v>
+        <v>13.55479999620002</v>
       </c>
       <c r="L43" t="n">
-        <v>0.8093749929685146</v>
+        <v>1.294999994570389</v>
       </c>
     </row>
     <row r="44">
       <c r="A44" t="n">
-        <v>0.156708003487438</v>
+        <v>0.2730999985942617</v>
       </c>
       <c r="B44" t="n">
-        <v>0.07087501580826938</v>
+        <v>0.1466999965487048</v>
       </c>
       <c r="C44" t="n">
-        <v>0.06045799818821251</v>
+        <v>0.09960000170394778</v>
       </c>
       <c r="D44" t="n">
-        <v>1.013417000649497</v>
+        <v>1.634100000956096</v>
       </c>
       <c r="E44" t="n">
-        <v>0.4350420203991234</v>
+        <v>0.826000003144145</v>
       </c>
       <c r="F44" t="n">
-        <v>0.1727089984342456</v>
+        <v>0.2775000029942021</v>
       </c>
       <c r="G44" t="n">
-        <v>4.710915993200615</v>
+        <v>7.156199993914925</v>
       </c>
       <c r="H44" t="n">
-        <v>1.929541991557926</v>
+        <v>3.28319999971427</v>
       </c>
       <c r="I44" t="n">
-        <v>0.3727910225279629</v>
+        <v>0.6056999991415069</v>
       </c>
       <c r="J44" t="n">
-        <v>21.03779101162218</v>
+        <v>30.50560000701807</v>
       </c>
       <c r="K44" t="n">
-        <v>8.349457988515496</v>
+        <v>13.49320000736043</v>
       </c>
       <c r="L44" t="n">
-        <v>0.8110409835353494</v>
+        <v>1.313999993726611</v>
       </c>
     </row>
     <row r="45">
       <c r="A45" t="n">
-        <v>0.160333001986146</v>
+        <v>0.2842999965650961</v>
       </c>
       <c r="B45" t="n">
-        <v>0.07075001485645771</v>
+        <v>0.1466999965487048</v>
       </c>
       <c r="C45" t="n">
-        <v>0.0682090176269412</v>
+        <v>0.1002000062726438</v>
       </c>
       <c r="D45" t="n">
-        <v>1.035916007822379</v>
+        <v>1.785000000381842</v>
       </c>
       <c r="E45" t="n">
-        <v>0.4422079946380109</v>
+        <v>0.8511000050930306</v>
       </c>
       <c r="F45" t="n">
-        <v>0.1718749990686774</v>
+        <v>0.2711999986786395</v>
       </c>
       <c r="G45" t="n">
-        <v>4.792583000380546</v>
+        <v>7.279099998413585</v>
       </c>
       <c r="H45" t="n">
-        <v>2.08658300107345</v>
+        <v>3.579099997295998</v>
       </c>
       <c r="I45" t="n">
-        <v>0.3824169980362058</v>
+        <v>0.5878999945707619</v>
       </c>
       <c r="J45" t="n">
-        <v>21.64399999310263</v>
+        <v>30.77380001195706</v>
       </c>
       <c r="K45" t="n">
-        <v>8.915457990951836</v>
+        <v>14.24590000533499</v>
       </c>
       <c r="L45" t="n">
-        <v>0.8114170050248504</v>
+        <v>1.292599990847521</v>
       </c>
     </row>
     <row r="46">
       <c r="A46" t="n">
-        <v>0.1506249827798456</v>
+        <v>0.2646999928401783</v>
       </c>
       <c r="B46" t="n">
-        <v>0.06608400144614279</v>
+        <v>0.1292999950237572</v>
       </c>
       <c r="C46" t="n">
-        <v>0.07329197251237929</v>
+        <v>0.09820000559557229</v>
       </c>
       <c r="D46" t="n">
-        <v>1.040917006321251</v>
+        <v>1.723699999274686</v>
       </c>
       <c r="E46" t="n">
-        <v>0.4045829991810024</v>
+        <v>0.77860000601504</v>
       </c>
       <c r="F46" t="n">
-        <v>0.1736669801175594</v>
+        <v>0.2749999985098839</v>
       </c>
       <c r="G46" t="n">
-        <v>4.712458001449704</v>
+        <v>7.186400005593896</v>
       </c>
       <c r="H46" t="n">
-        <v>1.955208019353449</v>
+        <v>3.370199992787093</v>
       </c>
       <c r="I46" t="n">
-        <v>0.3715829807333648</v>
+        <v>0.5967000033706427</v>
       </c>
       <c r="J46" t="n">
-        <v>20.85608302149922</v>
+        <v>30.06279999681283</v>
       </c>
       <c r="K46" t="n">
-        <v>8.127959008561447</v>
+        <v>13.15830000385176</v>
       </c>
       <c r="L46" t="n">
-        <v>0.8145830070134252</v>
+        <v>1.295999987632968</v>
       </c>
     </row>
     <row r="47">
       <c r="A47" t="n">
-        <v>0.1742920139804482</v>
+        <v>0.2968000044347718</v>
       </c>
       <c r="B47" t="n">
-        <v>0.08016699575819075</v>
+        <v>0.1566999999340624</v>
       </c>
       <c r="C47" t="n">
-        <v>0.06316698272712529</v>
+        <v>0.09869999485090375</v>
       </c>
       <c r="D47" t="n">
-        <v>1.062958996044472</v>
+        <v>1.782799998181872</v>
       </c>
       <c r="E47" t="n">
-        <v>0.4493329906836152</v>
+        <v>0.8898999949451536</v>
       </c>
       <c r="F47" t="n">
-        <v>0.1674169907346368</v>
+        <v>0.2690999972401187</v>
       </c>
       <c r="G47" t="n">
-        <v>4.70983301056549</v>
+        <v>7.175699996878393</v>
       </c>
       <c r="H47" t="n">
-        <v>1.931707985932007</v>
+        <v>3.336800000397488</v>
       </c>
       <c r="I47" t="n">
-        <v>0.3709580050781369</v>
+        <v>0.5960999988019466</v>
       </c>
       <c r="J47" t="n">
-        <v>21.77670900709927</v>
+        <v>30.63360000669491</v>
       </c>
       <c r="K47" t="n">
-        <v>8.749625005293638</v>
+        <v>14.0910000045551</v>
       </c>
       <c r="L47" t="n">
-        <v>0.8190840017050505</v>
+        <v>1.283799996599555</v>
       </c>
     </row>
     <row r="48">
       <c r="A48" t="n">
-        <v>0.1862500212155282</v>
+        <v>0.2746999962255359</v>
       </c>
       <c r="B48" t="n">
-        <v>0.06754198693670332</v>
+        <v>0.1313999964622781</v>
       </c>
       <c r="C48" t="n">
-        <v>0.06420802674256265</v>
+        <v>0.1008000108413398</v>
       </c>
       <c r="D48" t="n">
-        <v>1.055500004440546</v>
+        <v>1.761699997587129</v>
       </c>
       <c r="E48" t="n">
-        <v>0.4337499849498272</v>
+        <v>0.8463999984087422</v>
       </c>
       <c r="F48" t="n">
-        <v>0.1670420169830322</v>
+        <v>0.2681999903870746</v>
       </c>
       <c r="G48" t="n">
-        <v>4.503834003116935</v>
+        <v>6.84950000140816</v>
       </c>
       <c r="H48" t="n">
-        <v>1.891291991341859</v>
+        <v>3.222300001652911</v>
       </c>
       <c r="I48" t="n">
-        <v>0.3716250066645443</v>
+        <v>0.5918000097153708</v>
       </c>
       <c r="J48" t="n">
-        <v>21.23924999614246</v>
+        <v>30.71040000941139</v>
       </c>
       <c r="K48" t="n">
-        <v>8.545208023861051</v>
+        <v>13.74280000163708</v>
       </c>
       <c r="L48" t="n">
-        <v>0.8232500113081187</v>
+        <v>1.27710000379011</v>
       </c>
     </row>
     <row r="49">
       <c r="A49" t="n">
-        <v>0.1546249841339886</v>
+        <v>0.2616000128909945</v>
       </c>
       <c r="B49" t="n">
-        <v>0.06608298281207681</v>
+        <v>0.126799990539439</v>
       </c>
       <c r="C49" t="n">
-        <v>0.06354102515615523</v>
+        <v>0.09919999865815043</v>
       </c>
       <c r="D49" t="n">
-        <v>0.9890829969663173</v>
+        <v>1.68610000400804</v>
       </c>
       <c r="E49" t="n">
-        <v>0.4114169860258698</v>
+        <v>0.7976999913807958</v>
       </c>
       <c r="F49" t="n">
-        <v>0.1729580108076334</v>
+        <v>0.2749999985098839</v>
       </c>
       <c r="G49" t="n">
-        <v>4.574791993945837</v>
+        <v>6.989200002863072</v>
       </c>
       <c r="H49" t="n">
-        <v>1.854500005720183</v>
+        <v>3.120599998510443</v>
       </c>
       <c r="I49" t="n">
-        <v>0.3900000010617077</v>
+        <v>0.5941999988863245</v>
       </c>
       <c r="J49" t="n">
-        <v>21.15512499585748</v>
+        <v>30.45969999220688</v>
       </c>
       <c r="K49" t="n">
-        <v>8.435041003394872</v>
+        <v>13.70099998894148</v>
       </c>
       <c r="L49" t="n">
-        <v>0.7903749938122928</v>
+        <v>1.288500003283843</v>
       </c>
     </row>
     <row r="50">
       <c r="A50" t="n">
-        <v>0.1540410157758743</v>
+        <v>0.2741999924182892</v>
       </c>
       <c r="B50" t="n">
-        <v>0.06395799573510885</v>
+        <v>0.1320000010309741</v>
       </c>
       <c r="C50" t="n">
-        <v>0.05970799247734249</v>
+        <v>0.09760000102687627</v>
       </c>
       <c r="D50" t="n">
-        <v>1.087457989342511</v>
+        <v>1.849699998274446</v>
       </c>
       <c r="E50" t="n">
-        <v>0.462584022898227</v>
+        <v>0.8975999953690916</v>
       </c>
       <c r="F50" t="n">
-        <v>0.1706669863779098</v>
+        <v>0.2786999975796789</v>
       </c>
       <c r="G50" t="n">
-        <v>4.65954199898988</v>
+        <v>7.100300004822202</v>
       </c>
       <c r="H50" t="n">
-        <v>1.924209005665034</v>
+        <v>3.376599997864105</v>
       </c>
       <c r="I50" t="n">
-        <v>0.3786660090554506</v>
+        <v>0.5907000013394281</v>
       </c>
       <c r="J50" t="n">
-        <v>21.11937501467764</v>
+        <v>30.46110000286717</v>
       </c>
       <c r="K50" t="n">
-        <v>8.389333001105115</v>
+        <v>13.55410000542179</v>
       </c>
       <c r="L50" t="n">
-        <v>0.8130829955916852</v>
+        <v>1.286700004129671</v>
       </c>
     </row>
     <row r="51">
       <c r="A51" t="n">
-        <v>0.1558329968247563</v>
+        <v>0.2814000035868958</v>
       </c>
       <c r="B51" t="n">
-        <v>0.07054099114611745</v>
+        <v>0.1458999904571101</v>
       </c>
       <c r="C51" t="n">
-        <v>0.06029100040905178</v>
+        <v>0.09840000711847097</v>
       </c>
       <c r="D51" t="n">
-        <v>1.047249999828637</v>
+        <v>1.754500000970438</v>
       </c>
       <c r="E51" t="n">
-        <v>0.416250026319176</v>
+        <v>0.8338999905390665</v>
       </c>
       <c r="F51" t="n">
-        <v>0.1679169945418835</v>
+        <v>0.2733000001171604</v>
       </c>
       <c r="G51" t="n">
-        <v>4.56345800193958</v>
+        <v>6.971599999815226</v>
       </c>
       <c r="H51" t="n">
-        <v>1.867042010417208</v>
+        <v>3.215999997337349</v>
       </c>
       <c r="I51" t="n">
-        <v>0.3729170130100101</v>
+        <v>0.5842999962624162</v>
       </c>
       <c r="J51" t="n">
-        <v>21.46162500139326</v>
+        <v>30.38999999989755</v>
       </c>
       <c r="K51" t="n">
-        <v>8.562375005567446</v>
+        <v>13.77899998624343</v>
       </c>
       <c r="L51" t="n">
-        <v>0.8116670069284737</v>
+        <v>1.282600002014078</v>
       </c>
     </row>
     <row r="52">
       <c r="A52" t="n">
-        <v>0.1995000056922436</v>
+        <v>0.2811000013025478</v>
       </c>
       <c r="B52" t="n">
-        <v>0.0872919918037951</v>
+        <v>0.1906999968923628</v>
       </c>
       <c r="C52" t="n">
-        <v>0.06966700311750174</v>
+        <v>0.1249999913852662</v>
       </c>
       <c r="D52" t="n">
-        <v>1.009041006909683</v>
+        <v>1.725900001474656</v>
       </c>
       <c r="E52" t="n">
-        <v>0.3900410083588213</v>
+        <v>0.7477000035578385</v>
       </c>
       <c r="F52" t="n">
-        <v>0.1718329731374979</v>
+        <v>0.3020000003743917</v>
       </c>
       <c r="G52" t="n">
-        <v>4.814332991372794</v>
+        <v>7.25679998868145</v>
       </c>
       <c r="H52" t="n">
-        <v>2.001874992856756</v>
+        <v>3.341400006320328</v>
       </c>
       <c r="I52" t="n">
-        <v>0.4371670074760914</v>
+        <v>0.6209999992279336</v>
       </c>
       <c r="J52" t="n">
-        <v>21.93587497458793</v>
+        <v>31.24509999179281</v>
       </c>
       <c r="K52" t="n">
-        <v>8.865375013556331</v>
+        <v>14.28990000567865</v>
       </c>
       <c r="L52" t="n">
-        <v>0.8284159994218498</v>
+        <v>1.284199999645352</v>
       </c>
     </row>
     <row r="53">
       <c r="A53" t="n">
-        <v>0.1493750023655593</v>
+        <v>0.3042000025743619</v>
       </c>
       <c r="B53" t="n">
-        <v>0.06308400770649314</v>
+        <v>0.1218999968841672</v>
       </c>
       <c r="C53" t="n">
-        <v>0.06541699985973537</v>
+        <v>0.1218000106746331</v>
       </c>
       <c r="D53" t="n">
-        <v>0.9865419997368008</v>
+        <v>1.619699993170798</v>
       </c>
       <c r="E53" t="n">
-        <v>0.3885409969370812</v>
+        <v>0.7367999933194369</v>
       </c>
       <c r="F53" t="n">
-        <v>0.1724999747239053</v>
+        <v>0.2720000047702342</v>
       </c>
       <c r="G53" t="n">
-        <v>4.932207986712456</v>
+        <v>7.221199994091876</v>
       </c>
       <c r="H53" t="n">
-        <v>2.110332978190854</v>
+        <v>3.528000001097098</v>
       </c>
       <c r="I53" t="n">
-        <v>0.3717080107890069</v>
+        <v>0.5926000012550503</v>
       </c>
       <c r="J53" t="n">
-        <v>21.50908400653861</v>
+        <v>30.92639999522362</v>
       </c>
       <c r="K53" t="n">
-        <v>8.707625005627051</v>
+        <v>14.15089999500196</v>
       </c>
       <c r="L53" t="n">
-        <v>0.8134170202538371</v>
+        <v>1.277800009120256</v>
       </c>
     </row>
     <row r="54">
       <c r="A54" t="n">
-        <v>0.1631249906495214</v>
+        <v>0.2516999957151711</v>
       </c>
       <c r="B54" t="n">
-        <v>0.06466600461862981</v>
+        <v>0.1205000007757917</v>
       </c>
       <c r="C54" t="n">
-        <v>0.06245801341719925</v>
+        <v>0.09719999798107892</v>
       </c>
       <c r="D54" t="n">
-        <v>1.051166997058317</v>
+        <v>1.725200010696426</v>
       </c>
       <c r="E54" t="n">
-        <v>0.4702919977717102</v>
+        <v>0.82230000407435</v>
       </c>
       <c r="F54" t="n">
-        <v>0.1768340007402003</v>
+        <v>0.2708999963942915</v>
       </c>
       <c r="G54" t="n">
-        <v>4.607209004461765</v>
+        <v>7.104200005414896</v>
       </c>
       <c r="H54" t="n">
-        <v>1.893958018627018</v>
+        <v>3.247400003601797</v>
       </c>
       <c r="I54" t="n">
-        <v>0.3671250015031546</v>
+        <v>0.59710000641644</v>
       </c>
       <c r="J54" t="n">
-        <v>21.33412499097176</v>
+        <v>31.09470001072623</v>
       </c>
       <c r="K54" t="n">
-        <v>8.596083003794774</v>
+        <v>13.81560000299942</v>
       </c>
       <c r="L54" t="n">
-        <v>0.8192909881472588</v>
+        <v>1.284900004975498</v>
       </c>
     </row>
     <row r="55">
       <c r="A55" t="n">
-        <v>0.1576670038048178</v>
+        <v>0.2596999984234571</v>
       </c>
       <c r="B55" t="n">
-        <v>0.07583401747979224</v>
+        <v>0.1302000018768013</v>
       </c>
       <c r="C55" t="n">
-        <v>0.06200000643730164</v>
+        <v>0.09580000187270343</v>
       </c>
       <c r="D55" t="n">
-        <v>1.021041010972112</v>
+        <v>1.744900000630878</v>
       </c>
       <c r="E55" t="n">
-        <v>0.4327500064391643</v>
+        <v>0.8296000014524907</v>
       </c>
       <c r="F55" t="n">
-        <v>0.1710829965304583</v>
+        <v>0.2738999901339412</v>
       </c>
       <c r="G55" t="n">
-        <v>4.6645829861518</v>
+        <v>7.29029999638442</v>
       </c>
       <c r="H55" t="n">
-        <v>1.949457975570112</v>
+        <v>3.401900001335889</v>
       </c>
       <c r="I55" t="n">
-        <v>0.3763750137295574</v>
+        <v>0.5985999887343496</v>
       </c>
       <c r="J55" t="n">
-        <v>21.29987502121367</v>
+        <v>30.26680000766646</v>
       </c>
       <c r="K55" t="n">
-        <v>8.545165997929871</v>
+        <v>13.26520000293385</v>
       </c>
       <c r="L55" t="n">
-        <v>0.8735840092413127</v>
+        <v>1.29709999600891</v>
       </c>
     </row>
     <row r="56">
       <c r="A56" t="n">
-        <v>0.1600830000825226</v>
+        <v>0.2655999996932223</v>
       </c>
       <c r="B56" t="n">
-        <v>0.06437499541789293</v>
+        <v>0.1225000014528632</v>
       </c>
       <c r="C56" t="n">
-        <v>0.0620420032646507</v>
+        <v>0.09980000322684646</v>
       </c>
       <c r="D56" t="n">
-        <v>1.031667023198679</v>
+        <v>1.741300002322532</v>
       </c>
       <c r="E56" t="n">
-        <v>0.4368330119177699</v>
+        <v>0.8374000026378781</v>
       </c>
       <c r="F56" t="n">
-        <v>0.1739590079523623</v>
+        <v>0.2730999985942617</v>
       </c>
       <c r="G56" t="n">
-        <v>4.438833013409749</v>
+        <v>6.724799997755326</v>
       </c>
       <c r="H56" t="n">
-        <v>1.81445901398547</v>
+        <v>3.154600010020658</v>
       </c>
       <c r="I56" t="n">
-        <v>0.3710419987328351</v>
+        <v>0.5951999919489026</v>
       </c>
       <c r="J56" t="n">
-        <v>21.87250001588836</v>
+        <v>31.35400000610389</v>
       </c>
       <c r="K56" t="n">
-        <v>9.114791988395154</v>
+        <v>14.46839999698568</v>
       </c>
       <c r="L56" t="n">
-        <v>0.8142919978126884</v>
+        <v>1.281799995922484</v>
       </c>
     </row>
     <row r="57">
       <c r="A57" t="n">
-        <v>0.1434170117136091</v>
+        <v>0.2338000049348921</v>
       </c>
       <c r="B57" t="n">
-        <v>0.0587090034969151</v>
+        <v>0.1113000034820288</v>
       </c>
       <c r="C57" t="n">
-        <v>0.06145797669887543</v>
+        <v>0.09889999637380242</v>
       </c>
       <c r="D57" t="n">
-        <v>1.039041002513841</v>
+        <v>1.735600002575666</v>
       </c>
       <c r="E57" t="n">
-        <v>0.4237079992890358</v>
+        <v>0.8288999961223453</v>
       </c>
       <c r="F57" t="n">
-        <v>0.1872909779194742</v>
+        <v>0.2787999983411282</v>
       </c>
       <c r="G57" t="n">
-        <v>4.450833017472178</v>
+        <v>6.748600004357286</v>
       </c>
       <c r="H57" t="n">
-        <v>1.768707996234298</v>
+        <v>3.068999998504296</v>
       </c>
       <c r="I57" t="n">
-        <v>0.3716250066645443</v>
+        <v>0.592500000493601</v>
       </c>
       <c r="J57" t="n">
-        <v>21.47491701180115</v>
+        <v>30.29680000327062</v>
       </c>
       <c r="K57" t="n">
-        <v>8.75812501180917</v>
+        <v>13.91690000309609</v>
       </c>
       <c r="L57" t="n">
-        <v>0.821624998934567</v>
+        <v>1.323500007856637</v>
       </c>
     </row>
     <row r="58">
       <c r="A58" t="n">
-        <v>0.1554999907966703</v>
+        <v>0.2573000092525035</v>
       </c>
       <c r="B58" t="n">
-        <v>0.05849997978657484</v>
+        <v>0.1100000081351027</v>
       </c>
       <c r="C58" t="n">
-        <v>0.06145800580270588</v>
+        <v>0.1041999930748716</v>
       </c>
       <c r="D58" t="n">
-        <v>1.021792006213218</v>
+        <v>1.69639999512583</v>
       </c>
       <c r="E58" t="n">
-        <v>0.4501249932218343</v>
+        <v>0.8570000063627958</v>
       </c>
       <c r="F58" t="n">
-        <v>0.1682919973973185</v>
+        <v>0.2718000032473356</v>
       </c>
       <c r="G58" t="n">
-        <v>4.785500001162291</v>
+        <v>7.197099999757484</v>
       </c>
       <c r="H58" t="n">
-        <v>2.052416995866224</v>
+        <v>3.55429999763146</v>
       </c>
       <c r="I58" t="n">
-        <v>0.3720840031746775</v>
+        <v>0.5999999993946403</v>
       </c>
       <c r="J58" t="n">
-        <v>21.38070898945443</v>
+        <v>31.27719998883549</v>
       </c>
       <c r="K58" t="n">
-        <v>8.67866599583067</v>
+        <v>13.81079999555368</v>
       </c>
       <c r="L58" t="n">
-        <v>0.8092499920167029</v>
+        <v>2.114399991114624</v>
       </c>
     </row>
     <row r="59">
       <c r="A59" t="n">
-        <v>0.1740420120768249</v>
+        <v>0.2578999992692843</v>
       </c>
       <c r="B59" t="n">
-        <v>0.06987500819377601</v>
+        <v>0.1317999995080754</v>
       </c>
       <c r="C59" t="n">
-        <v>0.06208298145793378</v>
+        <v>0.09830000635702163</v>
       </c>
       <c r="D59" t="n">
-        <v>0.9335840004496276</v>
+        <v>1.557299998239614</v>
       </c>
       <c r="E59" t="n">
-        <v>0.3755000070668757</v>
+        <v>0.7100999937392771</v>
       </c>
       <c r="F59" t="n">
-        <v>0.170832994626835</v>
+        <v>0.2747000107774511</v>
       </c>
       <c r="G59" t="n">
-        <v>4.536583001026884</v>
+        <v>6.838800007244572</v>
       </c>
       <c r="H59" t="n">
-        <v>1.839667005697265</v>
+        <v>3.172900003846735</v>
       </c>
       <c r="I59" t="n">
-        <v>0.3718340012710541</v>
+        <v>0.5854999908478931</v>
       </c>
       <c r="J59" t="n">
-        <v>21.48645897977985</v>
+        <v>30.91509999649134</v>
       </c>
       <c r="K59" t="n">
-        <v>8.515749999787658</v>
+        <v>13.49159999517724</v>
       </c>
       <c r="L59" t="n">
-        <v>0.814792001619935</v>
+        <v>1.270799999474548</v>
       </c>
     </row>
     <row r="60">
       <c r="A60" t="n">
-        <v>0.1422910136170685</v>
+        <v>0.2394000039203092</v>
       </c>
       <c r="B60" t="n">
-        <v>0.06858399137854576</v>
+        <v>0.1292000088142231</v>
       </c>
       <c r="C60" t="n">
-        <v>0.06058299914002419</v>
+        <v>0.09700001101009548</v>
       </c>
       <c r="D60" t="n">
-        <v>1.003834011498839</v>
+        <v>1.695899991318583</v>
       </c>
       <c r="E60" t="n">
-        <v>0.4187500162515789</v>
+        <v>0.7992000028025359</v>
       </c>
       <c r="F60" t="n">
-        <v>0.1754999975673854</v>
+        <v>0.2743000077316537</v>
       </c>
       <c r="G60" t="n">
-        <v>4.656584002077579</v>
+        <v>7.253399991896003</v>
       </c>
       <c r="H60" t="n">
-        <v>1.966916985111311</v>
+        <v>3.38019999617245</v>
       </c>
       <c r="I60" t="n">
-        <v>0.3587919927667826</v>
+        <v>0.5895000067539513</v>
       </c>
       <c r="J60" t="n">
-        <v>22.09041701280512</v>
+        <v>30.95609998854343</v>
       </c>
       <c r="K60" t="n">
-        <v>8.714458002941683</v>
+        <v>13.7107000045944</v>
       </c>
       <c r="L60" t="n">
-        <v>0.8210839878302068</v>
+        <v>1.306499994825572</v>
       </c>
     </row>
     <row r="61">
       <c r="A61" t="n">
-        <v>0.1620420080143958</v>
+        <v>0.2773000014713034</v>
       </c>
       <c r="B61" t="n">
-        <v>0.07870799163356423</v>
+        <v>0.1482000079704449</v>
       </c>
       <c r="C61" t="n">
-        <v>0.06216598558239639</v>
+        <v>0.09980000322684646</v>
       </c>
       <c r="D61" t="n">
-        <v>1.029959006700665</v>
+        <v>1.703599991742522</v>
       </c>
       <c r="E61" t="n">
-        <v>0.4194159992039204</v>
+        <v>0.7994999905349687</v>
       </c>
       <c r="F61" t="n">
-        <v>0.1682500005699694</v>
+        <v>0.2730999985942617</v>
       </c>
       <c r="G61" t="n">
-        <v>4.737375013064593</v>
+        <v>7.296299998415634</v>
       </c>
       <c r="H61" t="n">
-        <v>1.94566699792631</v>
+        <v>3.389999998034909</v>
       </c>
       <c r="I61" t="n">
-        <v>0.3895830013789237</v>
+        <v>0.5920999974478036</v>
       </c>
       <c r="J61" t="n">
-        <v>21.58924998366274</v>
+        <v>30.97079999861307</v>
       </c>
       <c r="K61" t="n">
-        <v>12.98008399317041</v>
+        <v>13.52600000973325</v>
       </c>
       <c r="L61" t="n">
-        <v>0.836499995784834</v>
+        <v>1.290300002438016</v>
       </c>
     </row>
     <row r="62">
       <c r="A62" t="n">
-        <v>0.180582981556654</v>
+        <v>0.2672999980859458</v>
       </c>
       <c r="B62" t="n">
-        <v>0.07804099004715681</v>
+        <v>0.1340000017080456</v>
       </c>
       <c r="C62" t="n">
-        <v>0.06350001785904169</v>
+        <v>0.09689999569673091</v>
       </c>
       <c r="D62" t="n">
-        <v>1.156541984528303</v>
+        <v>1.728600007481873</v>
       </c>
       <c r="E62" t="n">
-        <v>0.4818329762201756</v>
+        <v>0.9395999950356781</v>
       </c>
       <c r="F62" t="n">
-        <v>0.2051669871434569</v>
+        <v>0.2829000004567206</v>
       </c>
       <c r="G62" t="n">
-        <v>4.807999997865409</v>
+        <v>7.164100010413677</v>
       </c>
       <c r="H62" t="n">
-        <v>1.932665996719152</v>
+        <v>3.288899999461137</v>
       </c>
       <c r="I62" t="n">
-        <v>0.499875022796914</v>
+        <v>0.7545999978901818</v>
       </c>
       <c r="J62" t="n">
-        <v>23.17245799349621</v>
+        <v>30.35149999777786</v>
       </c>
       <c r="K62" t="n">
-        <v>9.258250007405877</v>
+        <v>13.28419998753816</v>
       </c>
       <c r="L62" t="n">
-        <v>0.8586250187363476</v>
+        <v>1.279000003705733</v>
       </c>
     </row>
     <row r="63">
       <c r="A63" t="n">
-        <v>0.1568750012665987</v>
+        <v>0.2976999967359006</v>
       </c>
       <c r="B63" t="n">
-        <v>0.07783298497088253</v>
+        <v>0.1339000009465963</v>
       </c>
       <c r="C63" t="n">
-        <v>0.06683298852294683</v>
+        <v>0.1224000006914139</v>
       </c>
       <c r="D63" t="n">
-        <v>1.011834014207125</v>
+        <v>1.738699997076765</v>
       </c>
       <c r="E63" t="n">
-        <v>0.433250010246411</v>
+        <v>0.8309999975608662</v>
       </c>
       <c r="F63" t="n">
-        <v>0.177334004547447</v>
+        <v>0.2817000058712438</v>
       </c>
       <c r="G63" t="n">
-        <v>4.606167000019923</v>
+        <v>6.955899996683002</v>
       </c>
       <c r="H63" t="n">
-        <v>1.854624977568164</v>
+        <v>3.204699998605065</v>
       </c>
       <c r="I63" t="n">
-        <v>0.3766249865293503</v>
+        <v>0.593700009630993</v>
       </c>
       <c r="J63" t="n">
-        <v>23.50516701699235</v>
+        <v>30.42149999237154</v>
       </c>
       <c r="K63" t="n">
-        <v>8.478415984427556</v>
+        <v>13.29230000555981</v>
       </c>
       <c r="L63" t="n">
-        <v>0.8115840028040111</v>
+        <v>1.318800001172349</v>
       </c>
     </row>
     <row r="64">
       <c r="A64" t="n">
-        <v>0.1717090199235827</v>
+        <v>0.284200010355562</v>
       </c>
       <c r="B64" t="n">
-        <v>0.07445801747962832</v>
+        <v>0.139000010676682</v>
       </c>
       <c r="C64" t="n">
-        <v>0.06295897765085101</v>
+        <v>0.09779998799785972</v>
       </c>
       <c r="D64" t="n">
-        <v>1.132540986873209</v>
+        <v>1.810099987778813</v>
       </c>
       <c r="E64" t="n">
-        <v>0.4190409963484854</v>
+        <v>0.8630999946035445</v>
       </c>
       <c r="F64" t="n">
-        <v>0.1711669901851565</v>
+        <v>0.271999990218319</v>
       </c>
       <c r="G64" t="n">
-        <v>4.856416984694079</v>
+        <v>7.521499996073544</v>
       </c>
       <c r="H64" t="n">
-        <v>2.107667009113356</v>
+        <v>3.746300004422665</v>
       </c>
       <c r="I64" t="n">
-        <v>0.3710830060299486</v>
+        <v>0.6037999992258847</v>
       </c>
       <c r="J64" t="n">
-        <v>21.58983299159445</v>
+        <v>30.65339999739081</v>
       </c>
       <c r="K64" t="n">
-        <v>8.843249990604818</v>
+        <v>13.98329999938142</v>
       </c>
       <c r="L64" t="n">
-        <v>0.8277920132968575</v>
+        <v>1.282500001252629</v>
       </c>
     </row>
     <row r="65">
       <c r="A65" t="n">
-        <v>0.1716249971650541</v>
+        <v>0.2736999886110425</v>
       </c>
       <c r="B65" t="n">
-        <v>0.09629200212657452</v>
+        <v>0.1291000080527738</v>
       </c>
       <c r="C65" t="n">
-        <v>0.06333400961011648</v>
+        <v>0.09529999806545675</v>
       </c>
       <c r="D65" t="n">
-        <v>0.9323330014012754</v>
+        <v>1.622799987671897</v>
       </c>
       <c r="E65" t="n">
-        <v>0.4030000127386302</v>
+        <v>0.7703000010224059</v>
       </c>
       <c r="F65" t="n">
-        <v>0.1707499905023724</v>
+        <v>0.2708999963942915</v>
       </c>
       <c r="G65" t="n">
-        <v>4.68608399387449</v>
+        <v>7.306799991056323</v>
       </c>
       <c r="H65" t="n">
-        <v>1.942083006724715</v>
+        <v>3.451299999142066</v>
       </c>
       <c r="I65" t="n">
-        <v>0.368125009117648</v>
+        <v>0.5993999948259443</v>
       </c>
       <c r="J65" t="n">
-        <v>22.46362497680821</v>
+        <v>30.62970000610221</v>
       </c>
       <c r="K65" t="n">
-        <v>8.708333014510572</v>
+        <v>13.80020000215154</v>
       </c>
       <c r="L65" t="n">
-        <v>0.8464579877909273</v>
+        <v>1.274600013857707</v>
       </c>
     </row>
     <row r="66">
       <c r="A66" t="n">
-        <v>0.1790410024113953</v>
+        <v>0.2781000075628981</v>
       </c>
       <c r="B66" t="n">
-        <v>0.07675000233575702</v>
+        <v>0.1435000012861565</v>
       </c>
       <c r="C66" t="n">
-        <v>0.07074998575262725</v>
+        <v>0.09639999188948423</v>
       </c>
       <c r="D66" t="n">
-        <v>0.9377920068800449</v>
+        <v>1.603600001544692</v>
       </c>
       <c r="E66" t="n">
-        <v>0.3915839770343155</v>
+        <v>0.7773999968776479</v>
       </c>
       <c r="F66" t="n">
-        <v>0.1720000000204891</v>
+        <v>0.2729999978328124</v>
       </c>
       <c r="G66" t="n">
-        <v>4.626875015674159</v>
+        <v>7.072899999911897</v>
       </c>
       <c r="H66" t="n">
-        <v>1.884083001641557</v>
+        <v>3.308100000140257</v>
       </c>
       <c r="I66" t="n">
-        <v>0.3846249892376363</v>
+        <v>0.585700006922707</v>
       </c>
       <c r="J66" t="n">
-        <v>22.46112501597963</v>
+        <v>31.80949999659788</v>
       </c>
       <c r="K66" t="n">
-        <v>9.382207994349301</v>
+        <v>14.18709999416023</v>
       </c>
       <c r="L66" t="n">
-        <v>0.8465000137221068</v>
+        <v>1.280399999814108</v>
       </c>
     </row>
     <row r="67">
       <c r="A67" t="n">
-        <v>0.1421250053681433</v>
+        <v>0.2491000050213188</v>
       </c>
       <c r="B67" t="n">
-        <v>0.05962501745671034</v>
+        <v>0.1175000070361421</v>
       </c>
       <c r="C67" t="n">
-        <v>0.06033299723640084</v>
+        <v>0.09580000187270343</v>
       </c>
       <c r="D67" t="n">
-        <v>1.010750012937933</v>
+        <v>1.813300012145191</v>
       </c>
       <c r="E67" t="n">
-        <v>0.4182920092716813</v>
+        <v>0.8612999954493716</v>
       </c>
       <c r="F67" t="n">
-        <v>0.1674169907346368</v>
+        <v>0.2742000069702044</v>
       </c>
       <c r="G67" t="n">
-        <v>4.613333003362641</v>
+        <v>7.054899993818253</v>
       </c>
       <c r="H67" t="n">
-        <v>1.886375015601516</v>
+        <v>3.29359999159351</v>
       </c>
       <c r="I67" t="n">
-        <v>0.3969579993281513</v>
+        <v>0.5951999919489026</v>
       </c>
       <c r="J67" t="n">
-        <v>22.43554199230857</v>
+        <v>30.83609999157488</v>
       </c>
       <c r="K67" t="n">
-        <v>9.224250010447577</v>
+        <v>14.07800000743009</v>
       </c>
       <c r="L67" t="n">
-        <v>0.8562500006519258</v>
+        <v>1.268899999558926</v>
       </c>
     </row>
     <row r="68">
       <c r="A68" t="n">
-        <v>0.1560839882586151</v>
+        <v>0.2741000062087551</v>
       </c>
       <c r="B68" t="n">
-        <v>0.06308400770649314</v>
+        <v>0.1241999998455867</v>
       </c>
       <c r="C68" t="n">
-        <v>0.06024999311193824</v>
+        <v>0.09700001101009548</v>
       </c>
       <c r="D68" t="n">
-        <v>1.05275001260452</v>
+        <v>1.856300004874356</v>
       </c>
       <c r="E68" t="n">
-        <v>0.4592920013237745</v>
+        <v>0.9312999900430441</v>
       </c>
       <c r="F68" t="n">
-        <v>0.1709579955786467</v>
+        <v>0.2725000085774809</v>
       </c>
       <c r="G68" t="n">
-        <v>4.690208006650209</v>
+        <v>7.242799998493865</v>
       </c>
       <c r="H68" t="n">
-        <v>1.93520900211297</v>
+        <v>3.348600002937019</v>
       </c>
       <c r="I68" t="n">
-        <v>0.3745830035768449</v>
+        <v>0.592500000493601</v>
       </c>
       <c r="J68" t="n">
-        <v>22.26566601893865</v>
+        <v>31.24389999720734</v>
       </c>
       <c r="K68" t="n">
-        <v>9.02654099627398</v>
+        <v>14.06549999956042</v>
       </c>
       <c r="L68" t="n">
-        <v>0.8423340041190386</v>
+        <v>1.286600003368221</v>
       </c>
     </row>
     <row r="69">
       <c r="A69" t="n">
-        <v>0.1573750050738454</v>
+        <v>0.335900011123158</v>
       </c>
       <c r="B69" t="n">
-        <v>0.06579200271517038</v>
+        <v>0.1306000049225986</v>
       </c>
       <c r="C69" t="n">
-        <v>0.05995799438096583</v>
+        <v>0.09750000026542693</v>
       </c>
       <c r="D69" t="n">
-        <v>0.9821249986998737</v>
+        <v>1.693700003670529</v>
       </c>
       <c r="E69" t="n">
-        <v>0.3882500168401748</v>
+        <v>0.7919999916339293</v>
       </c>
       <c r="F69" t="n">
-        <v>0.1751249947119504</v>
+        <v>0.2767999976640567</v>
       </c>
       <c r="G69" t="n">
-        <v>4.483541997615248</v>
+        <v>6.838200002675876</v>
       </c>
       <c r="H69" t="n">
-        <v>1.809125009458512</v>
+        <v>3.143399997497909</v>
       </c>
       <c r="I69" t="n">
-        <v>0.3825409803539515</v>
+        <v>0.5918999959249049</v>
       </c>
       <c r="J69" t="n">
-        <v>21.6795829765033</v>
+        <v>30.41680000023916</v>
       </c>
       <c r="K69" t="n">
-        <v>8.807332982541993</v>
+        <v>13.1890999909956</v>
       </c>
       <c r="L69" t="n">
-        <v>0.828874995931983</v>
+        <v>1.273599991691299</v>
       </c>
     </row>
     <row r="70">
       <c r="A70" t="n">
-        <v>0.166874990100041</v>
+        <v>0.2954999945359305</v>
       </c>
       <c r="B70" t="n">
-        <v>0.0772500061430037</v>
+        <v>0.152900000102818</v>
       </c>
       <c r="C70" t="n">
-        <v>0.06104199565015733</v>
+        <v>0.09830000635702163</v>
       </c>
       <c r="D70" t="n">
-        <v>1.008417020784691</v>
+        <v>1.714800004265271</v>
       </c>
       <c r="E70" t="n">
-        <v>0.4056249745190144</v>
+        <v>0.8091000054264441</v>
       </c>
       <c r="F70" t="n">
-        <v>0.1757080026436597</v>
+        <v>0.2709000109462067</v>
       </c>
       <c r="G70" t="n">
-        <v>4.425833991263062</v>
+        <v>6.667699999525212</v>
       </c>
       <c r="H70" t="n">
-        <v>1.825832994654775</v>
+        <v>3.165999994962476</v>
       </c>
       <c r="I70" t="n">
-        <v>0.3740829997695982</v>
+        <v>0.5875999922864139</v>
       </c>
       <c r="J70" t="n">
-        <v>22.20149998902343</v>
+        <v>30.65099999366794</v>
       </c>
       <c r="K70" t="n">
-        <v>9.028833999764174</v>
+        <v>13.77160000265576</v>
       </c>
       <c r="L70" t="n">
-        <v>0.8540419803466648</v>
+        <v>1.258400006918237</v>
       </c>
     </row>
     <row r="71">
       <c r="A71" t="n">
-        <v>0.1515419862698764</v>
+        <v>0.2592999953776598</v>
       </c>
       <c r="B71" t="n">
-        <v>0.06391701754182577</v>
+        <v>0.1270000066142529</v>
       </c>
       <c r="C71" t="n">
-        <v>0.06133300485089421</v>
+        <v>0.1013000000966713</v>
       </c>
       <c r="D71" t="n">
-        <v>1.014416018733755</v>
+        <v>1.729299998260103</v>
       </c>
       <c r="E71" t="n">
-        <v>0.3981250047218055</v>
+        <v>0.7993000035639852</v>
       </c>
       <c r="F71" t="n">
-        <v>0.1719169958960265</v>
+        <v>0.2778999914880842</v>
       </c>
       <c r="G71" t="n">
-        <v>4.845541989197955</v>
+        <v>7.634499997948296</v>
       </c>
       <c r="H71" t="n">
-        <v>2.026875008596107</v>
+        <v>3.507999994326383</v>
       </c>
       <c r="I71" t="n">
-        <v>0.3696669882629067</v>
+        <v>0.5893000052310526</v>
       </c>
       <c r="J71" t="n">
-        <v>21.88158300123177</v>
+        <v>30.27269999438431</v>
       </c>
       <c r="K71" t="n">
-        <v>8.815666020382196</v>
+        <v>13.36939999600872</v>
       </c>
       <c r="L71" t="n">
-        <v>0.8151249785441905</v>
+        <v>1.280999989830889</v>
       </c>
     </row>
     <row r="72">
       <c r="A72" t="n">
-        <v>0.1883750082924962</v>
+        <v>0.2840000088326633</v>
       </c>
       <c r="B72" t="n">
-        <v>0.08558400440961123</v>
+        <v>0.181199997314252</v>
       </c>
       <c r="C72" t="n">
-        <v>0.06770799518562853</v>
+        <v>0.1037000038195401</v>
       </c>
       <c r="D72" t="n">
-        <v>0.9752080077305436</v>
+        <v>1.697100000455976</v>
       </c>
       <c r="E72" t="n">
-        <v>0.5116669926792383</v>
+        <v>1.045099998009391</v>
       </c>
       <c r="F72" t="n">
-        <v>0.1732910168357193</v>
+        <v>0.2706999948713928</v>
       </c>
       <c r="G72" t="n">
-        <v>4.635166988009587</v>
+        <v>6.955600008950569</v>
       </c>
       <c r="H72" t="n">
-        <v>1.957291009603068</v>
+        <v>3.365299999131821</v>
       </c>
       <c r="I72" t="n">
-        <v>0.402874982682988</v>
+        <v>0.5918000097153708</v>
       </c>
       <c r="J72" t="n">
-        <v>21.99654100695625</v>
+        <v>30.41180000582244</v>
       </c>
       <c r="K72" t="n">
-        <v>8.773915993515402</v>
+        <v>13.37090000743046</v>
       </c>
       <c r="L72" t="n">
-        <v>0.8259590249508619</v>
+        <v>1.287699997192249</v>
       </c>
     </row>
     <row r="73">
       <c r="A73" t="n">
-        <v>0.1460420025978237</v>
+        <v>0.3013000095961615</v>
       </c>
       <c r="B73" t="n">
-        <v>0.0644999963697046</v>
+        <v>0.1201999984914437</v>
       </c>
       <c r="C73" t="n">
-        <v>0.06200000643730164</v>
+        <v>0.1000000047497451</v>
       </c>
       <c r="D73" t="n">
-        <v>1.048915990395471</v>
+        <v>1.780699996743351</v>
       </c>
       <c r="E73" t="n">
-        <v>0.5099580157548189</v>
+        <v>1.193499992950819</v>
       </c>
       <c r="F73" t="n">
-        <v>0.175583001691848</v>
+        <v>0.2739000046858564</v>
       </c>
       <c r="G73" t="n">
-        <v>4.640958009986207</v>
+        <v>7.06789999094326</v>
       </c>
       <c r="H73" t="n">
-        <v>1.86845802818425</v>
+        <v>3.27879999531433</v>
       </c>
       <c r="I73" t="n">
-        <v>0.3670410078484565</v>
+        <v>0.5883000121684745</v>
       </c>
       <c r="J73" t="n">
-        <v>21.66416600812227</v>
+        <v>30.61729999899399</v>
       </c>
       <c r="K73" t="n">
-        <v>8.473166002659127</v>
+        <v>13.2828000059817</v>
       </c>
       <c r="L73" t="n">
-        <v>0.8607080089859664</v>
+        <v>1.29130001005251</v>
       </c>
     </row>
     <row r="74">
       <c r="A74" t="n">
-        <v>0.1681249996181577</v>
+        <v>0.2498999965609983</v>
       </c>
       <c r="B74" t="n">
-        <v>0.06520899478346109</v>
+        <v>0.1293999957852066</v>
       </c>
       <c r="C74" t="n">
-        <v>0.06133399438112974</v>
+        <v>0.102100006188266</v>
       </c>
       <c r="D74" t="n">
-        <v>0.946540996665135</v>
+        <v>1.626400000532158</v>
       </c>
       <c r="E74" t="n">
-        <v>0.3922909963876009</v>
+        <v>0.7768999930704013</v>
       </c>
       <c r="F74" t="n">
-        <v>0.1781669852789491</v>
+        <v>0.283399989712052</v>
       </c>
       <c r="G74" t="n">
-        <v>4.761709016747773</v>
+        <v>7.206900001619942</v>
       </c>
       <c r="H74" t="n">
-        <v>1.971541001694277</v>
+        <v>3.433200006838888</v>
       </c>
       <c r="I74" t="n">
-        <v>0.3736669896170497</v>
+        <v>0.5953999934718013</v>
       </c>
       <c r="J74" t="n">
-        <v>20.51574998768046</v>
+        <v>28.93240000412334</v>
       </c>
       <c r="K74" t="n">
-        <v>9.036999981617555</v>
+        <v>13.65259999874979</v>
       </c>
       <c r="L74" t="n">
-        <v>0.8150830108206719</v>
+        <v>1.27940000675153</v>
       </c>
     </row>
     <row r="75">
       <c r="A75" t="n">
-        <v>0.1699590065982193</v>
+        <v>0.2797999914037064</v>
       </c>
       <c r="B75" t="n">
-        <v>0.08299999171867967</v>
+        <v>0.1532999885967001</v>
       </c>
       <c r="C75" t="n">
-        <v>0.0644999963697046</v>
+        <v>0.09590000263415277</v>
       </c>
       <c r="D75" t="n">
-        <v>1.019957999233156</v>
+        <v>1.710099997580983</v>
       </c>
       <c r="E75" t="n">
-        <v>0.4363750049378723</v>
+        <v>0.8267999946838245</v>
       </c>
       <c r="F75" t="n">
-        <v>0.1738339778967202</v>
+        <v>0.2763999946182594</v>
       </c>
       <c r="G75" t="n">
-        <v>4.703582992078736</v>
+        <v>7.239800004754215</v>
       </c>
       <c r="H75" t="n">
-        <v>2.007000002777204</v>
+        <v>3.486800007522106</v>
       </c>
       <c r="I75" t="n">
-        <v>0.3730000171344727</v>
+        <v>0.589400005992502</v>
       </c>
       <c r="J75" t="n">
-        <v>21.28004198311828</v>
+        <v>30.66870001202915</v>
       </c>
       <c r="K75" t="n">
-        <v>8.610582997789606</v>
+        <v>13.43639999686275</v>
       </c>
       <c r="L75" t="n">
-        <v>0.8290830010082573</v>
+        <v>1.305400001001544</v>
       </c>
     </row>
     <row r="76">
       <c r="A76" t="n">
-        <v>0.1717080012895167</v>
+        <v>0.2863999980036169</v>
       </c>
       <c r="B76" t="n">
-        <v>0.07754200487397611</v>
+        <v>0.14519999967888</v>
       </c>
       <c r="C76" t="n">
-        <v>0.06225000834092498</v>
+        <v>0.09629999112803489</v>
       </c>
       <c r="D76" t="n">
-        <v>0.964250008109957</v>
+        <v>1.641499999095686</v>
       </c>
       <c r="E76" t="n">
-        <v>0.4164580022916198</v>
+        <v>0.8068000024650246</v>
       </c>
       <c r="F76" t="n">
-        <v>0.1957080094143748</v>
+        <v>0.2693999995244667</v>
       </c>
       <c r="G76" t="n">
-        <v>4.817916022147983</v>
+        <v>7.171599994762801</v>
       </c>
       <c r="H76" t="n">
-        <v>2.086332999169827</v>
+        <v>3.516600001603365</v>
       </c>
       <c r="I76" t="n">
-        <v>0.3722920082509518</v>
+        <v>0.5984000017633662</v>
       </c>
       <c r="J76" t="n">
-        <v>21.78941699094139</v>
+        <v>30.16419999767095</v>
       </c>
       <c r="K76" t="n">
-        <v>9.289291978348047</v>
+        <v>14.08189999347087</v>
       </c>
       <c r="L76" t="n">
-        <v>0.8706669905222952</v>
+        <v>1.29269999160897</v>
       </c>
     </row>
     <row r="77">
       <c r="A77" t="n">
-        <v>0.1703750167507678</v>
+        <v>0.2899000101024285</v>
       </c>
       <c r="B77" t="n">
-        <v>0.07479099440388381</v>
+        <v>0.1417999883415177</v>
       </c>
       <c r="C77" t="n">
-        <v>0.0629170099273324</v>
+        <v>0.09729999874252826</v>
       </c>
       <c r="D77" t="n">
-        <v>1.014959008898586</v>
+        <v>1.732899996568449</v>
       </c>
       <c r="E77" t="n">
-        <v>0.4069169808644801</v>
+        <v>0.8239000017056242</v>
       </c>
       <c r="F77" t="n">
-        <v>0.1774999836925417</v>
+        <v>0.2749999985098839</v>
       </c>
       <c r="G77" t="n">
-        <v>4.624375025741756</v>
+        <v>7.026699997368269</v>
       </c>
       <c r="H77" t="n">
-        <v>1.842500001657754</v>
+        <v>3.204199994797818</v>
       </c>
       <c r="I77" t="n">
-        <v>0.3688329888973385</v>
+        <v>0.5821999948238954</v>
       </c>
       <c r="J77" t="n">
-        <v>22.88054200471379</v>
+        <v>30.80149999004789</v>
       </c>
       <c r="K77" t="n">
-        <v>9.792500000912696</v>
+        <v>13.46990000456572</v>
       </c>
       <c r="L77" t="n">
-        <v>0.8280840120278299</v>
+        <v>1.291799999307841</v>
       </c>
     </row>
     <row r="78">
       <c r="A78" t="n">
-        <v>0.1633330248296261</v>
+        <v>0.2715000009629875</v>
       </c>
       <c r="B78" t="n">
-        <v>0.07008298416621983</v>
+        <v>0.1326000055996701</v>
       </c>
       <c r="C78" t="n">
-        <v>0.06166601087898016</v>
+        <v>0.09650000720284879</v>
       </c>
       <c r="D78" t="n">
-        <v>0.9628749976400286</v>
+        <v>1.645399999688379</v>
       </c>
       <c r="E78" t="n">
-        <v>0.4193749919068068</v>
+        <v>0.7757999992463738</v>
       </c>
       <c r="F78" t="n">
-        <v>0.1718330022413284</v>
+        <v>0.2735000016400591</v>
       </c>
       <c r="G78" t="n">
-        <v>4.459750023670495</v>
+        <v>6.873799997265451</v>
       </c>
       <c r="H78" t="n">
-        <v>1.651875005336478</v>
+        <v>2.837199994246475</v>
       </c>
       <c r="I78" t="n">
-        <v>0.3733749908860773</v>
+        <v>0.5907000013394281</v>
       </c>
       <c r="J78" t="n">
-        <v>22.98179198987782</v>
+        <v>30.28679999988526</v>
       </c>
       <c r="K78" t="n">
-        <v>8.929000003263354</v>
+        <v>13.32520000869408</v>
       </c>
       <c r="L78" t="n">
-        <v>0.8500420080963522</v>
+        <v>1.286500002606772</v>
       </c>
     </row>
     <row r="79">
       <c r="A79" t="n">
-        <v>0.1573330082464963</v>
+        <v>0.2717999886954203</v>
       </c>
       <c r="B79" t="n">
-        <v>0.07000000914558768</v>
+        <v>0.1363999908789992</v>
       </c>
       <c r="C79" t="n">
-        <v>0.06237500929273665</v>
+        <v>0.09660000796429813</v>
       </c>
       <c r="D79" t="n">
-        <v>0.9393329964950681</v>
+        <v>1.59499999426771</v>
       </c>
       <c r="E79" t="n">
-        <v>0.3877909912262112</v>
+        <v>0.7359000010183081</v>
       </c>
       <c r="F79" t="n">
-        <v>0.1734170073177665</v>
+        <v>0.2740000054473057</v>
       </c>
       <c r="G79" t="n">
-        <v>4.642499989131466</v>
+        <v>7.016600007773377</v>
       </c>
       <c r="H79" t="n">
-        <v>1.831083005527034</v>
+        <v>3.198800011887215</v>
       </c>
       <c r="I79" t="n">
-        <v>0.3880409931298345</v>
+        <v>0.592500000493601</v>
       </c>
       <c r="J79" t="n">
-        <v>22.61699998052791</v>
+        <v>30.9519000002183</v>
       </c>
       <c r="K79" t="n">
-        <v>9.363667020807043</v>
+        <v>14.2863000073703</v>
       </c>
       <c r="L79" t="n">
-        <v>0.8365410030819476</v>
+        <v>1.28229999972973</v>
       </c>
     </row>
     <row r="80">
       <c r="A80" t="n">
-        <v>0.1713749952614307</v>
+        <v>0.2831000019796193</v>
       </c>
       <c r="B80" t="n">
-        <v>0.07120799273252487</v>
+        <v>0.1392000121995807</v>
       </c>
       <c r="C80" t="n">
-        <v>0.06312501500360668</v>
+        <v>0.09560000034980476</v>
       </c>
       <c r="D80" t="n">
-        <v>0.9929999941959977</v>
+        <v>1.710199998342432</v>
       </c>
       <c r="E80" t="n">
-        <v>0.4064159875269979</v>
+        <v>0.7986999989952892</v>
       </c>
       <c r="F80" t="n">
-        <v>0.1705419854260981</v>
+        <v>0.2726999955484644</v>
       </c>
       <c r="G80" t="n">
-        <v>4.756790993269533</v>
+        <v>7.335000002058223</v>
       </c>
       <c r="H80" t="n">
-        <v>2.008749986998737</v>
+        <v>3.587200000765733</v>
       </c>
       <c r="I80" t="n">
-        <v>0.3730839816853404</v>
+        <v>0.5897999944863841</v>
       </c>
       <c r="J80" t="n">
-        <v>21.79433399578556</v>
+        <v>30.46890000405256</v>
       </c>
       <c r="K80" t="n">
-        <v>8.490915992297232</v>
+        <v>13.35870000184514</v>
       </c>
       <c r="L80" t="n">
-        <v>0.8298330067191273</v>
+        <v>1.290899992454797</v>
       </c>
     </row>
     <row r="81">
       <c r="A81" t="n">
-        <v>0.1600419927854091</v>
+        <v>0.2682000049389899</v>
       </c>
       <c r="B81" t="n">
-        <v>0.07145799463614821</v>
+        <v>0.1358000008622184</v>
       </c>
       <c r="C81" t="n">
-        <v>0.06250001024454832</v>
+        <v>0.09460000728722662</v>
       </c>
       <c r="D81" t="n">
-        <v>1.061041984939948</v>
+        <v>1.797400007490069</v>
       </c>
       <c r="E81" t="n">
-        <v>0.4515420005191118</v>
+        <v>0.8712000126251951</v>
       </c>
       <c r="F81" t="n">
-        <v>0.1760419982019812</v>
+        <v>0.2734000008786097</v>
       </c>
       <c r="G81" t="n">
-        <v>4.564375005429611</v>
+        <v>6.886599992867559</v>
       </c>
       <c r="H81" t="n">
-        <v>1.84304200229235</v>
+        <v>3.215299992007203</v>
       </c>
       <c r="I81" t="n">
-        <v>0.3695000195875764</v>
+        <v>0.5867999861948192</v>
       </c>
       <c r="J81" t="n">
-        <v>21.29420801065862</v>
+        <v>30.16700000443961</v>
       </c>
       <c r="K81" t="n">
-        <v>8.540917013306171</v>
+        <v>13.18090000131633</v>
       </c>
       <c r="L81" t="n">
-        <v>0.8220839954447001</v>
+        <v>1.315000001341105</v>
       </c>
     </row>
     <row r="82">
       <c r="A82" t="n">
-        <v>0.1787499932106584</v>
+        <v>0.2759000053629279</v>
       </c>
       <c r="B82" t="n">
-        <v>0.08100000559352338</v>
+        <v>0.1479000056860968</v>
       </c>
       <c r="C82" t="n">
-        <v>0.07041599019430578</v>
+        <v>0.09940000018104911</v>
       </c>
       <c r="D82" t="n">
-        <v>1.241167017724365</v>
+        <v>1.659699992160313</v>
       </c>
       <c r="E82" t="n">
-        <v>1.19554199045524</v>
+        <v>0.7671000057598576</v>
       </c>
       <c r="F82" t="n">
-        <v>0.4736670234706253</v>
+        <v>0.2685000072233379</v>
       </c>
       <c r="G82" t="n">
-        <v>4.909082985250279</v>
+        <v>7.641499993042089</v>
       </c>
       <c r="H82" t="n">
-        <v>1.958582986844704</v>
+        <v>3.421800007345155</v>
       </c>
       <c r="I82" t="n">
-        <v>0.3841249854303896</v>
+        <v>0.5931999912718311</v>
       </c>
       <c r="J82" t="n">
-        <v>21.80583300651051</v>
+        <v>31.12090000649914</v>
       </c>
       <c r="K82" t="n">
-        <v>9.001541999168694</v>
+        <v>13.78999999724329</v>
       </c>
       <c r="L82" t="n">
-        <v>0.8140830032061785</v>
+        <v>1.289199994062074</v>
       </c>
     </row>
     <row r="83">
       <c r="A83" t="n">
-        <v>0.1547079882584512</v>
+        <v>0.2631999959703535</v>
       </c>
       <c r="B83" t="n">
-        <v>0.06812499486841261</v>
+        <v>0.1371999969705939</v>
       </c>
       <c r="C83" t="n">
-        <v>0.07045897655189037</v>
+        <v>0.0973999995039776</v>
       </c>
       <c r="D83" t="n">
-        <v>1.064292009687051</v>
+        <v>1.612799998838454</v>
       </c>
       <c r="E83" t="n">
-        <v>0.4247920005582273</v>
+        <v>0.7676999957766384</v>
       </c>
       <c r="F83" t="n">
-        <v>0.1852919813245535</v>
+        <v>0.2746999962255359</v>
       </c>
       <c r="G83" t="n">
-        <v>4.496875015320256</v>
+        <v>6.870099998195656</v>
       </c>
       <c r="H83" t="n">
-        <v>1.926375000039116</v>
+        <v>3.269799999543466</v>
       </c>
       <c r="I83" t="n">
-        <v>0.3809579939115793</v>
+        <v>0.5953999934718013</v>
       </c>
       <c r="J83" t="n">
-        <v>21.18870901176706</v>
+        <v>30.87919999961741</v>
       </c>
       <c r="K83" t="n">
-        <v>8.450624998658895</v>
+        <v>13.36660000379197</v>
       </c>
       <c r="L83" t="n">
-        <v>0.8319169864989817</v>
+        <v>1.295199996093288</v>
       </c>
     </row>
     <row r="84">
       <c r="A84" t="n">
-        <v>0.1620420080143958</v>
+        <v>0.2442999975755811</v>
       </c>
       <c r="B84" t="n">
-        <v>0.06654098979197443</v>
+        <v>0.1222999999299645</v>
       </c>
       <c r="C84" t="n">
-        <v>0.06275001214817166</v>
+        <v>0.09929999941959977</v>
       </c>
       <c r="D84" t="n">
-        <v>1.043999975081533</v>
+        <v>1.661599992075935</v>
       </c>
       <c r="E84" t="n">
-        <v>0.4312079981900752</v>
+        <v>0.79340000229422</v>
       </c>
       <c r="F84" t="n">
-        <v>0.1834589929785579</v>
+        <v>0.2719000040087849</v>
       </c>
       <c r="G84" t="n">
-        <v>4.727458988782018</v>
+        <v>7.300299999769777</v>
       </c>
       <c r="H84" t="n">
-        <v>1.923999981954694</v>
+        <v>3.298299998277798</v>
       </c>
       <c r="I84" t="n">
-        <v>0.3717920044437051</v>
+        <v>0.5964000010862947</v>
       </c>
       <c r="J84" t="n">
-        <v>21.62808299181052</v>
+        <v>31.27900000254158</v>
       </c>
       <c r="K84" t="n">
-        <v>10.27004199568182</v>
+        <v>14.21249999839347</v>
       </c>
       <c r="L84" t="n">
-        <v>0.9536249854136258</v>
+        <v>1.292500004637986</v>
       </c>
     </row>
     <row r="85">
       <c r="A85" t="n">
-        <v>0.1834160066209733</v>
+        <v>0.2894000062951818</v>
       </c>
       <c r="B85" t="n">
-        <v>0.08308299584314227</v>
+        <v>0.1480999926570803</v>
       </c>
       <c r="C85" t="n">
-        <v>0.06425002356991172</v>
+        <v>0.09989998943638057</v>
       </c>
       <c r="D85" t="n">
-        <v>1.013208995573223</v>
+        <v>1.699600004940294</v>
       </c>
       <c r="E85" t="n">
-        <v>0.4384579951874912</v>
+        <v>0.8516999951098114</v>
       </c>
       <c r="F85" t="n">
-        <v>0.1733340031933039</v>
+        <v>0.269199998001568</v>
       </c>
       <c r="G85" t="n">
-        <v>4.764250013977289</v>
+        <v>7.2851000004448</v>
       </c>
       <c r="H85" t="n">
-        <v>2.016583981458098</v>
+        <v>3.414899998460896</v>
       </c>
       <c r="I85" t="n">
-        <v>0.3821660066023469</v>
+        <v>0.5957000103080645</v>
       </c>
       <c r="J85" t="n">
-        <v>21.57829201314598</v>
+        <v>31.18410000752192</v>
       </c>
       <c r="K85" t="n">
-        <v>8.937042002798989</v>
+        <v>14.17080000101123</v>
       </c>
       <c r="L85" t="n">
-        <v>0.9687080164439976</v>
+        <v>1.29640000523068</v>
       </c>
     </row>
     <row r="86">
       <c r="A86" t="n">
-        <v>0.1726250047795475</v>
+        <v>0.247300005867146</v>
       </c>
       <c r="B86" t="n">
-        <v>0.09120898903347552</v>
+        <v>0.1273000088986009</v>
       </c>
       <c r="C86" t="n">
-        <v>0.06716698408126831</v>
+        <v>0.1085000112652779</v>
       </c>
       <c r="D86" t="n">
-        <v>1.03312500868924</v>
+        <v>1.733900004182942</v>
       </c>
       <c r="E86" t="n">
-        <v>0.4500829963944852</v>
+        <v>0.8753000001888722</v>
       </c>
       <c r="F86" t="n">
-        <v>0.1743339817039669</v>
+        <v>0.2742999931797385</v>
       </c>
       <c r="G86" t="n">
-        <v>4.775832989253104</v>
+        <v>7.370999999693595</v>
       </c>
       <c r="H86" t="n">
-        <v>2.032541990047321</v>
+        <v>3.539700002875179</v>
       </c>
       <c r="I86" t="n">
-        <v>0.3709160082507879</v>
+        <v>0.5841000092914328</v>
       </c>
       <c r="J86" t="n">
-        <v>21.06425000238232</v>
+        <v>30.1949999993667</v>
       </c>
       <c r="K86" t="n">
-        <v>8.277499990072101</v>
+        <v>13.02660000510514</v>
       </c>
       <c r="L86" t="n">
-        <v>0.8212079992517829</v>
+        <v>1.279999996768311</v>
       </c>
     </row>
     <row r="87">
       <c r="A87" t="n">
-        <v>0.1607909798622131</v>
+        <v>0.2739000046858564</v>
       </c>
       <c r="B87" t="n">
-        <v>0.06854202365502715</v>
+        <v>0.1339000009465963</v>
       </c>
       <c r="C87" t="n">
-        <v>0.08524997974745929</v>
+        <v>0.1005999947665259</v>
       </c>
       <c r="D87" t="n">
-        <v>0.9839170088525862</v>
+        <v>1.643299998249859</v>
       </c>
       <c r="E87" t="n">
-        <v>0.3830000059679151</v>
+        <v>0.7451999990735203</v>
       </c>
       <c r="F87" t="n">
-        <v>0.1728750066831708</v>
+        <v>0.269800002570264</v>
       </c>
       <c r="G87" t="n">
-        <v>4.710416018497199</v>
+        <v>7.231600000523031</v>
       </c>
       <c r="H87" t="n">
-        <v>2.016291982727125</v>
+        <v>3.446300004725344</v>
       </c>
       <c r="I87" t="n">
-        <v>0.3791670023929328</v>
+        <v>0.6003000016789883</v>
       </c>
       <c r="J87" t="n">
-        <v>21.41695798491128</v>
+        <v>30.80979999504052</v>
       </c>
       <c r="K87" t="n">
-        <v>8.431750000454485</v>
+        <v>13.36019999871496</v>
       </c>
       <c r="L87" t="n">
-        <v>0.8756669994909316</v>
+        <v>1.283300007344224</v>
       </c>
     </row>
     <row r="88">
       <c r="A88" t="n">
-        <v>0.1521249942015857</v>
+        <v>0.2587999915704131</v>
       </c>
       <c r="B88" t="n">
-        <v>0.06750001921318471</v>
+        <v>0.1327000063611194</v>
       </c>
       <c r="C88" t="n">
-        <v>0.06041699089109898</v>
+        <v>0.09839999256655574</v>
       </c>
       <c r="D88" t="n">
-        <v>0.9733750193845481</v>
+        <v>1.644399992073886</v>
       </c>
       <c r="E88" t="n">
-        <v>0.4114999901503325</v>
+        <v>0.8040999964578077</v>
       </c>
       <c r="F88" t="n">
-        <v>0.1702090085018426</v>
+        <v>0.2641000028233975</v>
       </c>
       <c r="G88" t="n">
-        <v>4.695207986515015</v>
+        <v>7.2851000004448</v>
       </c>
       <c r="H88" t="n">
-        <v>1.959790999535471</v>
+        <v>3.430100012337789</v>
       </c>
       <c r="I88" t="n">
-        <v>0.373874994693324</v>
+        <v>0.5959999980404973</v>
       </c>
       <c r="J88" t="n">
-        <v>21.47391598555259</v>
+        <v>31.19799999694806</v>
       </c>
       <c r="K88" t="n">
-        <v>8.548332989448681</v>
+        <v>13.74979999673087</v>
       </c>
       <c r="L88" t="n">
-        <v>0.8199999865610152</v>
+        <v>1.315599991357885</v>
       </c>
     </row>
     <row r="89">
       <c r="A89" t="n">
-        <v>0.1520829973742366</v>
+        <v>0.259600012213923</v>
       </c>
       <c r="B89" t="n">
-        <v>0.0671250163577497</v>
+        <v>0.1317999995080754</v>
       </c>
       <c r="C89" t="n">
-        <v>0.06012499216012657</v>
+        <v>0.09709999721962959</v>
       </c>
       <c r="D89" t="n">
-        <v>1.058624999132007</v>
+        <v>1.748999988194555</v>
       </c>
       <c r="E89" t="n">
-        <v>0.4432090208865702</v>
+        <v>0.8531000057701021</v>
       </c>
       <c r="F89" t="n">
-        <v>0.1722500019241124</v>
+        <v>0.2665000065462664</v>
       </c>
       <c r="G89" t="n">
-        <v>4.682792001403868</v>
+        <v>7.562099999631755</v>
       </c>
       <c r="H89" t="n">
-        <v>1.956332998815924</v>
+        <v>3.366699995240197</v>
       </c>
       <c r="I89" t="n">
-        <v>0.3765000146813691</v>
+        <v>0.592199998209253</v>
       </c>
       <c r="J89" t="n">
-        <v>21.91404197947122</v>
+        <v>31.71949999523349</v>
       </c>
       <c r="K89" t="n">
-        <v>9.050624998053536</v>
+        <v>14.47530000586994</v>
       </c>
       <c r="L89" t="n">
-        <v>0.8181250013876706</v>
+        <v>1.270299995667301</v>
       </c>
     </row>
     <row r="90">
       <c r="A90" t="n">
-        <v>0.1570419990457594</v>
+        <v>0.2723999932641163</v>
       </c>
       <c r="B90" t="n">
-        <v>0.06483399192802608</v>
+        <v>0.1272999943466857</v>
       </c>
       <c r="C90" t="n">
-        <v>0.06000002031214535</v>
+        <v>0.09710001177154481</v>
       </c>
       <c r="D90" t="n">
-        <v>0.9668749989941716</v>
+        <v>1.596700007212348</v>
       </c>
       <c r="E90" t="n">
-        <v>0.4103329847566783</v>
+        <v>0.7877000025473535</v>
       </c>
       <c r="F90" t="n">
-        <v>0.1716670230962336</v>
+        <v>0.2668000088306144</v>
       </c>
       <c r="G90" t="n">
-        <v>4.647666006349027</v>
+        <v>7.105299999238923</v>
       </c>
       <c r="H90" t="n">
-        <v>1.972166995983571</v>
+        <v>3.438900006585754</v>
       </c>
       <c r="I90" t="n">
-        <v>0.3703749971464276</v>
+        <v>0.5875999922864139</v>
       </c>
       <c r="J90" t="n">
-        <v>21.81116701103747</v>
+        <v>31.40269999857992</v>
       </c>
       <c r="K90" t="n">
-        <v>8.848208002746105</v>
+        <v>14.20130000042263</v>
       </c>
       <c r="L90" t="n">
-        <v>0.8150840003509074</v>
+        <v>1.265800005057827</v>
       </c>
     </row>
     <row r="91">
       <c r="A91" t="n">
-        <v>0.1568330044392496</v>
+        <v>0.2690000110305846</v>
       </c>
       <c r="B91" t="n">
-        <v>0.07249999907799065</v>
+        <v>0.1423999929102138</v>
       </c>
       <c r="C91" t="n">
-        <v>0.05891700857318938</v>
+        <v>0.0990999978967011</v>
       </c>
       <c r="D91" t="n">
-        <v>0.9729579905979335</v>
+        <v>1.614399996469729</v>
       </c>
       <c r="E91" t="n">
-        <v>0.4135000053793192</v>
+        <v>0.7979000074556097</v>
       </c>
       <c r="F91" t="n">
-        <v>0.1727909839246422</v>
+        <v>0.2668999950401485</v>
       </c>
       <c r="G91" t="n">
-        <v>4.631999996490777</v>
+        <v>7.043200006592087</v>
       </c>
       <c r="H91" t="n">
-        <v>1.906750025227666</v>
+        <v>3.240000005462207</v>
       </c>
       <c r="I91" t="n">
-        <v>0.3690840094350278</v>
+        <v>0.5854999908478931</v>
       </c>
       <c r="J91" t="n">
-        <v>21.82820800226182</v>
+        <v>31.89159999601543</v>
       </c>
       <c r="K91" t="n">
-        <v>8.903875015676022</v>
+        <v>14.05810000142083</v>
       </c>
       <c r="L91" t="n">
-        <v>0.8141659782268107</v>
+        <v>1.267699990421534</v>
       </c>
     </row>
     <row r="92">
       <c r="A92" t="n">
-        <v>0.1960000081453472</v>
+        <v>0.2831999881891534</v>
       </c>
       <c r="B92" t="n">
-        <v>0.06770898471586406</v>
+        <v>0.127399995108135</v>
       </c>
       <c r="C92" t="n">
-        <v>0.06512500112876296</v>
+        <v>0.09609998960513622</v>
       </c>
       <c r="D92" t="n">
-        <v>1.120375003665686</v>
+        <v>1.668500000960194</v>
       </c>
       <c r="E92" t="n">
-        <v>0.4770419909618795</v>
+        <v>0.8353000011993572</v>
       </c>
       <c r="F92" t="n">
-        <v>0.1842080091591924</v>
+        <v>0.2724999940255657</v>
       </c>
       <c r="G92" t="n">
-        <v>4.741292010294273</v>
+        <v>7.346300000790507</v>
       </c>
       <c r="H92" t="n">
-        <v>2.144875004887581</v>
+        <v>3.48320000921376</v>
       </c>
       <c r="I92" t="n">
-        <v>0.3690830199047923</v>
+        <v>0.5969000048935413</v>
       </c>
       <c r="J92" t="n">
-        <v>21.36212500045076</v>
+        <v>30.10530000028666</v>
       </c>
       <c r="K92" t="n">
-        <v>8.489250001730397</v>
+        <v>13.07769998675212</v>
       </c>
       <c r="L92" t="n">
-        <v>0.8137499971780926</v>
+        <v>1.26530000125058</v>
       </c>
     </row>
     <row r="93">
       <c r="A93" t="n">
-        <v>0.1424590009264648</v>
+        <v>0.2500999980838969</v>
       </c>
       <c r="B93" t="n">
-        <v>0.07375000859610736</v>
+        <v>0.1172999909613281</v>
       </c>
       <c r="C93" t="n">
-        <v>0.05929201142862439</v>
+        <v>0.0973999995039776</v>
       </c>
       <c r="D93" t="n">
-        <v>0.9471669909544289</v>
+        <v>1.610899998922832</v>
       </c>
       <c r="E93" t="n">
-        <v>0.4149170126765966</v>
+        <v>0.9481000015512109</v>
       </c>
       <c r="F93" t="n">
-        <v>0.1731670054141432</v>
+        <v>0.273199999355711</v>
       </c>
       <c r="G93" t="n">
-        <v>4.698416974861175</v>
+        <v>7.135799998650327</v>
       </c>
       <c r="H93" t="n">
-        <v>1.901541982078925</v>
+        <v>3.243899991502985</v>
       </c>
       <c r="I93" t="n">
-        <v>0.3770829935092479</v>
+        <v>0.5875000060768798</v>
       </c>
       <c r="J93" t="n">
-        <v>21.18537502246909</v>
+        <v>30.83119999791961</v>
       </c>
       <c r="K93" t="n">
-        <v>8.576541993534192</v>
+        <v>13.29129999794532</v>
       </c>
       <c r="L93" t="n">
-        <v>0.8234999841079116</v>
+        <v>1.2816000089515</v>
       </c>
     </row>
     <row r="94">
       <c r="A94" t="n">
-        <v>0.1729170035105199</v>
+        <v>0.269500000285916</v>
       </c>
       <c r="B94" t="n">
-        <v>0.07179201929830015</v>
+        <v>0.1442999928258359</v>
       </c>
       <c r="C94" t="n">
-        <v>0.06041699089109898</v>
+        <v>0.1003999932436273</v>
       </c>
       <c r="D94" t="n">
-        <v>0.9148340031970292</v>
+        <v>1.521500002127141</v>
       </c>
       <c r="E94" t="n">
-        <v>0.393458001781255</v>
+        <v>0.6907000060891733</v>
       </c>
       <c r="F94" t="n">
-        <v>0.192915991647169</v>
+        <v>0.2704999933484942</v>
       </c>
       <c r="G94" t="n">
-        <v>4.749583022203296</v>
+        <v>7.341100004850887</v>
       </c>
       <c r="H94" t="n">
-        <v>1.973375008674338</v>
+        <v>3.408999997191131</v>
       </c>
       <c r="I94" t="n">
-        <v>0.385499995900318</v>
+        <v>0.5895000067539513</v>
       </c>
       <c r="J94" t="n">
-        <v>21.4685829996597</v>
+        <v>31.3041999907</v>
       </c>
       <c r="K94" t="n">
-        <v>8.713125018402934</v>
+        <v>13.90099999844097</v>
       </c>
       <c r="L94" t="n">
-        <v>0.8105000015348196</v>
+        <v>1.275700007681735</v>
       </c>
     </row>
     <row r="95">
       <c r="A95" t="n">
-        <v>0.1435409940313548</v>
+        <v>0.3138000029139221</v>
       </c>
       <c r="B95" t="n">
-        <v>0.05954201333224773</v>
+        <v>0.1190000039059669</v>
       </c>
       <c r="C95" t="n">
-        <v>0.06041701999492943</v>
+        <v>0.1316999987466261</v>
       </c>
       <c r="D95" t="n">
-        <v>0.9952499822247773</v>
+        <v>1.694699996733107</v>
       </c>
       <c r="E95" t="n">
-        <v>0.4408340028021485</v>
+        <v>0.7730000070296228</v>
       </c>
       <c r="F95" t="n">
-        <v>0.174082990270108</v>
+        <v>0.2703999925870448</v>
       </c>
       <c r="G95" t="n">
-        <v>4.75954101420939</v>
+        <v>7.448799995472655</v>
       </c>
       <c r="H95" t="n">
-        <v>2.011709002545103</v>
+        <v>3.392500002519228</v>
       </c>
       <c r="I95" t="n">
-        <v>0.3707910072989762</v>
+        <v>0.5941999988863245</v>
       </c>
       <c r="J95" t="n">
-        <v>21.63391601061448</v>
+        <v>31.3010999961989</v>
       </c>
       <c r="K95" t="n">
-        <v>9.170959005132318</v>
+        <v>13.74399999622256</v>
       </c>
       <c r="L95" t="n">
-        <v>0.8141660073306412</v>
+        <v>1.28309999126941</v>
       </c>
     </row>
     <row r="96">
       <c r="A96" t="n">
-        <v>0.1522499951533973</v>
+        <v>0.2534000086598098</v>
       </c>
       <c r="B96" t="n">
-        <v>0.07816602010279894</v>
+        <v>0.123399993753992</v>
       </c>
       <c r="C96" t="n">
-        <v>0.05954099469818175</v>
+        <v>0.1023999939206988</v>
       </c>
       <c r="D96" t="n">
-        <v>0.9688329882919788</v>
+        <v>1.586600003065541</v>
       </c>
       <c r="E96" t="n">
-        <v>0.4015409795101732</v>
+        <v>0.7614999922225252</v>
       </c>
       <c r="F96" t="n">
-        <v>0.1662079885136336</v>
+        <v>0.2706999948713928</v>
       </c>
       <c r="G96" t="n">
-        <v>4.533833009190857</v>
+        <v>7.230699993669987</v>
       </c>
       <c r="H96" t="n">
-        <v>1.94583399570547</v>
+        <v>3.360000002430752</v>
       </c>
       <c r="I96" t="n">
-        <v>0.3747080045286566</v>
+        <v>0.5983000010019168</v>
       </c>
       <c r="J96" t="n">
-        <v>22.04070900916122</v>
+        <v>30.69739999773446</v>
       </c>
       <c r="K96" t="n">
-        <v>9.385917015606537</v>
+        <v>13.85659999505151</v>
       </c>
       <c r="L96" t="n">
-        <v>0.9144169744104147</v>
+        <v>1.291599997784942</v>
       </c>
     </row>
     <row r="97">
       <c r="A97" t="n">
-        <v>0.1577909861225635</v>
+        <v>0.264299989794381</v>
       </c>
       <c r="B97" t="n">
-        <v>0.07000000914558768</v>
+        <v>0.1341000024694949</v>
       </c>
       <c r="C97" t="n">
-        <v>0.06166700040921569</v>
+        <v>0.09689999569673091</v>
       </c>
       <c r="D97" t="n">
-        <v>0.9763329871930182</v>
+        <v>1.635799999348819</v>
       </c>
       <c r="E97" t="n">
-        <v>0.4181670083198696</v>
+        <v>0.7794999983161688</v>
       </c>
       <c r="F97" t="n">
-        <v>0.175207998836413</v>
+        <v>0.272899997071363</v>
       </c>
       <c r="G97" t="n">
-        <v>4.503957985434681</v>
+        <v>7.036499999230728</v>
       </c>
       <c r="H97" t="n">
-        <v>1.895041990792379</v>
+        <v>3.298300012829714</v>
       </c>
       <c r="I97" t="n">
-        <v>0.3714589984156191</v>
+        <v>0.6129999965196475</v>
       </c>
       <c r="J97" t="n">
-        <v>22.74795802077278</v>
+        <v>30.29280000191648</v>
       </c>
       <c r="K97" t="n">
-        <v>8.75962499412708</v>
+        <v>12.82730000093579</v>
       </c>
       <c r="L97" t="n">
-        <v>0.837958010379225</v>
+        <v>1.270400010980666</v>
       </c>
     </row>
     <row r="98">
       <c r="A98" t="n">
-        <v>0.1610420003999025</v>
+        <v>0.2707999956328422</v>
       </c>
       <c r="B98" t="n">
-        <v>0.0702079851180315</v>
+        <v>0.1345999917248264</v>
       </c>
       <c r="C98" t="n">
-        <v>0.06166700040921569</v>
+        <v>0.09549999958835542</v>
       </c>
       <c r="D98" t="n">
-        <v>1.053084008162841</v>
+        <v>1.700199994957075</v>
       </c>
       <c r="E98" t="n">
-        <v>0.4067500121891499</v>
+        <v>0.7603999983984977</v>
       </c>
       <c r="F98" t="n">
-        <v>0.1739170111250132</v>
+        <v>0.2718000032473356</v>
       </c>
       <c r="G98" t="n">
-        <v>4.773583001224324</v>
+        <v>7.463100002496503</v>
       </c>
       <c r="H98" t="n">
-        <v>2.000999986194074</v>
+        <v>3.492699994239956</v>
       </c>
       <c r="I98" t="n">
-        <v>0.3791250055655837</v>
+        <v>0.6061000021873042</v>
       </c>
       <c r="J98" t="n">
-        <v>23.67545798188075</v>
+        <v>30.87149999919347</v>
       </c>
       <c r="K98" t="n">
-        <v>10.31658300780691</v>
+        <v>13.79119999182876</v>
       </c>
       <c r="L98" t="n">
-        <v>0.8287079981528223</v>
+        <v>1.267700004973449</v>
       </c>
     </row>
     <row r="99">
       <c r="A99" t="n">
-        <v>0.1725830079521984</v>
+        <v>0.2898000093409792</v>
       </c>
       <c r="B99" t="n">
-        <v>0.08437497308477759</v>
+        <v>0.1628999889362603</v>
       </c>
       <c r="C99" t="n">
-        <v>0.06154199945740402</v>
+        <v>0.09699999645818025</v>
       </c>
       <c r="D99" t="n">
-        <v>1.057082990882918</v>
+        <v>1.736800011713058</v>
       </c>
       <c r="E99" t="n">
-        <v>0.424917001510039</v>
+        <v>0.8170999935828149</v>
       </c>
       <c r="F99" t="n">
-        <v>0.1728330098558217</v>
+        <v>0.2693000133149326</v>
       </c>
       <c r="G99" t="n">
-        <v>4.740375006804243</v>
+        <v>7.441299996571615</v>
       </c>
       <c r="H99" t="n">
-        <v>1.946667005540803</v>
+        <v>3.297600007499568</v>
       </c>
       <c r="I99" t="n">
-        <v>0.372500013327226</v>
+        <v>0.58970000827685</v>
       </c>
       <c r="J99" t="n">
-        <v>21.53741600341164</v>
+        <v>30.7846000068821</v>
       </c>
       <c r="K99" t="n">
-        <v>8.636374986963347</v>
+        <v>13.28070000454318</v>
       </c>
       <c r="L99" t="n">
-        <v>0.8341250068042427</v>
+        <v>1.303199998801574</v>
       </c>
     </row>
     <row r="100">
       <c r="A100" t="n">
-        <v>0.1349170051980764</v>
+        <v>0.2289000112796202</v>
       </c>
       <c r="B100" t="n">
-        <v>0.05883301491849124</v>
+        <v>0.1131000026362017</v>
       </c>
       <c r="C100" t="n">
-        <v>0.06812499486841261</v>
+        <v>0.0948999950196594</v>
       </c>
       <c r="D100" t="n">
-        <v>1.003415993181989</v>
+        <v>1.681699999608099</v>
       </c>
       <c r="E100" t="n">
-        <v>0.422042008722201</v>
+        <v>0.7898000039858744</v>
       </c>
       <c r="F100" t="n">
-        <v>0.1725829788483679</v>
+        <v>0.2998999989358708</v>
       </c>
       <c r="G100" t="n">
-        <v>4.833874991163611</v>
+        <v>7.507899994379841</v>
       </c>
       <c r="H100" t="n">
-        <v>2.000125008635223</v>
+        <v>3.449000010732561</v>
       </c>
       <c r="I100" t="n">
-        <v>0.3816249954979867</v>
+        <v>0.5837999924551696</v>
       </c>
       <c r="J100" t="n">
-        <v>22.40862499456853</v>
+        <v>31.89429998747073</v>
       </c>
       <c r="K100" t="n">
-        <v>9.220166015438735</v>
+        <v>14.299900009064</v>
       </c>
       <c r="L100" t="n">
-        <v>0.8507499878760427</v>
+        <v>1.28529999346938</v>
       </c>
     </row>
     <row r="101">
       <c r="A101" t="n">
-        <v>0.1674999948590994</v>
+        <v>0.2710000117076561</v>
       </c>
       <c r="B101" t="n">
-        <v>0.079624995123595</v>
+        <v>0.1466999965487048</v>
       </c>
       <c r="C101" t="n">
-        <v>0.0634589814580977</v>
+        <v>0.09760000102687627</v>
       </c>
       <c r="D101" t="n">
-        <v>0.9632500004954636</v>
+        <v>1.636400003917515</v>
       </c>
       <c r="E101" t="n">
-        <v>0.4175840003881603</v>
+        <v>0.7941000076243654</v>
       </c>
       <c r="F101" t="n">
-        <v>0.1709579955786467</v>
+        <v>0.2801000082399696</v>
       </c>
       <c r="G101" t="n">
-        <v>4.8571249935776</v>
+        <v>7.525599998189136</v>
       </c>
       <c r="H101" t="n">
-        <v>2.048875001491979</v>
+        <v>3.524500003550202</v>
       </c>
       <c r="I101" t="n">
-        <v>0.3723329864442348</v>
+        <v>0.5926000012550503</v>
       </c>
       <c r="J101" t="n">
-        <v>21.9773749995511</v>
+        <v>30.83259999402799</v>
       </c>
       <c r="K101" t="n">
-        <v>8.987999986857176</v>
+        <v>13.77369998954237</v>
       </c>
       <c r="L101" t="n">
-        <v>0.8397920173592865</v>
+        <v>1.285999998799525</v>
       </c>
     </row>
   </sheetData>

--- a/resultados_algoritmos/datos_para_RISK.xlsx
+++ b/resultados_algoritmos/datos_para_RISK.xlsx
@@ -480,3802 +480,3802 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>0.2712999994400889</v>
+        <v>0.2589589857961982</v>
       </c>
       <c r="B2" t="n">
-        <v>0.1774999982444569</v>
+        <v>0.07795798592269421</v>
       </c>
       <c r="C2" t="n">
-        <v>0.1371999969705939</v>
+        <v>0.06849999772384763</v>
       </c>
       <c r="D2" t="n">
-        <v>1.680800007306971</v>
+        <v>1.051958010066301</v>
       </c>
       <c r="E2" t="n">
-        <v>0.7436000014422461</v>
+        <v>0.4569169832393527</v>
       </c>
       <c r="F2" t="n">
-        <v>0.2892000047722831</v>
+        <v>0.1924170064739883</v>
       </c>
       <c r="G2" t="n">
-        <v>7.054299989249557</v>
+        <v>4.79674999951385</v>
       </c>
       <c r="H2" t="n">
-        <v>3.378299996256828</v>
+        <v>2.001540997298434</v>
       </c>
       <c r="I2" t="n">
-        <v>0.5945000011706725</v>
+        <v>0.4394999996293336</v>
       </c>
       <c r="J2" t="n">
-        <v>33.53290000814013</v>
+        <v>21.21100001386367</v>
       </c>
       <c r="K2" t="n">
-        <v>14.27349999721628</v>
+        <v>8.690374990692362</v>
       </c>
       <c r="L2" t="n">
-        <v>1.265899991267361</v>
+        <v>0.815875013358891</v>
       </c>
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>0.2815999905578792</v>
+        <v>0.1754999975673854</v>
       </c>
       <c r="B3" t="n">
-        <v>0.1457999896956608</v>
+        <v>0.07787501090206206</v>
       </c>
       <c r="C3" t="n">
-        <v>0.1008999970508739</v>
+        <v>0.06666698027402163</v>
       </c>
       <c r="D3" t="n">
-        <v>1.834800001233816</v>
+        <v>1.055208005709574</v>
       </c>
       <c r="E3" t="n">
-        <v>0.9172999998554587</v>
+        <v>0.4436660092324018</v>
       </c>
       <c r="F3" t="n">
-        <v>0.2712999994400889</v>
+        <v>0.1691670040600002</v>
       </c>
       <c r="G3" t="n">
-        <v>7.045499995001592</v>
+        <v>4.677291988627985</v>
       </c>
       <c r="H3" t="n">
-        <v>3.131899997242726</v>
+        <v>1.805459003662691</v>
       </c>
       <c r="I3" t="n">
-        <v>0.5990000063320622</v>
+        <v>0.3711250028572977</v>
       </c>
       <c r="J3" t="n">
-        <v>30.88570000545587</v>
+        <v>21.12245801254176</v>
       </c>
       <c r="K3" t="n">
-        <v>13.6179999972228</v>
+        <v>8.51941600558348</v>
       </c>
       <c r="L3" t="n">
-        <v>1.271300003281794</v>
+        <v>0.8141669968608767</v>
       </c>
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>0.2867000002879649</v>
+        <v>0.1752089883666486</v>
       </c>
       <c r="B4" t="n">
-        <v>0.141500000609085</v>
+        <v>0.07541599916294217</v>
       </c>
       <c r="C4" t="n">
-        <v>0.1017000031424686</v>
+        <v>0.06691599264740944</v>
       </c>
       <c r="D4" t="n">
-        <v>1.785600004950538</v>
+        <v>1.058624999132007</v>
       </c>
       <c r="E4" t="n">
-        <v>0.8812000014586374</v>
+        <v>0.4479579802136868</v>
       </c>
       <c r="F4" t="n">
-        <v>0.2714000002015382</v>
+        <v>0.1728330098558217</v>
       </c>
       <c r="G4" t="n">
-        <v>7.268899993505329</v>
+        <v>4.831208992982283</v>
       </c>
       <c r="H4" t="n">
-        <v>3.298600000562146</v>
+        <v>1.881583011709154</v>
       </c>
       <c r="I4" t="n">
-        <v>0.5986000032862648</v>
+        <v>0.3718340012710541</v>
       </c>
       <c r="J4" t="n">
-        <v>30.65020000212826</v>
+        <v>21.41712501179427</v>
       </c>
       <c r="K4" t="n">
-        <v>13.86669999919832</v>
+        <v>8.730208006454632</v>
       </c>
       <c r="L4" t="n">
-        <v>1.27500000235159</v>
+        <v>0.8132920193020254</v>
       </c>
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>0.2948999899672344</v>
+        <v>0.1667080214247108</v>
       </c>
       <c r="B5" t="n">
-        <v>0.1566999999340624</v>
+        <v>0.0730419997125864</v>
       </c>
       <c r="C5" t="n">
-        <v>0.1020000054268166</v>
+        <v>0.06058398867025971</v>
       </c>
       <c r="D5" t="n">
-        <v>1.808999993954785</v>
+        <v>1.083624985767528</v>
       </c>
       <c r="E5" t="n">
-        <v>0.8317000028910115</v>
+        <v>0.4327920032665133</v>
       </c>
       <c r="F5" t="n">
-        <v>0.2717000024858862</v>
+        <v>0.1804580097086728</v>
       </c>
       <c r="G5" t="n">
-        <v>7.139599998481572</v>
+        <v>4.807249992154539</v>
       </c>
       <c r="H5" t="n">
-        <v>3.384299998288043</v>
+        <v>1.983666996238753</v>
       </c>
       <c r="I5" t="n">
-        <v>0.5941999988863245</v>
+        <v>0.3772500203922391</v>
       </c>
       <c r="J5" t="n">
-        <v>31.17799999017734</v>
+        <v>21.67216700036079</v>
       </c>
       <c r="K5" t="n">
-        <v>13.64640000974759</v>
+        <v>8.672750002006069</v>
       </c>
       <c r="L5" t="n">
-        <v>1.261099998373538</v>
+        <v>0.8334160083904862</v>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>0.2590999938547611</v>
+        <v>0.147000013384968</v>
       </c>
       <c r="B6" t="n">
-        <v>0.1243000006070361</v>
+        <v>0.06133399438112974</v>
       </c>
       <c r="C6" t="n">
-        <v>0.1027999969664961</v>
+        <v>0.06062502507120371</v>
       </c>
       <c r="D6" t="n">
-        <v>1.733700002660044</v>
+        <v>1.050708000548184</v>
       </c>
       <c r="E6" t="n">
-        <v>0.8674999990034848</v>
+        <v>0.4440000047907233</v>
       </c>
       <c r="F6" t="n">
-        <v>0.2708999963942915</v>
+        <v>0.1802500046323985</v>
       </c>
       <c r="G6" t="n">
-        <v>7.262599989189766</v>
+        <v>4.859791981289163</v>
       </c>
       <c r="H6" t="n">
-        <v>3.501999992295168</v>
+        <v>2.009250019909814</v>
       </c>
       <c r="I6" t="n">
-        <v>0.5947999889031053</v>
+        <v>0.3777920210268348</v>
       </c>
       <c r="J6" t="n">
-        <v>31.67900000698864</v>
+        <v>21.9754170102533</v>
       </c>
       <c r="K6" t="n">
-        <v>13.95759999286383</v>
+        <v>8.985166990896687</v>
       </c>
       <c r="L6" t="n">
-        <v>1.289099993300624</v>
+        <v>0.8259160094894469</v>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>0.2589999930933118</v>
+        <v>0.1607500016689301</v>
       </c>
       <c r="B7" t="n">
-        <v>0.1274999958695844</v>
+        <v>0.06283298716880381</v>
       </c>
       <c r="C7" t="n">
-        <v>0.09869999485090375</v>
+        <v>0.06416699034161866</v>
       </c>
       <c r="D7" t="n">
-        <v>1.735800004098564</v>
+        <v>1.045084005454555</v>
       </c>
       <c r="E7" t="n">
-        <v>0.8831999875837937</v>
+        <v>0.4583749978337437</v>
       </c>
       <c r="F7" t="n">
-        <v>0.2759000053629279</v>
+        <v>0.172666012076661</v>
       </c>
       <c r="G7" t="n">
-        <v>7.3302000091644</v>
+        <v>4.893999983323738</v>
       </c>
       <c r="H7" t="n">
-        <v>3.563200007192791</v>
+        <v>2.071708004223183</v>
       </c>
       <c r="I7" t="n">
-        <v>0.6009000062476844</v>
+        <v>0.3644580137915909</v>
       </c>
       <c r="J7" t="n">
-        <v>31.27530000347178</v>
+        <v>21.90129199880175</v>
       </c>
       <c r="K7" t="n">
-        <v>13.86160000402015</v>
+        <v>8.890957979019731</v>
       </c>
       <c r="L7" t="n">
-        <v>1.280499986023642</v>
+        <v>0.8305839728564024</v>
       </c>
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>0.2773000014713034</v>
+        <v>0.1662079885136336</v>
       </c>
       <c r="B8" t="n">
-        <v>0.1388000091537833</v>
+        <v>0.07408301462419331</v>
       </c>
       <c r="C8" t="n">
-        <v>0.09840000711847097</v>
+        <v>0.06333400961011648</v>
       </c>
       <c r="D8" t="n">
-        <v>1.828499996918254</v>
+        <v>1.236042007803917</v>
       </c>
       <c r="E8" t="n">
-        <v>0.934299998334609</v>
+        <v>0.5541249993257225</v>
       </c>
       <c r="F8" t="n">
-        <v>0.2778000052785501</v>
+        <v>0.1721250009723008</v>
       </c>
       <c r="G8" t="n">
-        <v>6.96730001072865</v>
+        <v>4.550624988041818</v>
       </c>
       <c r="H8" t="n">
-        <v>3.160399995977059</v>
+        <v>1.829415996326134</v>
       </c>
       <c r="I8" t="n">
-        <v>0.5930000043008476</v>
+        <v>0.3802499850280583</v>
       </c>
       <c r="J8" t="n">
-        <v>31.41860000323504</v>
+        <v>21.74300001934171</v>
       </c>
       <c r="K8" t="n">
-        <v>13.86920000368264</v>
+        <v>8.946791989728808</v>
       </c>
       <c r="L8" t="n">
-        <v>1.290800006245263</v>
+        <v>0.8090829942375422</v>
       </c>
     </row>
     <row r="9">
       <c r="A9" t="n">
-        <v>0.3029000072274357</v>
+        <v>0.1589169842191041</v>
       </c>
       <c r="B9" t="n">
-        <v>0.1420000044163316</v>
+        <v>0.07304101018235087</v>
       </c>
       <c r="C9" t="n">
-        <v>0.09800000407267362</v>
+        <v>0.0602919899392873</v>
       </c>
       <c r="D9" t="n">
-        <v>1.639599999180064</v>
+        <v>0.9879170102067292</v>
       </c>
       <c r="E9" t="n">
-        <v>0.8323000074597076</v>
+        <v>0.4171250038780272</v>
       </c>
       <c r="F9" t="n">
-        <v>0.2742999931797385</v>
+        <v>0.1722919987514615</v>
       </c>
       <c r="G9" t="n">
-        <v>7.419899993692525</v>
+        <v>4.988625005353242</v>
       </c>
       <c r="H9" t="n">
-        <v>3.538700009812601</v>
+        <v>2.063334017293528</v>
       </c>
       <c r="I9" t="n">
-        <v>0.5954000080237165</v>
+        <v>0.3766250156331807</v>
       </c>
       <c r="J9" t="n">
-        <v>31.38740001304541</v>
+        <v>21.82624998386018</v>
       </c>
       <c r="K9" t="n">
-        <v>14.0118999988772</v>
+        <v>8.873707993188873</v>
       </c>
       <c r="L9" t="n">
-        <v>1.29420000303071</v>
+        <v>0.7915830065030605</v>
       </c>
     </row>
     <row r="10">
       <c r="A10" t="n">
-        <v>0.2813000028254464</v>
+        <v>0.1669999910518527</v>
       </c>
       <c r="B10" t="n">
-        <v>0.1456000027246773</v>
+        <v>0.07441701018251479</v>
       </c>
       <c r="C10" t="n">
-        <v>0.09970000246539712</v>
+        <v>0.06079100421629846</v>
       </c>
       <c r="D10" t="n">
-        <v>1.679100008914247</v>
+        <v>1.000791002297774</v>
       </c>
       <c r="E10" t="n">
-        <v>0.7812999974703416</v>
+        <v>0.4008749965578318</v>
       </c>
       <c r="F10" t="n">
-        <v>0.2834999904735014</v>
+        <v>0.1741669839248061</v>
       </c>
       <c r="G10" t="n">
-        <v>7.106200006091967</v>
+        <v>4.7703750024084</v>
       </c>
       <c r="H10" t="n">
-        <v>3.322199991089292</v>
+        <v>1.839332981035113</v>
       </c>
       <c r="I10" t="n">
-        <v>0.6980000034673139</v>
+        <v>0.3687499847728759</v>
       </c>
       <c r="J10" t="n">
-        <v>31.17059999203775</v>
+        <v>21.77233400288969</v>
       </c>
       <c r="K10" t="n">
-        <v>13.56650001253001</v>
+        <v>8.699500001966953</v>
       </c>
       <c r="L10" t="n">
-        <v>1.280199998291209</v>
+        <v>0.820541987195611</v>
       </c>
     </row>
     <row r="11">
       <c r="A11" t="n">
-        <v>0.2779999922495335</v>
+        <v>0.1482910010963678</v>
       </c>
       <c r="B11" t="n">
-        <v>0.1311000087298453</v>
+        <v>0.06675001350231469</v>
       </c>
       <c r="C11" t="n">
-        <v>0.0973999995039776</v>
+        <v>0.06000002031214535</v>
       </c>
       <c r="D11" t="n">
-        <v>1.714300000458024</v>
+        <v>1.204875006806105</v>
       </c>
       <c r="E11" t="n">
-        <v>0.8343999943463132</v>
+        <v>0.4349999944679439</v>
       </c>
       <c r="F11" t="n">
-        <v>0.2728000108618289</v>
+        <v>0.1731659867800772</v>
       </c>
       <c r="G11" t="n">
-        <v>7.238899997901171</v>
+        <v>4.827166005270556</v>
       </c>
       <c r="H11" t="n">
-        <v>3.461300002527423</v>
+        <v>2.026542002568021</v>
       </c>
       <c r="I11" t="n">
-        <v>0.5932999920332804</v>
+        <v>0.3775410004891455</v>
       </c>
       <c r="J11" t="n">
-        <v>31.32700000423938</v>
+        <v>21.22104100999422</v>
       </c>
       <c r="K11" t="n">
-        <v>13.43479999923147</v>
+        <v>8.436000003712252</v>
       </c>
       <c r="L11" t="n">
-        <v>1.288800005568191</v>
+        <v>0.8167919877450913</v>
       </c>
     </row>
     <row r="12">
       <c r="A12" t="n">
-        <v>0.2659000019775704</v>
+        <v>0.1686250034254044</v>
       </c>
       <c r="B12" t="n">
-        <v>0.1226000022143126</v>
+        <v>0.06891699740663171</v>
       </c>
       <c r="C12" t="n">
-        <v>0.09900001168716699</v>
+        <v>0.1375410065520555</v>
       </c>
       <c r="D12" t="n">
-        <v>1.799699995899573</v>
+        <v>1.012332999380305</v>
       </c>
       <c r="E12" t="n">
-        <v>0.8803999953670427</v>
+        <v>0.472374988021329</v>
       </c>
       <c r="F12" t="n">
-        <v>0.2792000013869256</v>
+        <v>0.1706250186543912</v>
       </c>
       <c r="G12" t="n">
-        <v>7.538000005297363</v>
+        <v>4.918708000332117</v>
       </c>
       <c r="H12" t="n">
-        <v>3.583900004741736</v>
+        <v>2.127165993442759</v>
       </c>
       <c r="I12" t="n">
-        <v>0.5893000052310526</v>
+        <v>0.3638750058598816</v>
       </c>
       <c r="J12" t="n">
-        <v>30.34019999904558</v>
+        <v>21.38516699778847</v>
       </c>
       <c r="K12" t="n">
-        <v>13.66810000035912</v>
+        <v>8.54895799420774</v>
       </c>
       <c r="L12" t="n">
-        <v>1.435099999071099</v>
+        <v>0.9040840086527169</v>
       </c>
     </row>
     <row r="13">
       <c r="A13" t="n">
-        <v>0.2724000078160316</v>
+        <v>0.1585829886607826</v>
       </c>
       <c r="B13" t="n">
-        <v>0.1241999998455867</v>
+        <v>0.06933300755918026</v>
       </c>
       <c r="C13" t="n">
-        <v>0.1023999939206988</v>
+        <v>0.06683400715701282</v>
       </c>
       <c r="D13" t="n">
-        <v>1.56089999654796</v>
+        <v>0.9568340028636158</v>
       </c>
       <c r="E13" t="n">
-        <v>0.7710999925620854</v>
+        <v>0.4174580099061131</v>
       </c>
       <c r="F13" t="n">
-        <v>0.2822999958880246</v>
+        <v>0.1672089856583625</v>
       </c>
       <c r="G13" t="n">
-        <v>6.960800004890189</v>
+        <v>4.72645799163729</v>
       </c>
       <c r="H13" t="n">
-        <v>3.351000006659888</v>
+        <v>1.842375000705943</v>
       </c>
       <c r="I13" t="n">
-        <v>0.5903999990550801</v>
+        <v>0.4117500211577863</v>
       </c>
       <c r="J13" t="n">
-        <v>29.79230000346433</v>
+        <v>21.11879200674593</v>
       </c>
       <c r="K13" t="n">
-        <v>13.97450000513345</v>
+        <v>8.76354199135676</v>
       </c>
       <c r="L13" t="n">
-        <v>1.282500001252629</v>
+        <v>0.8101249986793846</v>
       </c>
     </row>
     <row r="14">
       <c r="A14" t="n">
-        <v>0.2697999880183488</v>
+        <v>0.170832994626835</v>
       </c>
       <c r="B14" t="n">
-        <v>0.1323000033153221</v>
+        <v>0.06770898471586406</v>
       </c>
       <c r="C14" t="n">
-        <v>0.09919999865815043</v>
+        <v>0.0604590168222785</v>
       </c>
       <c r="D14" t="n">
-        <v>1.696699997410178</v>
+        <v>1.041999988956377</v>
       </c>
       <c r="E14" t="n">
-        <v>0.8720999903744087</v>
+        <v>0.4498750204220414</v>
       </c>
       <c r="F14" t="n">
-        <v>0.2729999978328124</v>
+        <v>0.1768750080373138</v>
       </c>
       <c r="G14" t="n">
-        <v>7.165999995777383</v>
+        <v>4.804500000318512</v>
       </c>
       <c r="H14" t="n">
-        <v>3.458600011072122</v>
+        <v>1.999625004827976</v>
       </c>
       <c r="I14" t="n">
-        <v>0.5881000106455758</v>
+        <v>0.363375002052635</v>
       </c>
       <c r="J14" t="n">
-        <v>30.71009999257512</v>
+        <v>21.3391249999404</v>
       </c>
       <c r="K14" t="n">
-        <v>13.80950000020675</v>
+        <v>8.68654201622121</v>
       </c>
       <c r="L14" t="n">
-        <v>1.311100000748411</v>
+        <v>0.7955830078572035</v>
       </c>
     </row>
     <row r="15">
       <c r="A15" t="n">
-        <v>0.2420999953756109</v>
+        <v>0.1417080056853592</v>
       </c>
       <c r="B15" t="n">
-        <v>0.1181999978143722</v>
+        <v>0.06041600136086345</v>
       </c>
       <c r="C15" t="n">
-        <v>0.09929999941959977</v>
+        <v>0.05941698327660561</v>
       </c>
       <c r="D15" t="n">
-        <v>1.606399993761443</v>
+        <v>0.9679170034360141</v>
       </c>
       <c r="E15" t="n">
-        <v>0.7926000107545406</v>
+        <v>0.399582990212366</v>
       </c>
       <c r="F15" t="n">
-        <v>0.2736000024015084</v>
+        <v>0.1770830131135881</v>
       </c>
       <c r="G15" t="n">
-        <v>7.061099997372366</v>
+        <v>4.704249993665144</v>
       </c>
       <c r="H15" t="n">
-        <v>3.37809999473393</v>
+        <v>2.076250006211922</v>
       </c>
       <c r="I15" t="n">
-        <v>0.5903999990550801</v>
+        <v>0.3628749982453883</v>
       </c>
       <c r="J15" t="n">
-        <v>30.61109999543987</v>
+        <v>21.20854202075861</v>
       </c>
       <c r="K15" t="n">
-        <v>13.74899999063928</v>
+        <v>8.75758400070481</v>
       </c>
       <c r="L15" t="n">
-        <v>1.292900007683784</v>
+        <v>0.8235420100390911</v>
       </c>
     </row>
     <row r="16">
       <c r="A16" t="n">
-        <v>0.2871000033337623</v>
+        <v>0.1878330076579005</v>
       </c>
       <c r="B16" t="n">
-        <v>0.1441000058548525</v>
+        <v>0.0829579948913306</v>
       </c>
       <c r="C16" t="n">
-        <v>0.0990999978967011</v>
+        <v>0.06091699469834566</v>
       </c>
       <c r="D16" t="n">
-        <v>1.750600000377744</v>
+        <v>1.049125014105812</v>
       </c>
       <c r="E16" t="n">
-        <v>0.8361000072909519</v>
+        <v>0.4325410118326545</v>
       </c>
       <c r="F16" t="n">
-        <v>0.2750999992713332</v>
+        <v>0.1757080026436597</v>
       </c>
       <c r="G16" t="n">
-        <v>6.852899998193607</v>
+        <v>4.62904101004824</v>
       </c>
       <c r="H16" t="n">
-        <v>3.443499997956678</v>
+        <v>1.960458990652114</v>
       </c>
       <c r="I16" t="n">
-        <v>0.5920999974478036</v>
+        <v>0.4103330138605088</v>
       </c>
       <c r="J16" t="n">
-        <v>30.12009999656584</v>
+        <v>21.15754201076925</v>
       </c>
       <c r="K16" t="n">
-        <v>13.20180000038818</v>
+        <v>8.361415995750576</v>
       </c>
       <c r="L16" t="n">
-        <v>1.290700005483814</v>
+        <v>0.8090420160442591</v>
       </c>
     </row>
     <row r="17">
       <c r="A17" t="n">
-        <v>0.2485000004526228</v>
+        <v>0.1503329840488732</v>
       </c>
       <c r="B17" t="n">
-        <v>0.11629999789875</v>
+        <v>0.06262498209252954</v>
       </c>
       <c r="C17" t="n">
-        <v>0.09719999798107892</v>
+        <v>0.06325001595541835</v>
       </c>
       <c r="D17" t="n">
-        <v>1.674300001468509</v>
+        <v>0.9978330053854734</v>
       </c>
       <c r="E17" t="n">
-        <v>0.81490000593476</v>
+        <v>0.4222909919917583</v>
       </c>
       <c r="F17" t="n">
-        <v>0.2755000023171306</v>
+        <v>0.1722500019241124</v>
       </c>
       <c r="G17" t="n">
-        <v>6.946100009372458</v>
+        <v>4.702417005319148</v>
       </c>
       <c r="H17" t="n">
-        <v>3.264700004365295</v>
+        <v>1.901000010548159</v>
       </c>
       <c r="I17" t="n">
-        <v>0.5872000037925318</v>
+        <v>0.372083013644442</v>
       </c>
       <c r="J17" t="n">
-        <v>30.6739999941783</v>
+        <v>21.20087499497458</v>
       </c>
       <c r="K17" t="n">
-        <v>13.6140999966301</v>
+        <v>8.614249993115664</v>
       </c>
       <c r="L17" t="n">
-        <v>1.285999998799525</v>
+        <v>0.8238329901359975</v>
       </c>
     </row>
     <row r="18">
       <c r="A18" t="n">
-        <v>0.2460999967297539</v>
+        <v>0.1671669888310134</v>
       </c>
       <c r="B18" t="n">
-        <v>0.1211000053444877</v>
+        <v>0.0703750120010227</v>
       </c>
       <c r="C18" t="n">
-        <v>0.09849999332800508</v>
+        <v>0.07224999717436731</v>
       </c>
       <c r="D18" t="n">
-        <v>1.675899999099784</v>
+        <v>1.076249987818301</v>
       </c>
       <c r="E18" t="n">
-        <v>0.7748999923933297</v>
+        <v>0.3885840123984963</v>
       </c>
       <c r="F18" t="n">
-        <v>0.272299992502667</v>
+        <v>0.1754590193741024</v>
       </c>
       <c r="G18" t="n">
-        <v>7.086699988576584</v>
+        <v>4.834374994970858</v>
       </c>
       <c r="H18" t="n">
-        <v>3.480900006252341</v>
+        <v>2.017499995417893</v>
       </c>
       <c r="I18" t="n">
-        <v>0.5898999952478334</v>
+        <v>0.3952500119339675</v>
       </c>
       <c r="J18" t="n">
-        <v>31.12929999770131</v>
+        <v>21.32466700277291</v>
       </c>
       <c r="K18" t="n">
-        <v>13.78009999461938</v>
+        <v>8.740375022171065</v>
       </c>
       <c r="L18" t="n">
-        <v>1.280500000575557</v>
+        <v>0.8134590170811862</v>
       </c>
     </row>
     <row r="19">
       <c r="A19" t="n">
-        <v>0.269199998001568</v>
+        <v>0.1747909991536289</v>
       </c>
       <c r="B19" t="n">
-        <v>0.1376000000163913</v>
+        <v>0.08170798537321389</v>
       </c>
       <c r="C19" t="n">
-        <v>0.0973999995039776</v>
+        <v>0.07537499186582863</v>
       </c>
       <c r="D19" t="n">
-        <v>1.687600000877865</v>
+        <v>1.027332997182384</v>
       </c>
       <c r="E19" t="n">
-        <v>0.814300001366064</v>
+        <v>0.4158329975325614</v>
       </c>
       <c r="F19" t="n">
-        <v>0.2754999877652153</v>
+        <v>0.1673750230111182</v>
       </c>
       <c r="G19" t="n">
-        <v>7.084800003212877</v>
+        <v>4.715582996141165</v>
       </c>
       <c r="H19" t="n">
-        <v>3.464199995505624</v>
+        <v>1.937541994266212</v>
       </c>
       <c r="I19" t="n">
-        <v>0.5862999969394878</v>
+        <v>0.3935839922633022</v>
       </c>
       <c r="J19" t="n">
-        <v>30.25450000131968</v>
+        <v>21.1498330172617</v>
       </c>
       <c r="K19" t="n">
-        <v>13.64380000450183</v>
+        <v>8.51662500645034</v>
       </c>
       <c r="L19" t="n">
-        <v>1.28240000049118</v>
+        <v>0.8087090100161731</v>
       </c>
     </row>
     <row r="20">
       <c r="A20" t="n">
-        <v>0.2766999969026074</v>
+        <v>0.1678749977145344</v>
       </c>
       <c r="B20" t="n">
-        <v>0.130499989609234</v>
+        <v>0.06895800470374525</v>
       </c>
       <c r="C20" t="n">
-        <v>0.09899999713525176</v>
+        <v>0.0624579843133688</v>
       </c>
       <c r="D20" t="n">
-        <v>1.700299995718524</v>
+        <v>1.046375022269785</v>
       </c>
       <c r="E20" t="n">
-        <v>0.8204999903682619</v>
+        <v>0.4279999993741512</v>
       </c>
       <c r="F20" t="n">
-        <v>0.2727000101003796</v>
+        <v>0.1743339817039669</v>
       </c>
       <c r="G20" t="n">
-        <v>7.290600013220683</v>
+        <v>4.948999994667247</v>
       </c>
       <c r="H20" t="n">
-        <v>3.562699988833629</v>
+        <v>2.034709003055468</v>
       </c>
       <c r="I20" t="n">
-        <v>0.588800001423806</v>
+        <v>0.3928329970221967</v>
       </c>
       <c r="J20" t="n">
-        <v>30.59270000085235</v>
+        <v>21.07479202095419</v>
       </c>
       <c r="K20" t="n">
-        <v>13.17190000554547</v>
+        <v>8.338083018315956</v>
       </c>
       <c r="L20" t="n">
-        <v>1.280900003621355</v>
+        <v>0.8122079889290035</v>
       </c>
     </row>
     <row r="21">
       <c r="A21" t="n">
-        <v>0.2496000088285655</v>
+        <v>0.146583013702184</v>
       </c>
       <c r="B21" t="n">
-        <v>0.1295999973081052</v>
+        <v>0.06654197932220995</v>
       </c>
       <c r="C21" t="n">
-        <v>0.09810000483412296</v>
+        <v>0.06062499596737325</v>
       </c>
       <c r="D21" t="n">
-        <v>1.711599994450808</v>
+        <v>1.087332988390699</v>
       </c>
       <c r="E21" t="n">
-        <v>0.8157999982358888</v>
+        <v>0.4652500210795552</v>
       </c>
       <c r="F21" t="n">
-        <v>0.2749999985098839</v>
+        <v>0.1751249947119504</v>
       </c>
       <c r="G21" t="n">
-        <v>7.168099997215904</v>
+        <v>4.943416977766901</v>
       </c>
       <c r="H21" t="n">
-        <v>3.47880000481382</v>
+        <v>2.039290993707255</v>
       </c>
       <c r="I21" t="n">
-        <v>0.6104000058257952</v>
+        <v>0.4072499868925661</v>
       </c>
       <c r="J21" t="n">
-        <v>30.10839999478776</v>
+        <v>21.39312500366941</v>
       </c>
       <c r="K21" t="n">
-        <v>13.53699999162927</v>
+        <v>8.488332998240367</v>
       </c>
       <c r="L21" t="n">
-        <v>1.286600003368221</v>
+        <v>0.8135419921018183</v>
       </c>
     </row>
     <row r="22">
       <c r="A22" t="n">
-        <v>0.323900007060729</v>
+        <v>0.1825420185923576</v>
       </c>
       <c r="B22" t="n">
-        <v>0.1331000094069168</v>
+        <v>0.07104198448359966</v>
       </c>
       <c r="C22" t="n">
-        <v>0.1067999983206391</v>
+        <v>0.07120799273252487</v>
       </c>
       <c r="D22" t="n">
-        <v>1.517800003057346</v>
+        <v>0.9375840018037707</v>
       </c>
       <c r="E22" t="n">
-        <v>0.6851000071037561</v>
+        <v>0.3982500056736171</v>
       </c>
       <c r="F22" t="n">
-        <v>0.2766999969026074</v>
+        <v>0.1679160050116479</v>
       </c>
       <c r="G22" t="n">
-        <v>6.965400010813028</v>
+        <v>4.553250008029863</v>
       </c>
       <c r="H22" t="n">
-        <v>3.10469999385532</v>
+        <v>1.835209026467055</v>
       </c>
       <c r="I22" t="n">
-        <v>0.5913999921176583</v>
+        <v>0.3935830027330667</v>
       </c>
       <c r="J22" t="n">
-        <v>30.37870000116527</v>
+        <v>21.26420897548087</v>
       </c>
       <c r="K22" t="n">
-        <v>13.78409999597352</v>
+        <v>8.572749997256324</v>
       </c>
       <c r="L22" t="n">
-        <v>1.292799992370419</v>
+        <v>0.8122920116875321</v>
       </c>
     </row>
     <row r="23">
       <c r="A23" t="n">
-        <v>0.2810000005410984</v>
+        <v>0.1747919886838645</v>
       </c>
       <c r="B23" t="n">
-        <v>0.1687000039964914</v>
+        <v>0.07237499812617898</v>
       </c>
       <c r="C23" t="n">
-        <v>0.1367000077152625</v>
+        <v>0.06191700231283903</v>
       </c>
       <c r="D23" t="n">
-        <v>1.913400003104471</v>
+        <v>1.018624985590577</v>
       </c>
       <c r="E23" t="n">
-        <v>0.8591999940108508</v>
+        <v>0.4345829947851598</v>
       </c>
       <c r="F23" t="n">
-        <v>0.275399987003766</v>
+        <v>0.1702500157989562</v>
       </c>
       <c r="G23" t="n">
-        <v>7.248199995956384</v>
+        <v>4.758124996442348</v>
       </c>
       <c r="H23" t="n">
-        <v>3.454300007433631</v>
+        <v>2.025750000029802</v>
       </c>
       <c r="I23" t="n">
-        <v>0.596500001847744</v>
+        <v>0.3624160017352551</v>
       </c>
       <c r="J23" t="n">
-        <v>30.718900001375</v>
+        <v>21.27708299667574</v>
       </c>
       <c r="K23" t="n">
-        <v>13.80280000739731</v>
+        <v>8.585291972849518</v>
       </c>
       <c r="L23" t="n">
-        <v>1.309399987803772</v>
+        <v>0.8178749994840473</v>
       </c>
     </row>
     <row r="24">
       <c r="A24" t="n">
-        <v>0.2783999952953309</v>
+        <v>0.1637079985812306</v>
       </c>
       <c r="B24" t="n">
-        <v>0.1365999924018979</v>
+        <v>0.06733302143402398</v>
       </c>
       <c r="C24" t="n">
-        <v>0.1000999909592792</v>
+        <v>0.07429198012687266</v>
       </c>
       <c r="D24" t="n">
-        <v>1.675899999099784</v>
+        <v>1.168582995887846</v>
       </c>
       <c r="E24" t="n">
-        <v>0.8350999996764585</v>
+        <v>0.4153329937253147</v>
       </c>
       <c r="F24" t="n">
-        <v>0.2733000001171604</v>
+        <v>0.167207996128127</v>
       </c>
       <c r="G24" t="n">
-        <v>7.346300000790507</v>
+        <v>4.799041984369978</v>
       </c>
       <c r="H24" t="n">
-        <v>3.321199998026714</v>
+        <v>1.963624992640689</v>
       </c>
       <c r="I24" t="n">
-        <v>0.6031999946571887</v>
+        <v>0.3706660063471645</v>
       </c>
       <c r="J24" t="n">
-        <v>30.78329999698326</v>
+        <v>21.3946670119185</v>
       </c>
       <c r="K24" t="n">
-        <v>14.06069999211468</v>
+        <v>8.792082982836291</v>
       </c>
       <c r="L24" t="n">
-        <v>1.279200005228631</v>
+        <v>0.8047080191317946</v>
       </c>
     </row>
     <row r="25">
       <c r="A25" t="n">
-        <v>0.2539999986765906</v>
+        <v>0.1473749871365726</v>
       </c>
       <c r="B25" t="n">
-        <v>0.1316999987466261</v>
+        <v>0.064416992245242</v>
       </c>
       <c r="C25" t="n">
-        <v>0.09760000102687627</v>
+        <v>0.06016701809130609</v>
       </c>
       <c r="D25" t="n">
-        <v>1.725599999190308</v>
+        <v>1.036375004332513</v>
       </c>
       <c r="E25" t="n">
-        <v>0.8414000039920211</v>
+        <v>0.4366659850347787</v>
       </c>
       <c r="F25" t="n">
-        <v>0.2723999932641163</v>
+        <v>0.1756669953465462</v>
       </c>
       <c r="G25" t="n">
-        <v>7.192000004579313</v>
+        <v>4.752792010549456</v>
       </c>
       <c r="H25" t="n">
-        <v>3.291300003184006</v>
+        <v>2.011333999689668</v>
       </c>
       <c r="I25" t="n">
-        <v>0.5987999902572483</v>
+        <v>0.3720840031746775</v>
       </c>
       <c r="J25" t="n">
-        <v>30.9869000047911</v>
+        <v>21.34970799670555</v>
       </c>
       <c r="K25" t="n">
-        <v>13.89370000106283</v>
+        <v>8.710624999366701</v>
       </c>
       <c r="L25" t="n">
-        <v>1.297599999816157</v>
+        <v>0.8226670033764094</v>
       </c>
     </row>
     <row r="26">
       <c r="A26" t="n">
-        <v>0.2701000048546121</v>
+        <v>0.1600420218892395</v>
       </c>
       <c r="B26" t="n">
-        <v>0.1403000060236081</v>
+        <v>0.06816600216552615</v>
       </c>
       <c r="C26" t="n">
-        <v>0.0985000078799203</v>
+        <v>0.06029201904311776</v>
       </c>
       <c r="D26" t="n">
-        <v>1.640000002225861</v>
+        <v>0.9989159880205989</v>
       </c>
       <c r="E26" t="n">
-        <v>0.8379000064451247</v>
+        <v>0.4177920054644346</v>
       </c>
       <c r="F26" t="n">
-        <v>0.2727999963099137</v>
+        <v>0.1704170135781169</v>
       </c>
       <c r="G26" t="n">
-        <v>7.219700011773966</v>
+        <v>4.804333002539352</v>
       </c>
       <c r="H26" t="n">
-        <v>3.300600001239218</v>
+        <v>1.877624978078529</v>
       </c>
       <c r="I26" t="n">
-        <v>0.5960999988019466</v>
+        <v>0.3736669896170497</v>
       </c>
       <c r="J26" t="n">
-        <v>30.88320000097156</v>
+        <v>21.26450001378544</v>
       </c>
       <c r="K26" t="n">
-        <v>13.83359999454115</v>
+        <v>8.661917003337294</v>
       </c>
       <c r="L26" t="n">
-        <v>1.300799995078705</v>
+        <v>0.795583997387439</v>
       </c>
     </row>
     <row r="27">
       <c r="A27" t="n">
-        <v>0.2742999931797385</v>
+        <v>0.1582499826326966</v>
       </c>
       <c r="B27" t="n">
-        <v>0.146100006531924</v>
+        <v>0.07345800986513495</v>
       </c>
       <c r="C27" t="n">
-        <v>0.09800000407267362</v>
+        <v>0.06079100421629846</v>
       </c>
       <c r="D27" t="n">
-        <v>1.766599991242401</v>
+        <v>1.085583004169166</v>
       </c>
       <c r="E27" t="n">
-        <v>0.8990999922389165</v>
+        <v>0.4594170022755861</v>
       </c>
       <c r="F27" t="n">
-        <v>0.272899997071363</v>
+        <v>0.1758339931257069</v>
       </c>
       <c r="G27" t="n">
-        <v>7.105700002284721</v>
+        <v>4.691000009188429</v>
       </c>
       <c r="H27" t="n">
-        <v>3.164499998092651</v>
+        <v>1.878874987596646</v>
       </c>
       <c r="I27" t="n">
-        <v>0.6020000000717118</v>
+        <v>0.3623749944381416</v>
       </c>
       <c r="J27" t="n">
-        <v>32.32879999268334</v>
+        <v>21.50916701066308</v>
       </c>
       <c r="K27" t="n">
-        <v>14.07819999440107</v>
+        <v>8.880292007233948</v>
       </c>
       <c r="L27" t="n">
-        <v>1.425099995685741</v>
+        <v>0.7916250033304095</v>
       </c>
     </row>
     <row r="28">
       <c r="A28" t="n">
-        <v>0.2775000029942021</v>
+        <v>0.1619580143596977</v>
       </c>
       <c r="B28" t="n">
-        <v>0.1442999928258359</v>
+        <v>0.06983400089666247</v>
       </c>
       <c r="C28" t="n">
-        <v>0.09869999485090375</v>
+        <v>0.0601659994572401</v>
       </c>
       <c r="D28" t="n">
-        <v>1.648100005695596</v>
+        <v>0.9919580188579857</v>
       </c>
       <c r="E28" t="n">
-        <v>0.8206000056816265</v>
+        <v>0.5629169754683971</v>
       </c>
       <c r="F28" t="n">
-        <v>0.2707999956328422</v>
+        <v>0.1754169934429228</v>
       </c>
       <c r="G28" t="n">
-        <v>7.218700004159473</v>
+        <v>4.737499984912574</v>
       </c>
       <c r="H28" t="n">
-        <v>3.305699996417388</v>
+        <v>2.016416983678937</v>
       </c>
       <c r="I28" t="n">
-        <v>0.596199999563396</v>
+        <v>0.3989170072600245</v>
       </c>
       <c r="J28" t="n">
-        <v>30.12959999614395</v>
+        <v>21.01879200199619</v>
       </c>
       <c r="K28" t="n">
-        <v>13.19529999454971</v>
+        <v>8.230750012444332</v>
       </c>
       <c r="L28" t="n">
-        <v>1.687899988610297</v>
+        <v>0.8173749956768006</v>
       </c>
     </row>
     <row r="29">
       <c r="A29" t="n">
-        <v>0.2657000004546717</v>
+        <v>0.1501670049037784</v>
       </c>
       <c r="B29" t="n">
-        <v>0.149200001033023</v>
+        <v>0.07208299939520657</v>
       </c>
       <c r="C29" t="n">
-        <v>0.09750000026542693</v>
+        <v>0.07233300129882991</v>
       </c>
       <c r="D29" t="n">
-        <v>1.694899998256005</v>
+        <v>1.034417015034705</v>
       </c>
       <c r="E29" t="n">
-        <v>0.8214000117732212</v>
+        <v>0.4293749807402492</v>
       </c>
       <c r="F29" t="n">
-        <v>0.2693999995244667</v>
+        <v>0.1715420221444219</v>
       </c>
       <c r="G29" t="n">
-        <v>7.173900012276135</v>
+        <v>4.758458002470434</v>
       </c>
       <c r="H29" t="n">
-        <v>3.282099991338328</v>
+        <v>1.914082997245714</v>
       </c>
       <c r="I29" t="n">
-        <v>0.5966000026091933</v>
+        <v>0.3649999853223562</v>
       </c>
       <c r="J29" t="n">
-        <v>30.75400000670925</v>
+        <v>21.4371669862885</v>
       </c>
       <c r="K29" t="n">
-        <v>14.18119999289047</v>
+        <v>8.774957997957245</v>
       </c>
       <c r="L29" t="n">
-        <v>1.286700004129671</v>
+        <v>0.8150420035235584</v>
       </c>
     </row>
     <row r="30">
       <c r="A30" t="n">
-        <v>0.2807999990181997</v>
+        <v>0.1543330145068467</v>
       </c>
       <c r="B30" t="n">
-        <v>0.1309999934164807</v>
+        <v>0.06287501309998333</v>
       </c>
       <c r="C30" t="n">
-        <v>0.09990000398829579</v>
+        <v>0.06099999882280827</v>
       </c>
       <c r="D30" t="n">
-        <v>1.702599998679943</v>
+        <v>1.06412501190789</v>
       </c>
       <c r="E30" t="n">
-        <v>0.8421000093221664</v>
+        <v>0.4490419814828783</v>
       </c>
       <c r="F30" t="n">
-        <v>0.2739000046858564</v>
+        <v>0.1744159962981939</v>
       </c>
       <c r="G30" t="n">
-        <v>6.993999995756894</v>
+        <v>4.687625012593344</v>
       </c>
       <c r="H30" t="n">
-        <v>3.349500009790063</v>
+        <v>1.977792009711266</v>
       </c>
       <c r="I30" t="n">
-        <v>0.5953999934718013</v>
+        <v>0.382583006285131</v>
       </c>
       <c r="J30" t="n">
-        <v>30.39980000176001</v>
+        <v>21.09062499948777</v>
       </c>
       <c r="K30" t="n">
-        <v>13.88900000893045</v>
+        <v>8.476000017253682</v>
       </c>
       <c r="L30" t="n">
-        <v>1.282700002775528</v>
+        <v>0.8124579908326268</v>
       </c>
     </row>
     <row r="31">
       <c r="A31" t="n">
-        <v>0.2862999972421676</v>
+        <v>0.1641660055611283</v>
       </c>
       <c r="B31" t="n">
-        <v>0.1545999984955415</v>
+        <v>0.07425001240335405</v>
       </c>
       <c r="C31" t="n">
-        <v>0.1001000055111945</v>
+        <v>0.06045799818821251</v>
       </c>
       <c r="D31" t="n">
-        <v>1.728500006720424</v>
+        <v>1.013916975352913</v>
       </c>
       <c r="E31" t="n">
-        <v>0.8492999913869426</v>
+        <v>0.4583749978337437</v>
       </c>
       <c r="F31" t="n">
-        <v>0.2752000000327826</v>
+        <v>0.220083020394668</v>
       </c>
       <c r="G31" t="n">
-        <v>7.414899999275804</v>
+        <v>4.800541995791718</v>
       </c>
       <c r="H31" t="n">
-        <v>3.393499995581806</v>
+        <v>2.003000001423061</v>
       </c>
       <c r="I31" t="n">
-        <v>0.5898999952478334</v>
+        <v>0.36916698445566</v>
       </c>
       <c r="J31" t="n">
-        <v>31.02349999244325</v>
+        <v>21.37483301339671</v>
       </c>
       <c r="K31" t="n">
-        <v>14.25900000322144</v>
+        <v>8.639750012662262</v>
       </c>
       <c r="L31" t="n">
-        <v>1.270599997951649</v>
+        <v>0.8094169897958636</v>
       </c>
     </row>
     <row r="32">
       <c r="A32" t="n">
-        <v>0.3005000035045668</v>
+        <v>0.2000000094994903</v>
       </c>
       <c r="B32" t="n">
-        <v>0.1981999957934022</v>
+        <v>0.08754100417718291</v>
       </c>
       <c r="C32" t="n">
-        <v>0.123999998322688</v>
+        <v>0.0712089822627604</v>
       </c>
       <c r="D32" t="n">
-        <v>1.67130000772886</v>
+        <v>1.009083003737032</v>
       </c>
       <c r="E32" t="n">
-        <v>0.890900002559647</v>
+        <v>0.4508339916355908</v>
       </c>
       <c r="F32" t="n">
-        <v>0.272599994787015</v>
+        <v>0.1881670032162219</v>
       </c>
       <c r="G32" t="n">
-        <v>6.730000008246861</v>
+        <v>4.561708017718047</v>
       </c>
       <c r="H32" t="n">
-        <v>3.254700000979938</v>
+        <v>2.006416994845495</v>
       </c>
       <c r="I32" t="n">
-        <v>0.5895999929634854</v>
+        <v>0.3604580124374479</v>
       </c>
       <c r="J32" t="n">
-        <v>30.46170000743587</v>
+        <v>21.28745798836462</v>
       </c>
       <c r="K32" t="n">
-        <v>13.69210000848398</v>
+        <v>8.65629201871343</v>
       </c>
       <c r="L32" t="n">
-        <v>1.287599996430799</v>
+        <v>0.8774579910095781</v>
       </c>
     </row>
     <row r="33">
       <c r="A33" t="n">
-        <v>0.2573999954620376</v>
+        <v>0.1732079836074263</v>
       </c>
       <c r="B33" t="n">
-        <v>0.1307000056840479</v>
+        <v>0.06975000724196434</v>
       </c>
       <c r="C33" t="n">
-        <v>0.1029999984893948</v>
+        <v>0.06395799573510885</v>
       </c>
       <c r="D33" t="n">
-        <v>1.735500001814216</v>
+        <v>1.03870898601599</v>
       </c>
       <c r="E33" t="n">
-        <v>0.7888999971328303</v>
+        <v>0.4175000067334622</v>
       </c>
       <c r="F33" t="n">
-        <v>0.2820000081555918</v>
+        <v>0.1741249870974571</v>
       </c>
       <c r="G33" t="n">
-        <v>7.272800008649938</v>
+        <v>4.814458981854841</v>
       </c>
       <c r="H33" t="n">
-        <v>3.456499995081685</v>
+        <v>1.964791998034343</v>
       </c>
       <c r="I33" t="n">
-        <v>0.5975999956717715</v>
+        <v>0.3821669961325824</v>
       </c>
       <c r="J33" t="n">
-        <v>30.48159999889322</v>
+        <v>20.93054199940525</v>
       </c>
       <c r="K33" t="n">
-        <v>13.35280000057537</v>
+        <v>8.296416024677455</v>
       </c>
       <c r="L33" t="n">
-        <v>1.42460000643041</v>
+        <v>0.8134579984471202</v>
       </c>
     </row>
     <row r="34">
       <c r="A34" t="n">
-        <v>0.2613000106066465</v>
+        <v>0.1753749966155738</v>
       </c>
       <c r="B34" t="n">
-        <v>0.1382999907946214</v>
+        <v>0.1013749861158431</v>
       </c>
       <c r="C34" t="n">
-        <v>0.09719999798107892</v>
+        <v>0.07124998955987394</v>
       </c>
       <c r="D34" t="n">
-        <v>1.686300005530939</v>
+        <v>1.073041989002377</v>
       </c>
       <c r="E34" t="n">
-        <v>0.8212999964598566</v>
+        <v>0.4604159912560135</v>
       </c>
       <c r="F34" t="n">
-        <v>0.2726000093389302</v>
+        <v>0.1734170073177665</v>
       </c>
       <c r="G34" t="n">
-        <v>7.52430000284221</v>
+        <v>4.963582992786542</v>
       </c>
       <c r="H34" t="n">
-        <v>3.687899996293709</v>
+        <v>2.19537498196587</v>
       </c>
       <c r="I34" t="n">
-        <v>0.606099987635389</v>
+        <v>0.3778750251512975</v>
       </c>
       <c r="J34" t="n">
-        <v>30.82529999664985</v>
+        <v>21.23087499057874</v>
       </c>
       <c r="K34" t="n">
-        <v>13.77199999114964</v>
+        <v>8.616209001047537</v>
       </c>
       <c r="L34" t="n">
-        <v>1.283699995838106</v>
+        <v>0.8131670183502138</v>
       </c>
     </row>
     <row r="35">
       <c r="A35" t="n">
-        <v>0.335300006554462</v>
+        <v>0.200875016162172</v>
       </c>
       <c r="B35" t="n">
-        <v>0.1477000041631982</v>
+        <v>0.0834170205052942</v>
       </c>
       <c r="C35" t="n">
-        <v>0.1003000070340931</v>
+        <v>0.08141697617247701</v>
       </c>
       <c r="D35" t="n">
-        <v>1.626299999770708</v>
+        <v>1.015957997879013</v>
       </c>
       <c r="E35" t="n">
-        <v>0.8000999951036647</v>
+        <v>0.3986250085290521</v>
       </c>
       <c r="F35" t="n">
-        <v>0.275699989288114</v>
+        <v>0.1999590022023767</v>
       </c>
       <c r="G35" t="n">
-        <v>7.494699995731935</v>
+        <v>4.987833002815023</v>
       </c>
       <c r="H35" t="n">
-        <v>3.698699991218746</v>
+        <v>2.050209004664794</v>
       </c>
       <c r="I35" t="n">
-        <v>0.5930000043008476</v>
+        <v>0.385874998755753</v>
       </c>
       <c r="J35" t="n">
-        <v>29.71139999863226</v>
+        <v>20.78245897428133</v>
       </c>
       <c r="K35" t="n">
-        <v>13.03380000172183</v>
+        <v>7.943584001623094</v>
       </c>
       <c r="L35" t="n">
-        <v>1.282000011997297</v>
+        <v>0.8287910022772849</v>
       </c>
     </row>
     <row r="36">
       <c r="A36" t="n">
-        <v>0.2623999898787588</v>
+        <v>0.1589579915162176</v>
       </c>
       <c r="B36" t="n">
-        <v>0.1607000012882054</v>
+        <v>0.07179100066423416</v>
       </c>
       <c r="C36" t="n">
-        <v>0.1214999938383698</v>
+        <v>0.06395799573510885</v>
       </c>
       <c r="D36" t="n">
-        <v>1.556100003654137</v>
+        <v>0.9777089871931821</v>
       </c>
       <c r="E36" t="n">
-        <v>0.7498999912058935</v>
+        <v>0.3982920025009662</v>
       </c>
       <c r="F36" t="n">
-        <v>0.2708999963942915</v>
+        <v>0.1777500146999955</v>
       </c>
       <c r="G36" t="n">
-        <v>6.941699990420602</v>
+        <v>4.540624999208376</v>
       </c>
       <c r="H36" t="n">
-        <v>3.198499995050952</v>
+        <v>1.87908299267292</v>
       </c>
       <c r="I36" t="n">
-        <v>0.593100005062297</v>
+        <v>0.371375004760921</v>
       </c>
       <c r="J36" t="n">
-        <v>31.21020000253338</v>
+        <v>21.2922090140637</v>
       </c>
       <c r="K36" t="n">
-        <v>13.60249999561347</v>
+        <v>8.526958990842104</v>
       </c>
       <c r="L36" t="n">
-        <v>1.27789999532979</v>
+        <v>0.8191670058295131</v>
       </c>
     </row>
     <row r="37">
       <c r="A37" t="n">
-        <v>0.2417999930912629</v>
+        <v>0.1428750110790133</v>
       </c>
       <c r="B37" t="n">
-        <v>0.1200999977299944</v>
+        <v>0.06279099034145474</v>
       </c>
       <c r="C37" t="n">
-        <v>0.09619999036658555</v>
+        <v>0.06041600136086345</v>
       </c>
       <c r="D37" t="n">
-        <v>1.668400000198744</v>
+        <v>1.112541009206325</v>
       </c>
       <c r="E37" t="n">
-        <v>0.8354000019608065</v>
+        <v>0.4913330194540322</v>
       </c>
       <c r="F37" t="n">
-        <v>0.2763999946182594</v>
+        <v>0.1998749794438481</v>
       </c>
       <c r="G37" t="n">
-        <v>6.785799996578135</v>
+        <v>4.463666991796345</v>
       </c>
       <c r="H37" t="n">
-        <v>3.102299990132451</v>
+        <v>1.861041993834078</v>
       </c>
       <c r="I37" t="n">
-        <v>0.6004999886499718</v>
+        <v>0.3761659900192171</v>
       </c>
       <c r="J37" t="n">
-        <v>31.31900000153109</v>
+        <v>21.38695798930712</v>
       </c>
       <c r="K37" t="n">
-        <v>13.88749999750871</v>
+        <v>8.756583003560081</v>
       </c>
       <c r="L37" t="n">
-        <v>1.303199998801574</v>
+        <v>0.8160000143107027</v>
       </c>
     </row>
     <row r="38">
       <c r="A38" t="n">
-        <v>0.2687999949557707</v>
+        <v>0.1559589873068035</v>
       </c>
       <c r="B38" t="n">
-        <v>0.1430999982403591</v>
+        <v>0.07466599345207214</v>
       </c>
       <c r="C38" t="n">
-        <v>0.09780000254977494</v>
+        <v>0.06091699469834566</v>
       </c>
       <c r="D38" t="n">
-        <v>1.749300005030818</v>
+        <v>1.042666990542784</v>
       </c>
       <c r="E38" t="n">
-        <v>0.8722000056877732</v>
+        <v>0.4483750090003014</v>
       </c>
       <c r="F38" t="n">
-        <v>0.2730999985942617</v>
+        <v>0.1880839990917593</v>
       </c>
       <c r="G38" t="n">
-        <v>7.158599997637793</v>
+        <v>4.719624994322658</v>
       </c>
       <c r="H38" t="n">
-        <v>3.262400001403876</v>
+        <v>1.972458005184308</v>
       </c>
       <c r="I38" t="n">
-        <v>0.5862999969394878</v>
+        <v>0.3911250096280128</v>
       </c>
       <c r="J38" t="n">
-        <v>30.92600000672974</v>
+        <v>21.14787499886006</v>
       </c>
       <c r="K38" t="n">
-        <v>13.65799999621231</v>
+        <v>8.522457996150479</v>
       </c>
       <c r="L38" t="n">
-        <v>1.295500012929551</v>
+        <v>0.8094590157270432</v>
       </c>
     </row>
     <row r="39">
       <c r="A39" t="n">
-        <v>0.2657000004546717</v>
+        <v>0.1549589796923101</v>
       </c>
       <c r="B39" t="n">
-        <v>0.1210000045830384</v>
+        <v>0.06345799192786217</v>
       </c>
       <c r="C39" t="n">
-        <v>0.1014000008581206</v>
+        <v>0.05891700857318938</v>
       </c>
       <c r="D39" t="n">
-        <v>1.7268000083277</v>
+        <v>1.044459000695497</v>
       </c>
       <c r="E39" t="n">
-        <v>0.8202000026358292</v>
+        <v>0.4177920054644346</v>
       </c>
       <c r="F39" t="n">
-        <v>0.2763000084087253</v>
+        <v>0.1905840181279927</v>
       </c>
       <c r="G39" t="n">
-        <v>7.142600006773137</v>
+        <v>4.661082988604903</v>
       </c>
       <c r="H39" t="n">
-        <v>3.281599987531081</v>
+        <v>1.89516699174419</v>
       </c>
       <c r="I39" t="n">
-        <v>0.6111999973654747</v>
+        <v>0.3752909833565354</v>
       </c>
       <c r="J39" t="n">
-        <v>30.49570000439417</v>
+        <v>20.72804101044312</v>
       </c>
       <c r="K39" t="n">
-        <v>13.39870000083465</v>
+        <v>8.388667018152773</v>
       </c>
       <c r="L39" t="n">
-        <v>1.283600009628572</v>
+        <v>0.8102919964585453</v>
       </c>
     </row>
     <row r="40">
       <c r="A40" t="n">
-        <v>0.2724999940255657</v>
+        <v>0.1637910027056932</v>
       </c>
       <c r="B40" t="n">
-        <v>0.1460000057704747</v>
+        <v>0.07766700582578778</v>
       </c>
       <c r="C40" t="n">
-        <v>0.1000999909592792</v>
+        <v>0.06095797289162874</v>
       </c>
       <c r="D40" t="n">
-        <v>1.735099998768419</v>
+        <v>1.04750000173226</v>
       </c>
       <c r="E40" t="n">
-        <v>0.9188999974867329</v>
+        <v>0.5475410143844783</v>
       </c>
       <c r="F40" t="n">
-        <v>0.2775000029942021</v>
+        <v>0.1835419971030205</v>
       </c>
       <c r="G40" t="n">
-        <v>7.397699999273755</v>
+        <v>4.809375008335337</v>
       </c>
       <c r="H40" t="n">
-        <v>3.559300006600097</v>
+        <v>2.050917013548315</v>
       </c>
       <c r="I40" t="n">
-        <v>0.5945000011706725</v>
+        <v>0.4001250199507922</v>
       </c>
       <c r="J40" t="n">
-        <v>31.29269999044482</v>
+        <v>21.64908300619572</v>
       </c>
       <c r="K40" t="n">
-        <v>14.25959999323823</v>
+        <v>8.905917027732357</v>
       </c>
       <c r="L40" t="n">
-        <v>1.29190000006929</v>
+        <v>0.8132079965434968</v>
       </c>
     </row>
     <row r="41">
       <c r="A41" t="n">
-        <v>0.258700005360879</v>
+        <v>0.1558329968247563</v>
       </c>
       <c r="B41" t="n">
-        <v>0.1232999929925427</v>
+        <v>0.06466699414886534</v>
       </c>
       <c r="C41" t="n">
-        <v>0.09760000102687627</v>
+        <v>0.05966599564999342</v>
       </c>
       <c r="D41" t="n">
-        <v>1.675100007560104</v>
+        <v>0.9883750171866268</v>
       </c>
       <c r="E41" t="n">
-        <v>0.7762999885017052</v>
+        <v>0.3937500005122274</v>
       </c>
       <c r="F41" t="n">
-        <v>0.2687999949557707</v>
+        <v>0.185707991477102</v>
       </c>
       <c r="G41" t="n">
-        <v>7.220399988000281</v>
+        <v>4.691083013312891</v>
       </c>
       <c r="H41" t="n">
-        <v>3.223399995476939</v>
+        <v>1.882999989902601</v>
       </c>
       <c r="I41" t="n">
-        <v>0.5930000043008476</v>
+        <v>0.3796250093728304</v>
       </c>
       <c r="J41" t="n">
-        <v>30.98060000047553</v>
+        <v>21.51858399156481</v>
       </c>
       <c r="K41" t="n">
-        <v>14.00070000090636</v>
+        <v>8.755958027904853</v>
       </c>
       <c r="L41" t="n">
-        <v>1.303299999563023</v>
+        <v>0.8098329999484122</v>
       </c>
     </row>
     <row r="42">
       <c r="A42" t="n">
-        <v>0.2927000023191795</v>
+        <v>0.186792021850124</v>
       </c>
       <c r="B42" t="n">
-        <v>0.155999994603917</v>
+        <v>0.09787498856894672</v>
       </c>
       <c r="C42" t="n">
-        <v>0.1008999970508739</v>
+        <v>0.06812499486841261</v>
       </c>
       <c r="D42" t="n">
-        <v>1.728999995975755</v>
+        <v>1.021833013510332</v>
       </c>
       <c r="E42" t="n">
-        <v>0.8343999943463132</v>
+        <v>0.4482909862417728</v>
       </c>
       <c r="F42" t="n">
-        <v>0.3460000007180497</v>
+        <v>0.1923340023495257</v>
       </c>
       <c r="G42" t="n">
-        <v>7.197799990535714</v>
+        <v>4.764750017784536</v>
       </c>
       <c r="H42" t="n">
-        <v>3.292400011559948</v>
+        <v>1.94470799760893</v>
       </c>
       <c r="I42" t="n">
-        <v>0.6031000084476545</v>
+        <v>0.3707910072989762</v>
       </c>
       <c r="J42" t="n">
-        <v>29.97439999307971</v>
+        <v>21.15566699649207</v>
       </c>
       <c r="K42" t="n">
-        <v>13.71839999046642</v>
+        <v>8.538249996490777</v>
       </c>
       <c r="L42" t="n">
-        <v>1.334300002781674</v>
+        <v>0.8134579984471202</v>
       </c>
     </row>
     <row r="43">
       <c r="A43" t="n">
-        <v>0.2812999882735312</v>
+        <v>0.1570419990457594</v>
       </c>
       <c r="B43" t="n">
-        <v>0.1456999889342114</v>
+        <v>0.07062498480081558</v>
       </c>
       <c r="C43" t="n">
-        <v>0.1259999989997596</v>
+        <v>0.06087499787099659</v>
       </c>
       <c r="D43" t="n">
-        <v>1.746399997500703</v>
+        <v>1.019332994474098</v>
       </c>
       <c r="E43" t="n">
-        <v>0.8738999895285815</v>
+        <v>0.4895830061286688</v>
       </c>
       <c r="F43" t="n">
-        <v>0.2787999983411282</v>
+        <v>0.1856249873526394</v>
       </c>
       <c r="G43" t="n">
-        <v>7.005199993727729</v>
+        <v>4.653167008655146</v>
       </c>
       <c r="H43" t="n">
-        <v>3.161900007398799</v>
+        <v>1.795541000319645</v>
       </c>
       <c r="I43" t="n">
-        <v>0.5938999966019765</v>
+        <v>0.3755830111913383</v>
       </c>
       <c r="J43" t="n">
-        <v>30.03629999875557</v>
+        <v>21.49579199613072</v>
       </c>
       <c r="K43" t="n">
-        <v>13.55479999620002</v>
+        <v>8.445167011814192</v>
       </c>
       <c r="L43" t="n">
-        <v>1.294999994570389</v>
+        <v>0.8132079965434968</v>
       </c>
     </row>
     <row r="44">
       <c r="A44" t="n">
-        <v>0.2730999985942617</v>
+        <v>0.1555419876240194</v>
       </c>
       <c r="B44" t="n">
-        <v>0.1466999965487048</v>
+        <v>0.07075001485645771</v>
       </c>
       <c r="C44" t="n">
-        <v>0.09960000170394778</v>
+        <v>0.06975000724196434</v>
       </c>
       <c r="D44" t="n">
-        <v>1.634100000956096</v>
+        <v>0.9502499888185412</v>
       </c>
       <c r="E44" t="n">
-        <v>0.826000003144145</v>
+        <v>0.401042023440823</v>
       </c>
       <c r="F44" t="n">
-        <v>0.2775000029942021</v>
+        <v>0.1685419993009418</v>
       </c>
       <c r="G44" t="n">
-        <v>7.156199993914925</v>
+        <v>4.751583997858688</v>
       </c>
       <c r="H44" t="n">
-        <v>3.28319999971427</v>
+        <v>1.900000002933666</v>
       </c>
       <c r="I44" t="n">
-        <v>0.6056999991415069</v>
+        <v>0.3695420164149255</v>
       </c>
       <c r="J44" t="n">
-        <v>30.50560000701807</v>
+        <v>20.97412501461804</v>
       </c>
       <c r="K44" t="n">
-        <v>13.49320000736043</v>
+        <v>8.338917017681524</v>
       </c>
       <c r="L44" t="n">
-        <v>1.313999993726611</v>
+        <v>0.8300420013256371</v>
       </c>
     </row>
     <row r="45">
       <c r="A45" t="n">
-        <v>0.2842999965650961</v>
+        <v>0.1598749950062484</v>
       </c>
       <c r="B45" t="n">
-        <v>0.1466999965487048</v>
+        <v>0.07324997568503022</v>
       </c>
       <c r="C45" t="n">
-        <v>0.1002000062726438</v>
+        <v>0.0602919899392873</v>
       </c>
       <c r="D45" t="n">
-        <v>1.785000000381842</v>
+        <v>1.065875025233254</v>
       </c>
       <c r="E45" t="n">
-        <v>0.8511000050930306</v>
+        <v>0.4420419863890857</v>
       </c>
       <c r="F45" t="n">
-        <v>0.2711999986786395</v>
+        <v>0.1720000000204891</v>
       </c>
       <c r="G45" t="n">
-        <v>7.279099998413585</v>
+        <v>4.869832977419719</v>
       </c>
       <c r="H45" t="n">
-        <v>3.579099997295998</v>
+        <v>2.086291002342477</v>
       </c>
       <c r="I45" t="n">
-        <v>0.5878999945707619</v>
+        <v>0.3609579871408641</v>
       </c>
       <c r="J45" t="n">
-        <v>30.77380001195706</v>
+        <v>21.56533399829641</v>
       </c>
       <c r="K45" t="n">
-        <v>14.24590000533499</v>
+        <v>8.868333999998868</v>
       </c>
       <c r="L45" t="n">
-        <v>1.292599990847521</v>
+        <v>0.8119579870253801</v>
       </c>
     </row>
     <row r="46">
       <c r="A46" t="n">
-        <v>0.2646999928401783</v>
+        <v>0.1509589783381671</v>
       </c>
       <c r="B46" t="n">
-        <v>0.1292999950237572</v>
+        <v>0.06433299859054387</v>
       </c>
       <c r="C46" t="n">
-        <v>0.09820000559557229</v>
+        <v>0.06058299914002419</v>
       </c>
       <c r="D46" t="n">
-        <v>1.723699999274686</v>
+        <v>1.02416702429764</v>
       </c>
       <c r="E46" t="n">
-        <v>0.77860000601504</v>
+        <v>0.4116670170333236</v>
       </c>
       <c r="F46" t="n">
-        <v>0.2749999985098839</v>
+        <v>0.1864999940153211</v>
       </c>
       <c r="G46" t="n">
-        <v>7.186400005593896</v>
+        <v>4.837874992517754</v>
       </c>
       <c r="H46" t="n">
-        <v>3.370199992787093</v>
+        <v>1.965041010407731</v>
       </c>
       <c r="I46" t="n">
-        <v>0.5967000033706427</v>
+        <v>0.3610829880926758</v>
       </c>
       <c r="J46" t="n">
-        <v>30.06279999681283</v>
+        <v>20.80866601318121</v>
       </c>
       <c r="K46" t="n">
-        <v>13.15830000385176</v>
+        <v>8.12483302433975</v>
       </c>
       <c r="L46" t="n">
-        <v>1.295999987632968</v>
+        <v>0.8274590072687715</v>
       </c>
     </row>
     <row r="47">
       <c r="A47" t="n">
-        <v>0.2968000044347718</v>
+        <v>0.1714169920887798</v>
       </c>
       <c r="B47" t="n">
-        <v>0.1566999999340624</v>
+        <v>0.07795798592269421</v>
       </c>
       <c r="C47" t="n">
-        <v>0.09869999485090375</v>
+        <v>0.06179101183079183</v>
       </c>
       <c r="D47" t="n">
-        <v>1.782799998181872</v>
+        <v>1.148500014096498</v>
       </c>
       <c r="E47" t="n">
-        <v>0.8898999949451536</v>
+        <v>0.4460829950403422</v>
       </c>
       <c r="F47" t="n">
-        <v>0.2690999972401187</v>
+        <v>0.1702919835224748</v>
       </c>
       <c r="G47" t="n">
-        <v>7.175699996878393</v>
+        <v>4.752332984935492</v>
       </c>
       <c r="H47" t="n">
-        <v>3.336800000397488</v>
+        <v>1.940540998475626</v>
       </c>
       <c r="I47" t="n">
-        <v>0.5960999988019466</v>
+        <v>0.3764170105569065</v>
       </c>
       <c r="J47" t="n">
-        <v>30.63360000669491</v>
+        <v>21.6793330037035</v>
       </c>
       <c r="K47" t="n">
-        <v>14.0910000045551</v>
+        <v>8.757750008953735</v>
       </c>
       <c r="L47" t="n">
-        <v>1.283799996599555</v>
+        <v>0.8198749856092036</v>
       </c>
     </row>
     <row r="48">
       <c r="A48" t="n">
-        <v>0.2746999962255359</v>
+        <v>0.1557499927002937</v>
       </c>
       <c r="B48" t="n">
-        <v>0.1313999964622781</v>
+        <v>0.06554200081154704</v>
       </c>
       <c r="C48" t="n">
-        <v>0.1008000108413398</v>
+        <v>0.06349998875521123</v>
       </c>
       <c r="D48" t="n">
-        <v>1.761699997587129</v>
+        <v>1.058666995959356</v>
       </c>
       <c r="E48" t="n">
-        <v>0.8463999984087422</v>
+        <v>0.4269999917596579</v>
       </c>
       <c r="F48" t="n">
-        <v>0.2681999903870746</v>
+        <v>0.167582998983562</v>
       </c>
       <c r="G48" t="n">
-        <v>6.84950000140816</v>
+        <v>4.536708991508931</v>
       </c>
       <c r="H48" t="n">
-        <v>3.222300001652911</v>
+        <v>1.923082978464663</v>
       </c>
       <c r="I48" t="n">
-        <v>0.5918000097153708</v>
+        <v>0.3856660041492432</v>
       </c>
       <c r="J48" t="n">
-        <v>30.71040000941139</v>
+        <v>21.30987498094328</v>
       </c>
       <c r="K48" t="n">
-        <v>13.74280000163708</v>
+        <v>8.549958991352469</v>
       </c>
       <c r="L48" t="n">
-        <v>1.27710000379011</v>
+        <v>0.808208977105096</v>
       </c>
     </row>
     <row r="49">
       <c r="A49" t="n">
-        <v>0.2616000128909945</v>
+        <v>0.1771670067682862</v>
       </c>
       <c r="B49" t="n">
-        <v>0.126799990539439</v>
+        <v>0.06299998494796455</v>
       </c>
       <c r="C49" t="n">
-        <v>0.09919999865815043</v>
+        <v>0.06162500358186662</v>
       </c>
       <c r="D49" t="n">
-        <v>1.68610000400804</v>
+        <v>0.9919589792843908</v>
       </c>
       <c r="E49" t="n">
-        <v>0.7976999913807958</v>
+        <v>0.410082982853055</v>
       </c>
       <c r="F49" t="n">
-        <v>0.2749999985098839</v>
+        <v>0.1686250034254044</v>
       </c>
       <c r="G49" t="n">
-        <v>6.989200002863072</v>
+        <v>4.597000021021813</v>
       </c>
       <c r="H49" t="n">
-        <v>3.120599998510443</v>
+        <v>1.813333015888929</v>
       </c>
       <c r="I49" t="n">
-        <v>0.5941999988863245</v>
+        <v>0.3635829780250788</v>
       </c>
       <c r="J49" t="n">
-        <v>30.45969999220688</v>
+        <v>21.16725000087172</v>
       </c>
       <c r="K49" t="n">
-        <v>13.70099998894148</v>
+        <v>8.423666004091501</v>
       </c>
       <c r="L49" t="n">
-        <v>1.288500003283843</v>
+        <v>0.822000001790002</v>
       </c>
     </row>
     <row r="50">
       <c r="A50" t="n">
-        <v>0.2741999924182892</v>
+        <v>0.1639169931877404</v>
       </c>
       <c r="B50" t="n">
-        <v>0.1320000010309741</v>
+        <v>0.06762499106116593</v>
       </c>
       <c r="C50" t="n">
-        <v>0.09760000102687627</v>
+        <v>0.06445799954235554</v>
       </c>
       <c r="D50" t="n">
-        <v>1.849699998274446</v>
+        <v>1.066500000888482</v>
       </c>
       <c r="E50" t="n">
-        <v>0.8975999953690916</v>
+        <v>0.4732089873868972</v>
       </c>
       <c r="F50" t="n">
-        <v>0.2786999975796789</v>
+        <v>0.1691670040600002</v>
       </c>
       <c r="G50" t="n">
-        <v>7.100300004822202</v>
+        <v>4.735999973490834</v>
       </c>
       <c r="H50" t="n">
-        <v>3.376599997864105</v>
+        <v>1.929917023517191</v>
       </c>
       <c r="I50" t="n">
-        <v>0.5907000013394281</v>
+        <v>0.3796249802689999</v>
       </c>
       <c r="J50" t="n">
-        <v>30.46110000286717</v>
+        <v>21.01095800753683</v>
       </c>
       <c r="K50" t="n">
-        <v>13.55410000542179</v>
+        <v>8.338667015777901</v>
       </c>
       <c r="L50" t="n">
-        <v>1.286700004129671</v>
+        <v>0.811875012004748</v>
       </c>
     </row>
     <row r="51">
       <c r="A51" t="n">
-        <v>0.2814000035868958</v>
+        <v>0.1912500010803342</v>
       </c>
       <c r="B51" t="n">
-        <v>0.1458999904571101</v>
+        <v>0.08437500218860805</v>
       </c>
       <c r="C51" t="n">
-        <v>0.09840000711847097</v>
+        <v>0.06429199129343033</v>
       </c>
       <c r="D51" t="n">
-        <v>1.754500000970438</v>
+        <v>1.036166999256238</v>
       </c>
       <c r="E51" t="n">
-        <v>0.8338999905390665</v>
+        <v>0.4182499833405018</v>
       </c>
       <c r="F51" t="n">
-        <v>0.2733000001171604</v>
+        <v>0.1681249996181577</v>
       </c>
       <c r="G51" t="n">
-        <v>6.971599999815226</v>
+        <v>4.601916996762156</v>
       </c>
       <c r="H51" t="n">
-        <v>3.215999997337349</v>
+        <v>1.892250002129003</v>
       </c>
       <c r="I51" t="n">
-        <v>0.5842999962624162</v>
+        <v>0.3614999877754599</v>
       </c>
       <c r="J51" t="n">
-        <v>30.38999999989755</v>
+        <v>21.24479197664186</v>
       </c>
       <c r="K51" t="n">
-        <v>13.77899998624343</v>
+        <v>8.557416993426159</v>
       </c>
       <c r="L51" t="n">
-        <v>1.282600002014078</v>
+        <v>0.8120419806800783</v>
       </c>
     </row>
     <row r="52">
       <c r="A52" t="n">
-        <v>0.2811000013025478</v>
+        <v>0.1957080094143748</v>
       </c>
       <c r="B52" t="n">
-        <v>0.1906999968923628</v>
+        <v>0.09116699220612645</v>
       </c>
       <c r="C52" t="n">
-        <v>0.1249999913852662</v>
+        <v>0.07016700692474842</v>
       </c>
       <c r="D52" t="n">
-        <v>1.725900001474656</v>
+        <v>1.045292010530829</v>
       </c>
       <c r="E52" t="n">
-        <v>0.7477000035578385</v>
+        <v>0.379000004613772</v>
       </c>
       <c r="F52" t="n">
-        <v>0.3020000003743917</v>
+        <v>0.1737919810693711</v>
       </c>
       <c r="G52" t="n">
-        <v>7.25679998868145</v>
+        <v>4.93487500352785</v>
       </c>
       <c r="H52" t="n">
-        <v>3.341400006320328</v>
+        <v>1.994458987610415</v>
       </c>
       <c r="I52" t="n">
-        <v>0.6209999992279336</v>
+        <v>0.4152090114075691</v>
       </c>
       <c r="J52" t="n">
-        <v>31.24509999179281</v>
+        <v>21.60537499003112</v>
       </c>
       <c r="K52" t="n">
-        <v>14.28990000567865</v>
+        <v>8.818708010949194</v>
       </c>
       <c r="L52" t="n">
-        <v>1.284199999645352</v>
+        <v>0.8114160154946148</v>
       </c>
     </row>
     <row r="53">
       <c r="A53" t="n">
-        <v>0.3042000025743619</v>
+        <v>0.149500003317371</v>
       </c>
       <c r="B53" t="n">
-        <v>0.1218999968841672</v>
+        <v>0.06262501119635999</v>
       </c>
       <c r="C53" t="n">
-        <v>0.1218000106746331</v>
+        <v>0.06037499406374991</v>
       </c>
       <c r="D53" t="n">
-        <v>1.619699993170798</v>
+        <v>1.042374991811812</v>
       </c>
       <c r="E53" t="n">
-        <v>0.7367999933194369</v>
+        <v>0.4131250025238842</v>
       </c>
       <c r="F53" t="n">
-        <v>0.2720000047702342</v>
+        <v>0.1693750091362745</v>
       </c>
       <c r="G53" t="n">
-        <v>7.221199994091876</v>
+        <v>4.952624993165955</v>
       </c>
       <c r="H53" t="n">
-        <v>3.528000001097098</v>
+        <v>2.050958981271833</v>
       </c>
       <c r="I53" t="n">
-        <v>0.5926000012550503</v>
+        <v>0.3628749982453883</v>
       </c>
       <c r="J53" t="n">
-        <v>30.92639999522362</v>
+        <v>21.36554100434296</v>
       </c>
       <c r="K53" t="n">
-        <v>14.15089999500196</v>
+        <v>8.59833398135379</v>
       </c>
       <c r="L53" t="n">
-        <v>1.277800009120256</v>
+        <v>0.81291698734276</v>
       </c>
     </row>
     <row r="54">
       <c r="A54" t="n">
-        <v>0.2516999957151711</v>
+        <v>0.1578329829499125</v>
       </c>
       <c r="B54" t="n">
-        <v>0.1205000007757917</v>
+        <v>0.06229200516827404</v>
       </c>
       <c r="C54" t="n">
-        <v>0.09719999798107892</v>
+        <v>0.06104199565015733</v>
       </c>
       <c r="D54" t="n">
-        <v>1.725200010696426</v>
+        <v>1.054082997143269</v>
       </c>
       <c r="E54" t="n">
-        <v>0.82230000407435</v>
+        <v>0.4210829793009907</v>
       </c>
       <c r="F54" t="n">
-        <v>0.2708999963942915</v>
+        <v>0.1682500005699694</v>
       </c>
       <c r="G54" t="n">
-        <v>7.104200005414896</v>
+        <v>4.677124990848824</v>
       </c>
       <c r="H54" t="n">
-        <v>3.247400003601797</v>
+        <v>1.926875003846362</v>
       </c>
       <c r="I54" t="n">
-        <v>0.59710000641644</v>
+        <v>0.383624981623143</v>
       </c>
       <c r="J54" t="n">
-        <v>31.09470001072623</v>
+        <v>21.2611670140177</v>
       </c>
       <c r="K54" t="n">
-        <v>13.81560000299942</v>
+        <v>8.522624993929639</v>
       </c>
       <c r="L54" t="n">
-        <v>1.284900004975498</v>
+        <v>0.7913339941296726</v>
       </c>
     </row>
     <row r="55">
       <c r="A55" t="n">
-        <v>0.2596999984234571</v>
+        <v>0.1545420091133565</v>
       </c>
       <c r="B55" t="n">
-        <v>0.1302000018768013</v>
+        <v>0.06712498725391924</v>
       </c>
       <c r="C55" t="n">
-        <v>0.09580000187270343</v>
+        <v>0.05987499025650322</v>
       </c>
       <c r="D55" t="n">
-        <v>1.744900000630878</v>
+        <v>1.049457991030067</v>
       </c>
       <c r="E55" t="n">
-        <v>0.8296000014524907</v>
+        <v>0.4325410118326545</v>
       </c>
       <c r="F55" t="n">
-        <v>0.2738999901339412</v>
+        <v>0.1742089807521552</v>
       </c>
       <c r="G55" t="n">
-        <v>7.29029999638442</v>
+        <v>4.740417003631592</v>
       </c>
       <c r="H55" t="n">
-        <v>3.401900001335889</v>
+        <v>1.927832985529676</v>
       </c>
       <c r="I55" t="n">
-        <v>0.5985999887343496</v>
+        <v>0.3708750009536743</v>
       </c>
       <c r="J55" t="n">
-        <v>30.26680000766646</v>
+        <v>21.04824999696575</v>
       </c>
       <c r="K55" t="n">
-        <v>13.26520000293385</v>
+        <v>8.415916992817074</v>
       </c>
       <c r="L55" t="n">
-        <v>1.29709999600891</v>
+        <v>0.8069589966908097</v>
       </c>
     </row>
     <row r="56">
       <c r="A56" t="n">
-        <v>0.2655999996932223</v>
+        <v>0.1730419753585011</v>
       </c>
       <c r="B56" t="n">
-        <v>0.1225000014528632</v>
+        <v>0.06258301436901093</v>
       </c>
       <c r="C56" t="n">
-        <v>0.09980000322684646</v>
+        <v>0.06704102270305157</v>
       </c>
       <c r="D56" t="n">
-        <v>1.741300002322532</v>
+        <v>1.034916000207886</v>
       </c>
       <c r="E56" t="n">
-        <v>0.8374000026378781</v>
+        <v>0.485416006995365</v>
       </c>
       <c r="F56" t="n">
-        <v>0.2730999985942617</v>
+        <v>0.1729170035105199</v>
       </c>
       <c r="G56" t="n">
-        <v>6.724799997755326</v>
+        <v>4.4387910165824</v>
       </c>
       <c r="H56" t="n">
-        <v>3.154600010020658</v>
+        <v>1.854832982644439</v>
       </c>
       <c r="I56" t="n">
-        <v>0.5951999919489026</v>
+        <v>0.3708750009536743</v>
       </c>
       <c r="J56" t="n">
-        <v>31.35400000610389</v>
+        <v>21.80741602205671</v>
       </c>
       <c r="K56" t="n">
-        <v>14.46839999698568</v>
+        <v>9.096459019929171</v>
       </c>
       <c r="L56" t="n">
-        <v>1.281799995922484</v>
+        <v>0.8121669816318899</v>
       </c>
     </row>
     <row r="57">
       <c r="A57" t="n">
-        <v>0.2338000049348921</v>
+        <v>0.1530000008642673</v>
       </c>
       <c r="B57" t="n">
-        <v>0.1113000034820288</v>
+        <v>0.05829098518006504</v>
       </c>
       <c r="C57" t="n">
-        <v>0.09889999637380242</v>
+        <v>0.06200000643730164</v>
       </c>
       <c r="D57" t="n">
-        <v>1.735600002575666</v>
+        <v>1.023124990751967</v>
       </c>
       <c r="E57" t="n">
-        <v>0.8288999961223453</v>
+        <v>0.4716250114142895</v>
       </c>
       <c r="F57" t="n">
-        <v>0.2787999983411282</v>
+        <v>0.1683750015217811</v>
       </c>
       <c r="G57" t="n">
-        <v>6.748600004357286</v>
+        <v>4.48833400150761</v>
       </c>
       <c r="H57" t="n">
-        <v>3.068999998504296</v>
+        <v>1.7652919923421</v>
       </c>
       <c r="I57" t="n">
-        <v>0.592500000493601</v>
+        <v>0.3636249748524278</v>
       </c>
       <c r="J57" t="n">
-        <v>30.29680000327062</v>
+        <v>21.43758299644105</v>
       </c>
       <c r="K57" t="n">
-        <v>13.91690000309609</v>
+        <v>8.74987497809343</v>
       </c>
       <c r="L57" t="n">
-        <v>1.323500007856637</v>
+        <v>0.8188330102711916</v>
       </c>
     </row>
     <row r="58">
       <c r="A58" t="n">
-        <v>0.2573000092525035</v>
+        <v>0.1515830226708204</v>
       </c>
       <c r="B58" t="n">
-        <v>0.1100000081351027</v>
+        <v>0.0569589901715517</v>
       </c>
       <c r="C58" t="n">
-        <v>0.1041999930748716</v>
+        <v>0.05962501745671034</v>
       </c>
       <c r="D58" t="n">
-        <v>1.69639999512583</v>
+        <v>1.042125019012019</v>
       </c>
       <c r="E58" t="n">
-        <v>0.8570000063627958</v>
+        <v>0.4547909775283188</v>
       </c>
       <c r="F58" t="n">
-        <v>0.2718000032473356</v>
+        <v>0.1687500043772161</v>
       </c>
       <c r="G58" t="n">
-        <v>7.197099999757484</v>
+        <v>4.782250005519018</v>
       </c>
       <c r="H58" t="n">
-        <v>3.55429999763146</v>
+        <v>2.033541997661814</v>
       </c>
       <c r="I58" t="n">
-        <v>0.5999999993946403</v>
+        <v>0.3825839958153665</v>
       </c>
       <c r="J58" t="n">
-        <v>31.27719998883549</v>
+        <v>21.36441698530689</v>
       </c>
       <c r="K58" t="n">
-        <v>13.81079999555368</v>
+        <v>8.702791994437575</v>
       </c>
       <c r="L58" t="n">
-        <v>2.114399991114624</v>
+        <v>0.8157499833032489</v>
       </c>
     </row>
     <row r="59">
       <c r="A59" t="n">
-        <v>0.2578999992692843</v>
+        <v>0.1529589935671538</v>
       </c>
       <c r="B59" t="n">
-        <v>0.1317999995080754</v>
+        <v>0.06787499296478927</v>
       </c>
       <c r="C59" t="n">
-        <v>0.09830000635702163</v>
+        <v>0.06050002411939204</v>
       </c>
       <c r="D59" t="n">
-        <v>1.557299998239614</v>
+        <v>0.9360419935546815</v>
       </c>
       <c r="E59" t="n">
-        <v>0.7100999937392771</v>
+        <v>0.3744999994523823</v>
       </c>
       <c r="F59" t="n">
-        <v>0.2747000107774511</v>
+        <v>0.1716249971650541</v>
       </c>
       <c r="G59" t="n">
-        <v>6.838800007244572</v>
+        <v>4.546499985735863</v>
       </c>
       <c r="H59" t="n">
-        <v>3.172900003846735</v>
+        <v>1.798833982320502</v>
       </c>
       <c r="I59" t="n">
-        <v>0.5854999908478931</v>
+        <v>0.3900419978890568</v>
       </c>
       <c r="J59" t="n">
-        <v>30.91509999649134</v>
+        <v>21.1090829980094</v>
       </c>
       <c r="K59" t="n">
-        <v>13.49159999517724</v>
+        <v>8.530332997906953</v>
       </c>
       <c r="L59" t="n">
-        <v>1.270799999474548</v>
+        <v>0.8189160143956542</v>
       </c>
     </row>
     <row r="60">
       <c r="A60" t="n">
-        <v>0.2394000039203092</v>
+        <v>0.139708979986608</v>
       </c>
       <c r="B60" t="n">
-        <v>0.1292000088142231</v>
+        <v>0.06612497963942587</v>
       </c>
       <c r="C60" t="n">
-        <v>0.09700001101009548</v>
+        <v>0.05950001650489867</v>
       </c>
       <c r="D60" t="n">
-        <v>1.695899991318583</v>
+        <v>1.029415987432003</v>
       </c>
       <c r="E60" t="n">
-        <v>0.7992000028025359</v>
+        <v>0.4070000140927732</v>
       </c>
       <c r="F60" t="n">
-        <v>0.2743000077316537</v>
+        <v>0.1742920139804482</v>
       </c>
       <c r="G60" t="n">
-        <v>7.253399991896003</v>
+        <v>4.684999992605299</v>
       </c>
       <c r="H60" t="n">
-        <v>3.38019999617245</v>
+        <v>1.916083012474701</v>
       </c>
       <c r="I60" t="n">
-        <v>0.5895000067539513</v>
+        <v>0.3753339988179505</v>
       </c>
       <c r="J60" t="n">
-        <v>30.95609998854343</v>
+        <v>21.21345899649896</v>
       </c>
       <c r="K60" t="n">
-        <v>13.7107000045944</v>
+        <v>8.583290997194126</v>
       </c>
       <c r="L60" t="n">
-        <v>1.306499994825572</v>
+        <v>0.8115410164464265</v>
       </c>
     </row>
     <row r="61">
       <c r="A61" t="n">
-        <v>0.2773000014713034</v>
+        <v>0.1615840010344982</v>
       </c>
       <c r="B61" t="n">
-        <v>0.1482000079704449</v>
+        <v>0.07308300700969994</v>
       </c>
       <c r="C61" t="n">
-        <v>0.09980000322684646</v>
+        <v>0.06091699469834566</v>
       </c>
       <c r="D61" t="n">
-        <v>1.703599991742522</v>
+        <v>1.04825000744313</v>
       </c>
       <c r="E61" t="n">
-        <v>0.7994999905349687</v>
+        <v>0.4179999814368784</v>
       </c>
       <c r="F61" t="n">
-        <v>0.2730999985942617</v>
+        <v>0.166874990100041</v>
       </c>
       <c r="G61" t="n">
-        <v>7.296299998415634</v>
+        <v>4.704541992396116</v>
       </c>
       <c r="H61" t="n">
-        <v>3.389999998034909</v>
+        <v>1.940457994351164</v>
       </c>
       <c r="I61" t="n">
-        <v>0.5920999974478036</v>
+        <v>0.3732919867616147</v>
       </c>
       <c r="J61" t="n">
-        <v>30.97079999861307</v>
+        <v>21.18920799694024</v>
       </c>
       <c r="K61" t="n">
-        <v>13.52600000973325</v>
+        <v>8.362833003047854</v>
       </c>
       <c r="L61" t="n">
-        <v>1.290300002438016</v>
+        <v>0.8122499857563525</v>
       </c>
     </row>
     <row r="62">
       <c r="A62" t="n">
-        <v>0.2672999980859458</v>
+        <v>0.1950830046553165</v>
       </c>
       <c r="B62" t="n">
-        <v>0.1340000017080456</v>
+        <v>0.07204199209809303</v>
       </c>
       <c r="C62" t="n">
-        <v>0.09689999569673091</v>
+        <v>0.07654199725948274</v>
       </c>
       <c r="D62" t="n">
-        <v>1.728600007481873</v>
+        <v>1.047333993483335</v>
       </c>
       <c r="E62" t="n">
-        <v>0.9395999950356781</v>
+        <v>0.5042919947300106</v>
       </c>
       <c r="F62" t="n">
-        <v>0.2829000004567206</v>
+        <v>0.1939579960890114</v>
       </c>
       <c r="G62" t="n">
-        <v>7.164100010413677</v>
+        <v>4.789375001564622</v>
       </c>
       <c r="H62" t="n">
-        <v>3.288899999461137</v>
+        <v>1.969582983292639</v>
       </c>
       <c r="I62" t="n">
-        <v>0.7545999978901818</v>
+        <v>0.4301250155549496</v>
       </c>
       <c r="J62" t="n">
-        <v>30.35149999777786</v>
+        <v>21.18091701413505</v>
       </c>
       <c r="K62" t="n">
-        <v>13.28419998753816</v>
+        <v>8.687749999808148</v>
       </c>
       <c r="L62" t="n">
-        <v>1.279000003705733</v>
+        <v>0.8016670180950314</v>
       </c>
     </row>
     <row r="63">
       <c r="A63" t="n">
-        <v>0.2976999967359006</v>
+        <v>0.1531659800093621</v>
       </c>
       <c r="B63" t="n">
-        <v>0.1339000009465963</v>
+        <v>0.06816699169576168</v>
       </c>
       <c r="C63" t="n">
-        <v>0.1224000006914139</v>
+        <v>0.06233301246538758</v>
       </c>
       <c r="D63" t="n">
-        <v>1.738699997076765</v>
+        <v>1.01270800223574</v>
       </c>
       <c r="E63" t="n">
-        <v>0.8309999975608662</v>
+        <v>0.4696669930126518</v>
       </c>
       <c r="F63" t="n">
-        <v>0.2817000058712438</v>
+        <v>0.1757499994710088</v>
       </c>
       <c r="G63" t="n">
-        <v>6.955899996683002</v>
+        <v>4.62870899355039</v>
       </c>
       <c r="H63" t="n">
-        <v>3.204699998605065</v>
+        <v>1.848874991992489</v>
       </c>
       <c r="I63" t="n">
-        <v>0.593700009630993</v>
+        <v>0.3765420115087181</v>
       </c>
       <c r="J63" t="n">
-        <v>30.42149999237154</v>
+        <v>21.13849998568185</v>
       </c>
       <c r="K63" t="n">
-        <v>13.29230000555981</v>
+        <v>8.43662497936748</v>
       </c>
       <c r="L63" t="n">
-        <v>1.318800001172349</v>
+        <v>0.8152090013027191</v>
       </c>
     </row>
     <row r="64">
       <c r="A64" t="n">
-        <v>0.284200010355562</v>
+        <v>0.1636669912841171</v>
       </c>
       <c r="B64" t="n">
-        <v>0.139000010676682</v>
+        <v>0.07037498289719224</v>
       </c>
       <c r="C64" t="n">
-        <v>0.09779998799785972</v>
+        <v>0.05970898200757802</v>
       </c>
       <c r="D64" t="n">
-        <v>1.810099987778813</v>
+        <v>1.050374994520098</v>
       </c>
       <c r="E64" t="n">
-        <v>0.8630999946035445</v>
+        <v>0.4179580137133598</v>
       </c>
       <c r="F64" t="n">
-        <v>0.271999990218319</v>
+        <v>0.1673340157140046</v>
       </c>
       <c r="G64" t="n">
-        <v>7.521499996073544</v>
+        <v>4.821540991542861</v>
       </c>
       <c r="H64" t="n">
-        <v>3.746300004422665</v>
+        <v>2.154167013941333</v>
       </c>
       <c r="I64" t="n">
-        <v>0.6037999992258847</v>
+        <v>0.3719579835887998</v>
       </c>
       <c r="J64" t="n">
-        <v>30.65339999739081</v>
+        <v>21.57133398577571</v>
       </c>
       <c r="K64" t="n">
-        <v>13.98329999938142</v>
+        <v>8.775624999543652</v>
       </c>
       <c r="L64" t="n">
-        <v>1.282500001252629</v>
+        <v>0.8121660212054849</v>
       </c>
     </row>
     <row r="65">
       <c r="A65" t="n">
-        <v>0.2736999886110425</v>
+        <v>0.1582079858053476</v>
       </c>
       <c r="B65" t="n">
-        <v>0.1291000080527738</v>
+        <v>0.06766599835827947</v>
       </c>
       <c r="C65" t="n">
-        <v>0.09529999806545675</v>
+        <v>0.05995799438096583</v>
       </c>
       <c r="D65" t="n">
-        <v>1.622799987671897</v>
+        <v>0.9445420000702143</v>
       </c>
       <c r="E65" t="n">
-        <v>0.7703000010224059</v>
+        <v>0.3894999972544611</v>
       </c>
       <c r="F65" t="n">
-        <v>0.2708999963942915</v>
+        <v>0.1707089832052588</v>
       </c>
       <c r="G65" t="n">
-        <v>7.306799991056323</v>
+        <v>4.773499997099862</v>
       </c>
       <c r="H65" t="n">
-        <v>3.451299999142066</v>
+        <v>2.0241669844836</v>
       </c>
       <c r="I65" t="n">
-        <v>0.5993999948259443</v>
+        <v>0.3627919941209257</v>
       </c>
       <c r="J65" t="n">
-        <v>30.62970000610221</v>
+        <v>21.38466699398123</v>
       </c>
       <c r="K65" t="n">
-        <v>13.80020000215154</v>
+        <v>8.563415991375223</v>
       </c>
       <c r="L65" t="n">
-        <v>1.274600013857707</v>
+        <v>0.8162909944076091</v>
       </c>
     </row>
     <row r="66">
       <c r="A66" t="n">
-        <v>0.2781000075628981</v>
+        <v>0.167249992955476</v>
       </c>
       <c r="B66" t="n">
-        <v>0.1435000012861565</v>
+        <v>0.07658300455659628</v>
       </c>
       <c r="C66" t="n">
-        <v>0.09639999188948423</v>
+        <v>0.07024998194538057</v>
       </c>
       <c r="D66" t="n">
-        <v>1.603600001544692</v>
+        <v>0.9417910187039524</v>
       </c>
       <c r="E66" t="n">
-        <v>0.7773999968776479</v>
+        <v>0.3762499836739153</v>
       </c>
       <c r="F66" t="n">
-        <v>0.2729999978328124</v>
+        <v>0.1678330008871853</v>
       </c>
       <c r="G66" t="n">
-        <v>7.072899999911897</v>
+        <v>4.641832987545058</v>
       </c>
       <c r="H66" t="n">
-        <v>3.308100000140257</v>
+        <v>1.863375015091151</v>
       </c>
       <c r="I66" t="n">
-        <v>0.585700006922707</v>
+        <v>0.3685419796966016</v>
       </c>
       <c r="J66" t="n">
-        <v>31.80949999659788</v>
+        <v>21.80845898692496</v>
       </c>
       <c r="K66" t="n">
-        <v>14.18709999416023</v>
+        <v>9.020666999276727</v>
       </c>
       <c r="L66" t="n">
-        <v>1.280399999814108</v>
+        <v>0.8106669993139803</v>
       </c>
     </row>
     <row r="67">
       <c r="A67" t="n">
-        <v>0.2491000050213188</v>
+        <v>0.1513750175945461</v>
       </c>
       <c r="B67" t="n">
-        <v>0.1175000070361421</v>
+        <v>0.06999998004175723</v>
       </c>
       <c r="C67" t="n">
-        <v>0.09580000187270343</v>
+        <v>0.06366701563820243</v>
       </c>
       <c r="D67" t="n">
-        <v>1.813300012145191</v>
+        <v>1.016958995023742</v>
       </c>
       <c r="E67" t="n">
-        <v>0.8612999954493716</v>
+        <v>0.4188329912722111</v>
       </c>
       <c r="F67" t="n">
-        <v>0.2742000069702044</v>
+        <v>0.1767499779816717</v>
       </c>
       <c r="G67" t="n">
-        <v>7.054899993818253</v>
+        <v>4.590666008880362</v>
       </c>
       <c r="H67" t="n">
-        <v>3.29359999159351</v>
+        <v>1.854959002230316</v>
       </c>
       <c r="I67" t="n">
-        <v>0.5951999919489026</v>
+        <v>0.3771670162677765</v>
       </c>
       <c r="J67" t="n">
-        <v>30.83609999157488</v>
+        <v>21.44304197281599</v>
       </c>
       <c r="K67" t="n">
-        <v>14.07800000743009</v>
+        <v>8.926250011427328</v>
       </c>
       <c r="L67" t="n">
-        <v>1.268899999558926</v>
+        <v>0.8100839913822711</v>
       </c>
     </row>
     <row r="68">
       <c r="A68" t="n">
-        <v>0.2741000062087551</v>
+        <v>0.1827499945648015</v>
       </c>
       <c r="B68" t="n">
-        <v>0.1241999998455867</v>
+        <v>0.07400001049973071</v>
       </c>
       <c r="C68" t="n">
-        <v>0.09700001101009548</v>
+        <v>0.08004100527614355</v>
       </c>
       <c r="D68" t="n">
-        <v>1.856300004874356</v>
+        <v>1.081541005987674</v>
       </c>
       <c r="E68" t="n">
-        <v>0.9312999900430441</v>
+        <v>0.4493339802138507</v>
       </c>
       <c r="F68" t="n">
-        <v>0.2725000085774809</v>
+        <v>0.1674160012044013</v>
       </c>
       <c r="G68" t="n">
-        <v>7.242799998493865</v>
+        <v>4.715749993920326</v>
       </c>
       <c r="H68" t="n">
-        <v>3.348600002937019</v>
+        <v>1.930625003296882</v>
       </c>
       <c r="I68" t="n">
-        <v>0.592500000493601</v>
+        <v>0.3756250080186874</v>
       </c>
       <c r="J68" t="n">
-        <v>31.24389999720734</v>
+        <v>21.55091697932221</v>
       </c>
       <c r="K68" t="n">
-        <v>14.06549999956042</v>
+        <v>8.781291980994865</v>
       </c>
       <c r="L68" t="n">
-        <v>1.286600003368221</v>
+        <v>0.8116249809972942</v>
       </c>
     </row>
     <row r="69">
       <c r="A69" t="n">
-        <v>0.335900011123158</v>
+        <v>0.1625829900149256</v>
       </c>
       <c r="B69" t="n">
-        <v>0.1306000049225986</v>
+        <v>0.06779201794415712</v>
       </c>
       <c r="C69" t="n">
-        <v>0.09750000026542693</v>
+        <v>0.06158300675451756</v>
       </c>
       <c r="D69" t="n">
-        <v>1.693700003670529</v>
+        <v>0.960250006755814</v>
       </c>
       <c r="E69" t="n">
-        <v>0.7919999916339293</v>
+        <v>0.3777079982683063</v>
       </c>
       <c r="F69" t="n">
-        <v>0.2767999976640567</v>
+        <v>0.174166023498401</v>
       </c>
       <c r="G69" t="n">
-        <v>6.838200002675876</v>
+        <v>4.574165999656543</v>
       </c>
       <c r="H69" t="n">
-        <v>3.143399997497909</v>
+        <v>1.798665995011106</v>
       </c>
       <c r="I69" t="n">
-        <v>0.5918999959249049</v>
+        <v>0.3729999880306423</v>
       </c>
       <c r="J69" t="n">
-        <v>30.41680000023916</v>
+        <v>21.02508299867623</v>
       </c>
       <c r="K69" t="n">
-        <v>13.1890999909956</v>
+        <v>8.508208993589506</v>
       </c>
       <c r="L69" t="n">
-        <v>1.273599991691299</v>
+        <v>0.8190420048777014</v>
       </c>
     </row>
     <row r="70">
       <c r="A70" t="n">
-        <v>0.2954999945359305</v>
+        <v>0.1732500095386058</v>
       </c>
       <c r="B70" t="n">
-        <v>0.152900000102818</v>
+        <v>0.07949999417178333</v>
       </c>
       <c r="C70" t="n">
-        <v>0.09830000635702163</v>
+        <v>0.06158402538858354</v>
       </c>
       <c r="D70" t="n">
-        <v>1.714800004265271</v>
+        <v>0.9880829893518239</v>
       </c>
       <c r="E70" t="n">
-        <v>0.8091000054264441</v>
+        <v>0.3948330122511834</v>
       </c>
       <c r="F70" t="n">
-        <v>0.2709000109462067</v>
+        <v>0.1682079746387899</v>
       </c>
       <c r="G70" t="n">
-        <v>6.667699999525212</v>
+        <v>4.413707996718585</v>
       </c>
       <c r="H70" t="n">
-        <v>3.165999994962476</v>
+        <v>1.825917017413303</v>
       </c>
       <c r="I70" t="n">
-        <v>0.5875999922864139</v>
+        <v>0.3880830190610141</v>
       </c>
       <c r="J70" t="n">
-        <v>30.65099999366794</v>
+        <v>21.36895799776539</v>
       </c>
       <c r="K70" t="n">
-        <v>13.77160000265576</v>
+        <v>8.716209005797282</v>
       </c>
       <c r="L70" t="n">
-        <v>1.258400006918237</v>
+        <v>0.8176660048775375</v>
       </c>
     </row>
     <row r="71">
       <c r="A71" t="n">
-        <v>0.2592999953776598</v>
+        <v>0.152749998960644</v>
       </c>
       <c r="B71" t="n">
-        <v>0.1270000066142529</v>
+        <v>0.06562500493600965</v>
       </c>
       <c r="C71" t="n">
-        <v>0.1013000000966713</v>
+        <v>0.0619160127826035</v>
       </c>
       <c r="D71" t="n">
-        <v>1.729299998260103</v>
+        <v>1.020042021991685</v>
       </c>
       <c r="E71" t="n">
-        <v>0.7993000035639852</v>
+        <v>0.4020000051241368</v>
       </c>
       <c r="F71" t="n">
-        <v>0.2778999914880842</v>
+        <v>0.1758750004228204</v>
       </c>
       <c r="G71" t="n">
-        <v>7.634499997948296</v>
+        <v>4.937416990287602</v>
       </c>
       <c r="H71" t="n">
-        <v>3.507999994326383</v>
+        <v>2.051749994279817</v>
       </c>
       <c r="I71" t="n">
-        <v>0.5893000052310526</v>
+        <v>0.3729159943759441</v>
       </c>
       <c r="J71" t="n">
-        <v>30.27269999438431</v>
+        <v>21.17341599659994</v>
       </c>
       <c r="K71" t="n">
-        <v>13.36939999600872</v>
+        <v>8.49400000879541</v>
       </c>
       <c r="L71" t="n">
-        <v>1.280999989830889</v>
+        <v>0.8296660089399666</v>
       </c>
     </row>
     <row r="72">
       <c r="A72" t="n">
-        <v>0.2840000088326633</v>
+        <v>0.1886250101961195</v>
       </c>
       <c r="B72" t="n">
-        <v>0.181199997314252</v>
+        <v>0.08512497879564762</v>
       </c>
       <c r="C72" t="n">
-        <v>0.1037000038195401</v>
+        <v>0.0680000230204314</v>
       </c>
       <c r="D72" t="n">
-        <v>1.697100000455976</v>
+        <v>1.020499999867752</v>
       </c>
       <c r="E72" t="n">
-        <v>1.045099998009391</v>
+        <v>0.5416659987531602</v>
       </c>
       <c r="F72" t="n">
-        <v>0.2706999948713928</v>
+        <v>0.1688750053290278</v>
       </c>
       <c r="G72" t="n">
-        <v>6.955600008950569</v>
+        <v>4.791083018062636</v>
       </c>
       <c r="H72" t="n">
-        <v>3.365299999131821</v>
+        <v>1.902583986520767</v>
       </c>
       <c r="I72" t="n">
-        <v>0.5918000097153708</v>
+        <v>0.3622500225901604</v>
       </c>
       <c r="J72" t="n">
-        <v>30.41180000582244</v>
+        <v>21.25750001869164</v>
       </c>
       <c r="K72" t="n">
-        <v>13.37090000743046</v>
+        <v>8.567874989239499</v>
       </c>
       <c r="L72" t="n">
-        <v>1.287699997192249</v>
+        <v>0.8342500077560544</v>
       </c>
     </row>
     <row r="73">
       <c r="A73" t="n">
-        <v>0.3013000095961615</v>
+        <v>0.1697090046945959</v>
       </c>
       <c r="B73" t="n">
-        <v>0.1201999984914437</v>
+        <v>0.06316701183095574</v>
       </c>
       <c r="C73" t="n">
-        <v>0.1000000047497451</v>
+        <v>0.06029100040905178</v>
       </c>
       <c r="D73" t="n">
-        <v>1.780699996743351</v>
+        <v>1.135458005592227</v>
       </c>
       <c r="E73" t="n">
-        <v>1.193499992950819</v>
+        <v>0.4303329915273935</v>
       </c>
       <c r="F73" t="n">
-        <v>0.2739000046858564</v>
+        <v>0.167959020473063</v>
       </c>
       <c r="G73" t="n">
-        <v>7.06789999094326</v>
+        <v>4.681209014961496</v>
       </c>
       <c r="H73" t="n">
-        <v>3.27879999531433</v>
+        <v>1.94470799760893</v>
       </c>
       <c r="I73" t="n">
-        <v>0.5883000121684745</v>
+        <v>0.3955830179620534</v>
       </c>
       <c r="J73" t="n">
-        <v>30.61729999899399</v>
+        <v>21.09591598855332</v>
       </c>
       <c r="K73" t="n">
-        <v>13.2828000059817</v>
+        <v>8.375375007744879</v>
       </c>
       <c r="L73" t="n">
-        <v>1.29130001005251</v>
+        <v>0.831416982691735</v>
       </c>
     </row>
     <row r="74">
       <c r="A74" t="n">
-        <v>0.2498999965609983</v>
+        <v>0.1577090006321669</v>
       </c>
       <c r="B74" t="n">
-        <v>0.1293999957852066</v>
+        <v>0.06795901572331786</v>
       </c>
       <c r="C74" t="n">
-        <v>0.102100006188266</v>
+        <v>0.06295900675468147</v>
       </c>
       <c r="D74" t="n">
-        <v>1.626400000532158</v>
+        <v>0.9518339938949794</v>
       </c>
       <c r="E74" t="n">
-        <v>0.7768999930704013</v>
+        <v>0.4039170162286609</v>
       </c>
       <c r="F74" t="n">
-        <v>0.283399989712052</v>
+        <v>0.1688750053290278</v>
       </c>
       <c r="G74" t="n">
-        <v>7.206900001619942</v>
+        <v>4.829499986954033</v>
       </c>
       <c r="H74" t="n">
-        <v>3.433200006838888</v>
+        <v>1.93800000124611</v>
       </c>
       <c r="I74" t="n">
-        <v>0.5953999934718013</v>
+        <v>0.3881669836118817</v>
       </c>
       <c r="J74" t="n">
-        <v>28.93240000412334</v>
+        <v>20.41808300418779</v>
       </c>
       <c r="K74" t="n">
-        <v>13.65259999874979</v>
+        <v>8.651415992062539</v>
       </c>
       <c r="L74" t="n">
-        <v>1.27940000675153</v>
+        <v>0.8128329936880618</v>
       </c>
     </row>
     <row r="75">
       <c r="A75" t="n">
-        <v>0.2797999914037064</v>
+        <v>0.1645830052439123</v>
       </c>
       <c r="B75" t="n">
-        <v>0.1532999885967001</v>
+        <v>0.07620902033522725</v>
       </c>
       <c r="C75" t="n">
-        <v>0.09590000263415277</v>
+        <v>0.05937498644925654</v>
       </c>
       <c r="D75" t="n">
-        <v>1.710099997580983</v>
+        <v>1.033916982123628</v>
       </c>
       <c r="E75" t="n">
-        <v>0.8267999946838245</v>
+        <v>0.4370830138213933</v>
       </c>
       <c r="F75" t="n">
-        <v>0.2763999946182594</v>
+        <v>0.17120799748227</v>
       </c>
       <c r="G75" t="n">
-        <v>7.239800004754215</v>
+        <v>4.781041003298014</v>
       </c>
       <c r="H75" t="n">
-        <v>3.486800007522106</v>
+        <v>2.001042012125254</v>
       </c>
       <c r="I75" t="n">
-        <v>0.589400005992502</v>
+        <v>0.374625000404194</v>
       </c>
       <c r="J75" t="n">
-        <v>30.66870001202915</v>
+        <v>21.19724999647588</v>
       </c>
       <c r="K75" t="n">
-        <v>13.43639999686275</v>
+        <v>8.402166015002877</v>
       </c>
       <c r="L75" t="n">
-        <v>1.305400001001544</v>
+        <v>0.8134579984471202</v>
       </c>
     </row>
     <row r="76">
       <c r="A76" t="n">
-        <v>0.2863999980036169</v>
+        <v>0.1770000089891255</v>
       </c>
       <c r="B76" t="n">
-        <v>0.14519999967888</v>
+        <v>0.07704200106672943</v>
       </c>
       <c r="C76" t="n">
-        <v>0.09629999112803489</v>
+        <v>0.06733401096425951</v>
       </c>
       <c r="D76" t="n">
-        <v>1.641499999095686</v>
+        <v>1.055375003488734</v>
       </c>
       <c r="E76" t="n">
-        <v>0.8068000024650246</v>
+        <v>0.4041659994982183</v>
       </c>
       <c r="F76" t="n">
-        <v>0.2693999995244667</v>
+        <v>0.1666670141275972</v>
       </c>
       <c r="G76" t="n">
-        <v>7.171599994762801</v>
+        <v>4.858291998971254</v>
       </c>
       <c r="H76" t="n">
-        <v>3.516600001603365</v>
+        <v>2.040874998783693</v>
       </c>
       <c r="I76" t="n">
-        <v>0.5984000017633662</v>
+        <v>0.3746669972315431</v>
       </c>
       <c r="J76" t="n">
-        <v>30.16419999767095</v>
+        <v>21.1001250136178</v>
       </c>
       <c r="K76" t="n">
-        <v>14.08189999347087</v>
+        <v>8.719874982489273</v>
       </c>
       <c r="L76" t="n">
-        <v>1.29269999160897</v>
+        <v>0.7905839884188026</v>
       </c>
     </row>
     <row r="77">
       <c r="A77" t="n">
-        <v>0.2899000101024285</v>
+        <v>0.1711669901851565</v>
       </c>
       <c r="B77" t="n">
-        <v>0.1417999883415177</v>
+        <v>0.07462498615495861</v>
       </c>
       <c r="C77" t="n">
-        <v>0.09729999874252826</v>
+        <v>0.06316701183095574</v>
       </c>
       <c r="D77" t="n">
-        <v>1.732899996568449</v>
+        <v>0.9969169914256781</v>
       </c>
       <c r="E77" t="n">
-        <v>0.8239000017056242</v>
+        <v>0.4056250036228448</v>
       </c>
       <c r="F77" t="n">
-        <v>0.2749999985098839</v>
+        <v>0.1692500081844628</v>
       </c>
       <c r="G77" t="n">
-        <v>7.026699997368269</v>
+        <v>4.644874978112057</v>
       </c>
       <c r="H77" t="n">
-        <v>3.204199994797818</v>
+        <v>1.848791987868026</v>
       </c>
       <c r="I77" t="n">
-        <v>0.5821999948238954</v>
+        <v>0.3635419998317957</v>
       </c>
       <c r="J77" t="n">
-        <v>30.80149999004789</v>
+        <v>21.22462500119582</v>
       </c>
       <c r="K77" t="n">
-        <v>13.46990000456572</v>
+        <v>8.486832986818627</v>
       </c>
       <c r="L77" t="n">
-        <v>1.291799999307841</v>
+        <v>0.8379170030821115</v>
       </c>
     </row>
     <row r="78">
       <c r="A78" t="n">
-        <v>0.2715000009629875</v>
+        <v>0.1642500283196568</v>
       </c>
       <c r="B78" t="n">
-        <v>0.1326000055996701</v>
+        <v>0.06954200216569006</v>
       </c>
       <c r="C78" t="n">
-        <v>0.09650000720284879</v>
+        <v>0.06179200136102736</v>
       </c>
       <c r="D78" t="n">
-        <v>1.645399999688379</v>
+        <v>0.97366698901169</v>
       </c>
       <c r="E78" t="n">
-        <v>0.7757999992463738</v>
+        <v>0.418459007050842</v>
       </c>
       <c r="F78" t="n">
-        <v>0.2735000016400591</v>
+        <v>0.1669169869273901</v>
       </c>
       <c r="G78" t="n">
-        <v>6.873799997265451</v>
+        <v>4.477957991184667</v>
       </c>
       <c r="H78" t="n">
-        <v>2.837199994246475</v>
+        <v>1.659166009631008</v>
       </c>
       <c r="I78" t="n">
-        <v>0.5907000013394281</v>
+        <v>0.3727499861270189</v>
       </c>
       <c r="J78" t="n">
-        <v>30.28679999988526</v>
+        <v>21.04083300218917</v>
       </c>
       <c r="K78" t="n">
-        <v>13.32520000869408</v>
+        <v>8.41999999829568</v>
       </c>
       <c r="L78" t="n">
-        <v>1.286500002606772</v>
+        <v>0.8120420097839087</v>
       </c>
     </row>
     <row r="79">
       <c r="A79" t="n">
-        <v>0.2717999886954203</v>
+        <v>0.1566669961903244</v>
       </c>
       <c r="B79" t="n">
-        <v>0.1363999908789992</v>
+        <v>0.06987497908994555</v>
       </c>
       <c r="C79" t="n">
-        <v>0.09660000796429813</v>
+        <v>0.06254200707189739</v>
       </c>
       <c r="D79" t="n">
-        <v>1.59499999426771</v>
+        <v>1.01645800168626</v>
       </c>
       <c r="E79" t="n">
-        <v>0.7359000010183081</v>
+        <v>0.3746669972315431</v>
       </c>
       <c r="F79" t="n">
-        <v>0.2740000054473057</v>
+        <v>0.1732920063659549</v>
       </c>
       <c r="G79" t="n">
-        <v>7.016600007773377</v>
+        <v>4.665583022870123</v>
       </c>
       <c r="H79" t="n">
-        <v>3.198800011887215</v>
+        <v>1.866209000581875</v>
       </c>
       <c r="I79" t="n">
-        <v>0.592500000493601</v>
+        <v>0.3722080145962536</v>
       </c>
       <c r="J79" t="n">
-        <v>30.9519000002183</v>
+        <v>21.60266699502245</v>
       </c>
       <c r="K79" t="n">
-        <v>14.2863000073703</v>
+        <v>8.943499997258186</v>
       </c>
       <c r="L79" t="n">
-        <v>1.28229999972973</v>
+        <v>0.8135410025715828</v>
       </c>
     </row>
     <row r="80">
       <c r="A80" t="n">
-        <v>0.2831000019796193</v>
+        <v>0.1689170021563768</v>
       </c>
       <c r="B80" t="n">
-        <v>0.1392000121995807</v>
+        <v>0.07104198448359966</v>
       </c>
       <c r="C80" t="n">
-        <v>0.09560000034980476</v>
+        <v>0.06187500548548996</v>
       </c>
       <c r="D80" t="n">
-        <v>1.710199998342432</v>
+        <v>1.009500003419816</v>
       </c>
       <c r="E80" t="n">
-        <v>0.7986999989952892</v>
+        <v>0.4059589991811663</v>
       </c>
       <c r="F80" t="n">
-        <v>0.2726999955484644</v>
+        <v>0.170499988598749</v>
       </c>
       <c r="G80" t="n">
-        <v>7.335000002058223</v>
+        <v>4.889499978162348</v>
       </c>
       <c r="H80" t="n">
-        <v>3.587200000765733</v>
+        <v>1.9697499810718</v>
       </c>
       <c r="I80" t="n">
-        <v>0.5897999944863841</v>
+        <v>0.4342909960541874</v>
       </c>
       <c r="J80" t="n">
-        <v>30.46890000405256</v>
+        <v>21.14358299877495</v>
       </c>
       <c r="K80" t="n">
-        <v>13.35870000184514</v>
+        <v>8.394500007852912</v>
       </c>
       <c r="L80" t="n">
-        <v>1.290899992454797</v>
+        <v>0.8085840090643615</v>
       </c>
     </row>
     <row r="81">
       <c r="A81" t="n">
-        <v>0.2682000049389899</v>
+        <v>0.1650000049266964</v>
       </c>
       <c r="B81" t="n">
-        <v>0.1358000008622184</v>
+        <v>0.07641597767360508</v>
       </c>
       <c r="C81" t="n">
-        <v>0.09460000728722662</v>
+        <v>0.06383401341736317</v>
       </c>
       <c r="D81" t="n">
-        <v>1.797400007490069</v>
+        <v>1.123416994232684</v>
       </c>
       <c r="E81" t="n">
-        <v>0.8712000126251951</v>
+        <v>0.4493340093176812</v>
       </c>
       <c r="F81" t="n">
-        <v>0.2734000008786097</v>
+        <v>0.1722500019241124</v>
       </c>
       <c r="G81" t="n">
-        <v>6.886599992867559</v>
+        <v>4.534165986115113</v>
       </c>
       <c r="H81" t="n">
-        <v>3.215299992007203</v>
+        <v>1.77966698538512</v>
       </c>
       <c r="I81" t="n">
-        <v>0.5867999861948192</v>
+        <v>0.3596250026021153</v>
       </c>
       <c r="J81" t="n">
-        <v>30.16700000443961</v>
+        <v>21.12704099272378</v>
       </c>
       <c r="K81" t="n">
-        <v>13.18090000131633</v>
+        <v>8.535750006558374</v>
       </c>
       <c r="L81" t="n">
-        <v>1.315000001341105</v>
+        <v>0.7900840137153864</v>
       </c>
     </row>
     <row r="82">
       <c r="A82" t="n">
-        <v>0.2759000053629279</v>
+        <v>0.1882499782368541</v>
       </c>
       <c r="B82" t="n">
-        <v>0.1479000056860968</v>
+        <v>0.07795801502652466</v>
       </c>
       <c r="C82" t="n">
-        <v>0.09940000018104911</v>
+        <v>0.07229199400171638</v>
       </c>
       <c r="D82" t="n">
-        <v>1.659699992160313</v>
+        <v>1.090166973881423</v>
       </c>
       <c r="E82" t="n">
-        <v>0.7671000057598576</v>
+        <v>0.4127499996684492</v>
       </c>
       <c r="F82" t="n">
-        <v>0.2685000072233379</v>
+        <v>0.1699170097708702</v>
       </c>
       <c r="G82" t="n">
-        <v>7.641499993042089</v>
+        <v>4.915083991363645</v>
       </c>
       <c r="H82" t="n">
-        <v>3.421800007345155</v>
+        <v>2.008708019275218</v>
       </c>
       <c r="I82" t="n">
-        <v>0.5931999912718311</v>
+        <v>0.3612920118030161</v>
       </c>
       <c r="J82" t="n">
-        <v>31.12090000649914</v>
+        <v>21.88837499124929</v>
       </c>
       <c r="K82" t="n">
-        <v>13.78999999724329</v>
+        <v>8.935207995818928</v>
       </c>
       <c r="L82" t="n">
-        <v>1.289199994062074</v>
+        <v>0.8294160070363432</v>
       </c>
     </row>
     <row r="83">
       <c r="A83" t="n">
-        <v>0.2631999959703535</v>
+        <v>0.1605830038897693</v>
       </c>
       <c r="B83" t="n">
-        <v>0.1371999969705939</v>
+        <v>0.06416600081138313</v>
       </c>
       <c r="C83" t="n">
-        <v>0.0973999995039776</v>
+        <v>0.06079199374653399</v>
       </c>
       <c r="D83" t="n">
-        <v>1.612799998838454</v>
+        <v>0.9934160043485463</v>
       </c>
       <c r="E83" t="n">
-        <v>0.7676999957766384</v>
+        <v>0.389459019061178</v>
       </c>
       <c r="F83" t="n">
-        <v>0.2746999962255359</v>
+        <v>0.1787499932106584</v>
       </c>
       <c r="G83" t="n">
-        <v>6.870099998195656</v>
+        <v>4.524165997281671</v>
       </c>
       <c r="H83" t="n">
-        <v>3.269799999543466</v>
+        <v>1.879124989500269</v>
       </c>
       <c r="I83" t="n">
-        <v>0.5953999934718013</v>
+        <v>0.368125009117648</v>
       </c>
       <c r="J83" t="n">
-        <v>30.87919999961741</v>
+        <v>21.45474997814745</v>
       </c>
       <c r="K83" t="n">
-        <v>13.36660000379197</v>
+        <v>8.633124991320074</v>
       </c>
       <c r="L83" t="n">
-        <v>1.295199996093288</v>
+        <v>0.8130409987643361</v>
       </c>
     </row>
     <row r="84">
       <c r="A84" t="n">
-        <v>0.2442999975755811</v>
+        <v>0.1442499924451113</v>
       </c>
       <c r="B84" t="n">
-        <v>0.1222999999299645</v>
+        <v>0.07454201113432646</v>
       </c>
       <c r="C84" t="n">
-        <v>0.09929999941959977</v>
+        <v>0.05991701618768275</v>
       </c>
       <c r="D84" t="n">
-        <v>1.661599992075935</v>
+        <v>0.9851669892668724</v>
       </c>
       <c r="E84" t="n">
-        <v>0.79340000229422</v>
+        <v>0.4061250074300915</v>
       </c>
       <c r="F84" t="n">
-        <v>0.2719000040087849</v>
+        <v>0.1754590193741024</v>
       </c>
       <c r="G84" t="n">
-        <v>7.300299999769777</v>
+        <v>4.939334001392126</v>
       </c>
       <c r="H84" t="n">
-        <v>3.298299998277798</v>
+        <v>1.853916008258238</v>
       </c>
       <c r="I84" t="n">
-        <v>0.5964000010862947</v>
+        <v>0.3631669969763607</v>
       </c>
       <c r="J84" t="n">
-        <v>31.27900000254158</v>
+        <v>21.91512502031401</v>
       </c>
       <c r="K84" t="n">
-        <v>14.21249999839347</v>
+        <v>8.995875017717481</v>
       </c>
       <c r="L84" t="n">
-        <v>1.292500004637986</v>
+        <v>0.8627919887658209</v>
       </c>
     </row>
     <row r="85">
       <c r="A85" t="n">
-        <v>0.2894000062951818</v>
+        <v>0.2140830038115382</v>
       </c>
       <c r="B85" t="n">
-        <v>0.1480999926570803</v>
+        <v>0.07658300455659628</v>
       </c>
       <c r="C85" t="n">
-        <v>0.09989998943638057</v>
+        <v>0.06091600516811013</v>
       </c>
       <c r="D85" t="n">
-        <v>1.699600004940294</v>
+        <v>1.030083978548646</v>
       </c>
       <c r="E85" t="n">
-        <v>0.8516999951098114</v>
+        <v>0.4360000020824373</v>
       </c>
       <c r="F85" t="n">
-        <v>0.269199998001568</v>
+        <v>0.173374981386587</v>
       </c>
       <c r="G85" t="n">
-        <v>7.2851000004448</v>
+        <v>4.709959001047537</v>
       </c>
       <c r="H85" t="n">
-        <v>3.414899998460896</v>
+        <v>1.990832999581471</v>
       </c>
       <c r="I85" t="n">
-        <v>0.5957000103080645</v>
+        <v>0.3766250156331807</v>
       </c>
       <c r="J85" t="n">
-        <v>31.18410000752192</v>
+        <v>21.92958301748149</v>
       </c>
       <c r="K85" t="n">
-        <v>14.17080000101123</v>
+        <v>13.55779200093821</v>
       </c>
       <c r="L85" t="n">
-        <v>1.29640000523068</v>
+        <v>0.7866249943617731</v>
       </c>
     </row>
     <row r="86">
       <c r="A86" t="n">
-        <v>0.247300005867146</v>
+        <v>0.1549159933347255</v>
       </c>
       <c r="B86" t="n">
-        <v>0.1273000088986009</v>
+        <v>0.06824999582022429</v>
       </c>
       <c r="C86" t="n">
-        <v>0.1085000112652779</v>
+        <v>0.06479100557044148</v>
       </c>
       <c r="D86" t="n">
-        <v>1.733900004182942</v>
+        <v>1.126832998124883</v>
       </c>
       <c r="E86" t="n">
-        <v>0.8753000001888722</v>
+        <v>0.4370420065242797</v>
       </c>
       <c r="F86" t="n">
-        <v>0.2742999931797385</v>
+        <v>0.170166022144258</v>
       </c>
       <c r="G86" t="n">
-        <v>7.370999999693595</v>
+        <v>4.78254197514616</v>
       </c>
       <c r="H86" t="n">
-        <v>3.539700002875179</v>
+        <v>2.039916987996548</v>
       </c>
       <c r="I86" t="n">
-        <v>0.5841000092914328</v>
+        <v>0.3720420063473284</v>
       </c>
       <c r="J86" t="n">
-        <v>30.1949999993667</v>
+        <v>21.38804100104608</v>
       </c>
       <c r="K86" t="n">
-        <v>13.02660000510514</v>
+        <v>8.371459000045434</v>
       </c>
       <c r="L86" t="n">
-        <v>1.279999996768311</v>
+        <v>0.8135829993989319</v>
       </c>
     </row>
     <row r="87">
       <c r="A87" t="n">
-        <v>0.2739000046858564</v>
+        <v>0.1705000177025795</v>
       </c>
       <c r="B87" t="n">
-        <v>0.1339000009465963</v>
+        <v>0.07199999527074397</v>
       </c>
       <c r="C87" t="n">
-        <v>0.1005999947665259</v>
+        <v>0.07124998955987394</v>
       </c>
       <c r="D87" t="n">
-        <v>1.643299998249859</v>
+        <v>0.9517079743091017</v>
       </c>
       <c r="E87" t="n">
-        <v>0.7451999990735203</v>
+        <v>0.3972910053562373</v>
       </c>
       <c r="F87" t="n">
-        <v>0.269800002570264</v>
+        <v>0.167207996128127</v>
       </c>
       <c r="G87" t="n">
-        <v>7.231600000523031</v>
+        <v>4.714791983133182</v>
       </c>
       <c r="H87" t="n">
-        <v>3.446300004725344</v>
+        <v>5.809041002066806</v>
       </c>
       <c r="I87" t="n">
-        <v>0.6003000016789883</v>
+        <v>0.3765000146813691</v>
       </c>
       <c r="J87" t="n">
-        <v>30.80979999504052</v>
+        <v>21.46454202011228</v>
       </c>
       <c r="K87" t="n">
-        <v>13.36019999871496</v>
+        <v>8.474625006783754</v>
       </c>
       <c r="L87" t="n">
-        <v>1.283300007344224</v>
+        <v>0.8256669971160591</v>
       </c>
     </row>
     <row r="88">
       <c r="A88" t="n">
-        <v>0.2587999915704131</v>
+        <v>0.2237909939140081</v>
       </c>
       <c r="B88" t="n">
-        <v>0.1327000063611194</v>
+        <v>0.1038339978549629</v>
       </c>
       <c r="C88" t="n">
-        <v>0.09839999256655574</v>
+        <v>0.079624995123595</v>
       </c>
       <c r="D88" t="n">
-        <v>1.644399992073886</v>
+        <v>0.9927920182235539</v>
       </c>
       <c r="E88" t="n">
-        <v>0.8040999964578077</v>
+        <v>0.411209010053426</v>
       </c>
       <c r="F88" t="n">
-        <v>0.2641000028233975</v>
+        <v>0.1769580121617764</v>
       </c>
       <c r="G88" t="n">
-        <v>7.2851000004448</v>
+        <v>4.802584007848054</v>
       </c>
       <c r="H88" t="n">
-        <v>3.430100012337789</v>
+        <v>3.001749981194735</v>
       </c>
       <c r="I88" t="n">
-        <v>0.5959999980404973</v>
+        <v>0.966791994869709</v>
       </c>
       <c r="J88" t="n">
-        <v>31.19799999694806</v>
+        <v>21.74237501458265</v>
       </c>
       <c r="K88" t="n">
-        <v>13.74979999673087</v>
+        <v>8.571083977585658</v>
       </c>
       <c r="L88" t="n">
-        <v>1.315599991357885</v>
+        <v>0.8597080013714731</v>
       </c>
     </row>
     <row r="89">
       <c r="A89" t="n">
-        <v>0.259600012213923</v>
+        <v>0.1615829824004322</v>
       </c>
       <c r="B89" t="n">
-        <v>0.1317999995080754</v>
+        <v>0.06737498915754259</v>
       </c>
       <c r="C89" t="n">
-        <v>0.09709999721962959</v>
+        <v>0.06049999501556158</v>
       </c>
       <c r="D89" t="n">
-        <v>1.748999988194555</v>
+        <v>1.128291012719274</v>
       </c>
       <c r="E89" t="n">
-        <v>0.8531000057701021</v>
+        <v>0.4450409905984998</v>
       </c>
       <c r="F89" t="n">
-        <v>0.2665000065462664</v>
+        <v>0.1801670005079359</v>
       </c>
       <c r="G89" t="n">
-        <v>7.562099999631755</v>
+        <v>4.670124995755032</v>
       </c>
       <c r="H89" t="n">
-        <v>3.366699995240197</v>
+        <v>1.945125026395544</v>
       </c>
       <c r="I89" t="n">
-        <v>0.592199998209253</v>
+        <v>0.3926249919459224</v>
       </c>
       <c r="J89" t="n">
-        <v>31.71949999523349</v>
+        <v>21.71191599336453</v>
       </c>
       <c r="K89" t="n">
-        <v>14.47530000586994</v>
+        <v>8.874084014678374</v>
       </c>
       <c r="L89" t="n">
-        <v>1.270299995667301</v>
+        <v>0.8121669816318899</v>
       </c>
     </row>
     <row r="90">
       <c r="A90" t="n">
-        <v>0.2723999932641163</v>
+        <v>0.1656670065131038</v>
       </c>
       <c r="B90" t="n">
-        <v>0.1272999943466857</v>
+        <v>0.0704580161254853</v>
       </c>
       <c r="C90" t="n">
-        <v>0.09710001177154481</v>
+        <v>0.06074999691918492</v>
       </c>
       <c r="D90" t="n">
-        <v>1.596700007212348</v>
+        <v>0.9656670154072344</v>
       </c>
       <c r="E90" t="n">
-        <v>0.7877000025473535</v>
+        <v>0.4058339982293546</v>
       </c>
       <c r="F90" t="n">
-        <v>0.2668000088306144</v>
+        <v>0.1725830079521984</v>
       </c>
       <c r="G90" t="n">
-        <v>7.105299999238923</v>
+        <v>4.650667018722743</v>
       </c>
       <c r="H90" t="n">
-        <v>3.438900006585754</v>
+        <v>1.959000015631318</v>
       </c>
       <c r="I90" t="n">
-        <v>0.5875999922864139</v>
+        <v>0.3720829845406115</v>
       </c>
       <c r="J90" t="n">
-        <v>31.40269999857992</v>
+        <v>21.52999999816529</v>
       </c>
       <c r="K90" t="n">
-        <v>14.20130000042263</v>
+        <v>8.756791998166591</v>
       </c>
       <c r="L90" t="n">
-        <v>1.265800005057827</v>
+        <v>0.8427500142715871</v>
       </c>
     </row>
     <row r="91">
       <c r="A91" t="n">
-        <v>0.2690000110305846</v>
+        <v>0.1570000022184104</v>
       </c>
       <c r="B91" t="n">
-        <v>0.1423999929102138</v>
+        <v>0.07220800034701824</v>
       </c>
       <c r="C91" t="n">
-        <v>0.0990999978967011</v>
+        <v>0.06041600136086345</v>
       </c>
       <c r="D91" t="n">
-        <v>1.614399996469729</v>
+        <v>1.007416023639962</v>
       </c>
       <c r="E91" t="n">
-        <v>0.7979000074556097</v>
+        <v>0.431458989623934</v>
       </c>
       <c r="F91" t="n">
-        <v>0.2668999950401485</v>
+        <v>0.1775419805198908</v>
       </c>
       <c r="G91" t="n">
-        <v>7.043200006592087</v>
+        <v>4.666167020332068</v>
       </c>
       <c r="H91" t="n">
-        <v>3.240000005462207</v>
+        <v>1.871791988378391</v>
       </c>
       <c r="I91" t="n">
-        <v>0.5854999908478931</v>
+        <v>0.3695000195875764</v>
       </c>
       <c r="J91" t="n">
-        <v>31.89159999601543</v>
+        <v>21.40795800369233</v>
       </c>
       <c r="K91" t="n">
-        <v>14.05810000142083</v>
+        <v>8.728832995984703</v>
       </c>
       <c r="L91" t="n">
-        <v>1.267699990421534</v>
+        <v>0.8132910006679595</v>
       </c>
     </row>
     <row r="92">
       <c r="A92" t="n">
-        <v>0.2831999881891534</v>
+        <v>0.1868330000434071</v>
       </c>
       <c r="B92" t="n">
-        <v>0.127399995108135</v>
+        <v>0.0679589866194874</v>
       </c>
       <c r="C92" t="n">
-        <v>0.09609998960513622</v>
+        <v>0.06287501309998333</v>
       </c>
       <c r="D92" t="n">
-        <v>1.668500000960194</v>
+        <v>1.05966700357385</v>
       </c>
       <c r="E92" t="n">
-        <v>0.8353000011993572</v>
+        <v>0.4282080044504255</v>
       </c>
       <c r="F92" t="n">
-        <v>0.2724999940255657</v>
+        <v>0.1722080050967634</v>
       </c>
       <c r="G92" t="n">
-        <v>7.346300000790507</v>
+        <v>4.824250005185604</v>
       </c>
       <c r="H92" t="n">
-        <v>3.48320000921376</v>
+        <v>2.120541990734637</v>
       </c>
       <c r="I92" t="n">
-        <v>0.5969000048935413</v>
+        <v>0.3787499736063182</v>
       </c>
       <c r="J92" t="n">
-        <v>30.10530000028666</v>
+        <v>21.00549999158829</v>
       </c>
       <c r="K92" t="n">
-        <v>13.07769998675212</v>
+        <v>8.203415985917673</v>
       </c>
       <c r="L92" t="n">
-        <v>1.26530000125058</v>
+        <v>0.8211660024244338</v>
       </c>
     </row>
     <row r="93">
       <c r="A93" t="n">
-        <v>0.2500999980838969</v>
+        <v>0.1432079880032688</v>
       </c>
       <c r="B93" t="n">
-        <v>0.1172999909613281</v>
+        <v>0.06166700040921569</v>
       </c>
       <c r="C93" t="n">
-        <v>0.0973999995039776</v>
+        <v>0.059375015553087</v>
       </c>
       <c r="D93" t="n">
-        <v>1.610899998922832</v>
+        <v>0.9452080121263862</v>
       </c>
       <c r="E93" t="n">
-        <v>0.9481000015512109</v>
+        <v>0.4024169757030904</v>
       </c>
       <c r="F93" t="n">
-        <v>0.273199999355711</v>
+        <v>0.2067089953925461</v>
       </c>
       <c r="G93" t="n">
-        <v>7.135799998650327</v>
+        <v>4.728917003376409</v>
       </c>
       <c r="H93" t="n">
-        <v>3.243899991502985</v>
+        <v>1.930917002027854</v>
       </c>
       <c r="I93" t="n">
-        <v>0.5875000060768798</v>
+        <v>0.3748330054804683</v>
       </c>
       <c r="J93" t="n">
-        <v>30.83119999791961</v>
+        <v>21.33520899224095</v>
       </c>
       <c r="K93" t="n">
-        <v>13.29129999794532</v>
+        <v>8.465833001537248</v>
       </c>
       <c r="L93" t="n">
-        <v>1.2816000089515</v>
+        <v>0.8431670139543712</v>
       </c>
     </row>
     <row r="94">
       <c r="A94" t="n">
-        <v>0.269500000285916</v>
+        <v>0.1684999733697623</v>
       </c>
       <c r="B94" t="n">
-        <v>0.1442999928258359</v>
+        <v>0.07174999336712062</v>
       </c>
       <c r="C94" t="n">
-        <v>0.1003999932436273</v>
+        <v>0.06066699279472232</v>
       </c>
       <c r="D94" t="n">
-        <v>1.521500002127141</v>
+        <v>0.9154170111287385</v>
       </c>
       <c r="E94" t="n">
-        <v>0.6907000060891733</v>
+        <v>0.3594160079956055</v>
       </c>
       <c r="F94" t="n">
-        <v>0.2704999933484942</v>
+        <v>0.1760409795679152</v>
       </c>
       <c r="G94" t="n">
-        <v>7.341100004850887</v>
+        <v>4.775082983542234</v>
       </c>
       <c r="H94" t="n">
-        <v>3.408999997191131</v>
+        <v>1.894957997137681</v>
       </c>
       <c r="I94" t="n">
-        <v>0.5895000067539513</v>
+        <v>0.3712500038091093</v>
       </c>
       <c r="J94" t="n">
-        <v>31.3041999907</v>
+        <v>21.52754200506024</v>
       </c>
       <c r="K94" t="n">
-        <v>13.90099999844097</v>
+        <v>8.782374992733821</v>
       </c>
       <c r="L94" t="n">
-        <v>1.275700007681735</v>
+        <v>0.8095420198515058</v>
       </c>
     </row>
     <row r="95">
       <c r="A95" t="n">
-        <v>0.3138000029139221</v>
+        <v>0.1442909997422248</v>
       </c>
       <c r="B95" t="n">
-        <v>0.1190000039059669</v>
+        <v>0.05979099660180509</v>
       </c>
       <c r="C95" t="n">
-        <v>0.1316999987466261</v>
+        <v>0.06070800009183586</v>
       </c>
       <c r="D95" t="n">
-        <v>1.694699996733107</v>
+        <v>0.9705830016173422</v>
       </c>
       <c r="E95" t="n">
-        <v>0.7730000070296228</v>
+        <v>0.4060830106027424</v>
       </c>
       <c r="F95" t="n">
-        <v>0.2703999925870448</v>
+        <v>0.178084010258317</v>
       </c>
       <c r="G95" t="n">
-        <v>7.448799995472655</v>
+        <v>4.758166993269697</v>
       </c>
       <c r="H95" t="n">
-        <v>3.392500002519228</v>
+        <v>2.021416992647573</v>
       </c>
       <c r="I95" t="n">
-        <v>0.5941999988863245</v>
+        <v>0.3737919905688614</v>
       </c>
       <c r="J95" t="n">
-        <v>31.3010999961989</v>
+        <v>21.83470901218243</v>
       </c>
       <c r="K95" t="n">
-        <v>13.74399999622256</v>
+        <v>8.903834008378908</v>
       </c>
       <c r="L95" t="n">
-        <v>1.28309999126941</v>
+        <v>0.8302500064019114</v>
       </c>
     </row>
     <row r="96">
       <c r="A96" t="n">
-        <v>0.2534000086598098</v>
+        <v>0.1517079945188016</v>
       </c>
       <c r="B96" t="n">
-        <v>0.123399993753992</v>
+        <v>0.06208400009199977</v>
       </c>
       <c r="C96" t="n">
-        <v>0.1023999939206988</v>
+        <v>0.05979198613204062</v>
       </c>
       <c r="D96" t="n">
-        <v>1.586600003065541</v>
+        <v>1.058374997228384</v>
       </c>
       <c r="E96" t="n">
-        <v>0.7614999922225252</v>
+        <v>0.4022080102004111</v>
       </c>
       <c r="F96" t="n">
-        <v>0.2706999948713928</v>
+        <v>0.1664169831201434</v>
       </c>
       <c r="G96" t="n">
-        <v>7.230699993669987</v>
+        <v>4.545416973996907</v>
       </c>
       <c r="H96" t="n">
-        <v>3.360000002430752</v>
+        <v>1.955957995960489</v>
       </c>
       <c r="I96" t="n">
-        <v>0.5983000010019168</v>
+        <v>0.3732089826371521</v>
       </c>
       <c r="J96" t="n">
-        <v>30.69739999773446</v>
+        <v>21.84937501442619</v>
       </c>
       <c r="K96" t="n">
-        <v>13.85659999505151</v>
+        <v>8.984499989310279</v>
       </c>
       <c r="L96" t="n">
-        <v>1.291599997784942</v>
+        <v>0.8139579731505364</v>
       </c>
     </row>
     <row r="97">
       <c r="A97" t="n">
-        <v>0.264299989794381</v>
+        <v>0.1650000049266964</v>
       </c>
       <c r="B97" t="n">
-        <v>0.1341000024694949</v>
+        <v>0.06799999391660094</v>
       </c>
       <c r="C97" t="n">
-        <v>0.09689999569673091</v>
+        <v>0.0605420209467411</v>
       </c>
       <c r="D97" t="n">
-        <v>1.635799999348819</v>
+        <v>0.9793339995667338</v>
       </c>
       <c r="E97" t="n">
-        <v>0.7794999983161688</v>
+        <v>0.4378749872557819</v>
       </c>
       <c r="F97" t="n">
-        <v>0.272899997071363</v>
+        <v>0.1739580184221268</v>
       </c>
       <c r="G97" t="n">
-        <v>7.036499999230728</v>
+        <v>4.511625011218712</v>
       </c>
       <c r="H97" t="n">
-        <v>3.298300012829714</v>
+        <v>1.87012497917749</v>
       </c>
       <c r="I97" t="n">
-        <v>0.6129999965196475</v>
+        <v>0.3710419987328351</v>
       </c>
       <c r="J97" t="n">
-        <v>30.29280000191648</v>
+        <v>21.14450000226498</v>
       </c>
       <c r="K97" t="n">
-        <v>12.82730000093579</v>
+        <v>8.275250002043322</v>
       </c>
       <c r="L97" t="n">
-        <v>1.270400010980666</v>
+        <v>0.8327909745275974</v>
       </c>
     </row>
     <row r="98">
       <c r="A98" t="n">
-        <v>0.2707999956328422</v>
+        <v>0.1580830139573663</v>
       </c>
       <c r="B98" t="n">
-        <v>0.1345999917248264</v>
+        <v>0.06808299804106355</v>
       </c>
       <c r="C98" t="n">
-        <v>0.09549999958835542</v>
+        <v>0.07533299503847957</v>
       </c>
       <c r="D98" t="n">
-        <v>1.700199994957075</v>
+        <v>1.045665994752198</v>
       </c>
       <c r="E98" t="n">
-        <v>0.7603999983984977</v>
+        <v>0.4071250150445849</v>
       </c>
       <c r="F98" t="n">
-        <v>0.2718000032473356</v>
+        <v>0.1721250009723008</v>
       </c>
       <c r="G98" t="n">
-        <v>7.463100002496503</v>
+        <v>4.791374987689778</v>
       </c>
       <c r="H98" t="n">
-        <v>3.492699994239956</v>
+        <v>2.070750022539869</v>
       </c>
       <c r="I98" t="n">
-        <v>0.6061000021873042</v>
+        <v>0.3715420025400817</v>
       </c>
       <c r="J98" t="n">
-        <v>30.87149999919347</v>
+        <v>21.27312499214895</v>
       </c>
       <c r="K98" t="n">
-        <v>13.79119999182876</v>
+        <v>8.733290975214913</v>
       </c>
       <c r="L98" t="n">
-        <v>1.267700004973449</v>
+        <v>0.8302080095745623</v>
       </c>
     </row>
     <row r="99">
       <c r="A99" t="n">
-        <v>0.2898000093409792</v>
+        <v>0.1682500005699694</v>
       </c>
       <c r="B99" t="n">
-        <v>0.1628999889362603</v>
+        <v>0.08195801638066769</v>
       </c>
       <c r="C99" t="n">
-        <v>0.09699999645818025</v>
+        <v>0.05970898200757802</v>
       </c>
       <c r="D99" t="n">
-        <v>1.736800011713058</v>
+        <v>1.048458012519404</v>
       </c>
       <c r="E99" t="n">
-        <v>0.8170999935828149</v>
+        <v>0.4672089999075979</v>
       </c>
       <c r="F99" t="n">
-        <v>0.2693000133149326</v>
+        <v>0.1724169997032732</v>
       </c>
       <c r="G99" t="n">
-        <v>7.441299996571615</v>
+        <v>4.714790993602946</v>
       </c>
       <c r="H99" t="n">
-        <v>3.297600007499568</v>
+        <v>1.934749976499006</v>
       </c>
       <c r="I99" t="n">
-        <v>0.58970000827685</v>
+        <v>0.3737079969141632</v>
       </c>
       <c r="J99" t="n">
-        <v>30.7846000068821</v>
+        <v>21.18833400891162</v>
       </c>
       <c r="K99" t="n">
-        <v>13.28070000454318</v>
+        <v>8.515041990904137</v>
       </c>
       <c r="L99" t="n">
-        <v>1.303199998801574</v>
+        <v>0.8049999887589365</v>
       </c>
     </row>
     <row r="100">
       <c r="A100" t="n">
-        <v>0.2289000112796202</v>
+        <v>0.1322079915553331</v>
       </c>
       <c r="B100" t="n">
-        <v>0.1131000026362017</v>
+        <v>0.06004198803566396</v>
       </c>
       <c r="C100" t="n">
-        <v>0.0948999950196594</v>
+        <v>0.05916701047681272</v>
       </c>
       <c r="D100" t="n">
-        <v>1.681699999608099</v>
+        <v>0.9782499982975423</v>
       </c>
       <c r="E100" t="n">
-        <v>0.7898000039858744</v>
+        <v>0.4222499846946448</v>
       </c>
       <c r="F100" t="n">
-        <v>0.2998999989358708</v>
+        <v>0.1717499981168658</v>
       </c>
       <c r="G100" t="n">
-        <v>7.507899994379841</v>
+        <v>4.741375014418736</v>
       </c>
       <c r="H100" t="n">
-        <v>3.449000010732561</v>
+        <v>1.997292012674734</v>
       </c>
       <c r="I100" t="n">
-        <v>0.5837999924551696</v>
+        <v>0.3697080246638507</v>
       </c>
       <c r="J100" t="n">
-        <v>31.89429998747073</v>
+        <v>21.61083300597966</v>
       </c>
       <c r="K100" t="n">
-        <v>14.299900009064</v>
+        <v>8.987499983049929</v>
       </c>
       <c r="L100" t="n">
-        <v>1.28529999346938</v>
+        <v>0.803542003268376</v>
       </c>
     </row>
     <row r="101">
       <c r="A101" t="n">
-        <v>0.2710000117076561</v>
+        <v>0.1590420142747462</v>
       </c>
       <c r="B101" t="n">
-        <v>0.1466999965487048</v>
+        <v>0.07341700256802142</v>
       </c>
       <c r="C101" t="n">
-        <v>0.09760000102687627</v>
+        <v>0.06004198803566396</v>
       </c>
       <c r="D101" t="n">
-        <v>1.636400003917515</v>
+        <v>0.9966250217985362</v>
       </c>
       <c r="E101" t="n">
-        <v>0.7941000076243654</v>
+        <v>0.4212910134810954</v>
       </c>
       <c r="F101" t="n">
-        <v>0.2801000082399696</v>
+        <v>0.1781669852789491</v>
       </c>
       <c r="G101" t="n">
-        <v>7.525599998189136</v>
+        <v>4.857083986280486</v>
       </c>
       <c r="H101" t="n">
-        <v>3.524500003550202</v>
+        <v>1.988542004255578</v>
       </c>
       <c r="I101" t="n">
-        <v>0.5926000012550503</v>
+        <v>0.378249998902902</v>
       </c>
       <c r="J101" t="n">
-        <v>30.83259999402799</v>
+        <v>21.50420797988772</v>
       </c>
       <c r="K101" t="n">
-        <v>13.77369998954237</v>
+        <v>8.79812499624677</v>
       </c>
       <c r="L101" t="n">
-        <v>1.285999998799525</v>
+        <v>0.8349590061698109</v>
       </c>
     </row>
   </sheetData>
